--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,24 +9,24 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="West Town" sheetId="3" r:id="rId3"/>
-    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="5" r:id="rId5"/>
-    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
-    <sheet name="Rogers Park" sheetId="7" r:id="rId7"/>
-    <sheet name="Douglas" sheetId="8" r:id="rId8"/>
-    <sheet name="Jefferson Park" sheetId="9" r:id="rId9"/>
-    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
-    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
-    <sheet name="Austin" sheetId="12" r:id="rId12"/>
-    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
-    <sheet name="Grand Boulevard" sheetId="14" r:id="rId14"/>
-    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
-    <sheet name="Loop" sheetId="16" r:id="rId16"/>
-    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
-    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
-    <sheet name="Mount Greenwood" sheetId="19" r:id="rId19"/>
-    <sheet name="Gage Park" sheetId="20" r:id="rId20"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="4" r:id="rId4"/>
+    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
+    <sheet name="Rogers Park" sheetId="6" r:id="rId6"/>
+    <sheet name="Douglas" sheetId="7" r:id="rId7"/>
+    <sheet name="Jefferson Park" sheetId="8" r:id="rId8"/>
+    <sheet name="West Town" sheetId="9" r:id="rId9"/>
+    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
+    <sheet name="Albany Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Grand Boulevard" sheetId="12" r:id="rId12"/>
+    <sheet name="Belmont Cragin" sheetId="13" r:id="rId13"/>
+    <sheet name="Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
+    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="South Shore" sheetId="17" r:id="rId17"/>
+    <sheet name="Mount Greenwood" sheetId="18" r:id="rId18"/>
+    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
+    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
     <sheet name="West Loop" sheetId="21" r:id="rId21"/>
     <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
     <sheet name="Humboldt Park" sheetId="23" r:id="rId23"/>
@@ -48,9 +48,9 @@
     <sheet name="Roseland" sheetId="39" r:id="rId39"/>
     <sheet name="Woodlawn" sheetId="40" r:id="rId40"/>
     <sheet name="Fuller Park" sheetId="41" r:id="rId41"/>
-    <sheet name="O'Hare" sheetId="42" r:id="rId42"/>
-    <sheet name="Little Italy, UIC" sheetId="43" r:id="rId43"/>
-    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Little Italy, UIC" sheetId="42" r:id="rId42"/>
+    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
+    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
     <sheet name="Bucktown" sheetId="45" r:id="rId45"/>
     <sheet name="Calumet Heights" sheetId="46" r:id="rId46"/>
     <sheet name="Edgewater" sheetId="47" r:id="rId47"/>
@@ -1242,322 +1242,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>18</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>31</v>
-      </c>
-      <c r="E8">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>29</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>25</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>70</v>
-      </c>
-      <c r="D9">
-        <v>58</v>
-      </c>
-      <c r="E9">
-        <v>63</v>
-      </c>
-      <c r="F9">
-        <v>65</v>
-      </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <v>58</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>73</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1843,7 +1527,1307 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>14</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
+        <v>9</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>13</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>24</v>
+      </c>
+      <c r="J3">
+        <v>24</v>
+      </c>
+      <c r="K3">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>42</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8">
+        <v>63</v>
+      </c>
+      <c r="J8">
+        <v>44</v>
+      </c>
+      <c r="K8">
+        <v>38</v>
+      </c>
+      <c r="L8">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>120</v>
+      </c>
+      <c r="C9">
+        <v>208</v>
+      </c>
+      <c r="D9">
+        <v>364</v>
+      </c>
+      <c r="E9">
+        <v>443</v>
+      </c>
+      <c r="F9">
+        <v>415</v>
+      </c>
+      <c r="G9">
+        <v>139</v>
+      </c>
+      <c r="H9">
+        <v>68</v>
+      </c>
+      <c r="I9">
+        <v>145</v>
+      </c>
+      <c r="J9">
+        <v>85</v>
+      </c>
+      <c r="K9">
+        <v>75</v>
+      </c>
+      <c r="L9">
+        <v>59</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>156</v>
+      </c>
+      <c r="C10">
+        <v>249</v>
+      </c>
+      <c r="D10">
+        <v>422</v>
+      </c>
+      <c r="E10">
+        <v>499</v>
+      </c>
+      <c r="F10">
+        <v>470</v>
+      </c>
+      <c r="G10">
+        <v>201</v>
+      </c>
+      <c r="H10">
+        <v>126</v>
+      </c>
+      <c r="I10">
+        <v>245</v>
+      </c>
+      <c r="J10">
+        <v>173</v>
+      </c>
+      <c r="K10">
+        <v>150</v>
+      </c>
+      <c r="L10">
+        <v>131</v>
+      </c>
+      <c r="M10">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>19</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>54</v>
+      </c>
+      <c r="D8">
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>49</v>
+      </c>
+      <c r="F8">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>47</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>39</v>
+      </c>
+      <c r="J8">
+        <v>28</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>29</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2153,240 +3137,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>9</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -2449,23 +3202,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -2481,20 +3234,32 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -2502,130 +3267,122 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
         <v>6</v>
       </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
       <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
         <v>11</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>14</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2633,184 +3390,52 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2818,349 +3443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
-      </c>
-      <c r="L2">
-        <v>13</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>41</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
-      </c>
-      <c r="H8">
-        <v>40</v>
-      </c>
-      <c r="I8">
-        <v>63</v>
-      </c>
-      <c r="J8">
-        <v>44</v>
-      </c>
-      <c r="K8">
-        <v>38</v>
-      </c>
-      <c r="L8">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>120</v>
-      </c>
-      <c r="C9">
-        <v>208</v>
-      </c>
-      <c r="D9">
-        <v>364</v>
-      </c>
-      <c r="E9">
-        <v>443</v>
-      </c>
-      <c r="F9">
-        <v>415</v>
-      </c>
-      <c r="G9">
-        <v>139</v>
-      </c>
-      <c r="H9">
-        <v>68</v>
-      </c>
-      <c r="I9">
-        <v>145</v>
-      </c>
-      <c r="J9">
-        <v>85</v>
-      </c>
-      <c r="K9">
-        <v>75</v>
-      </c>
-      <c r="L9">
-        <v>59</v>
-      </c>
-      <c r="M9">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>156</v>
-      </c>
-      <c r="C10">
-        <v>249</v>
-      </c>
-      <c r="D10">
-        <v>422</v>
-      </c>
-      <c r="E10">
-        <v>499</v>
-      </c>
-      <c r="F10">
-        <v>470</v>
-      </c>
-      <c r="G10">
-        <v>201</v>
-      </c>
-      <c r="H10">
-        <v>126</v>
-      </c>
-      <c r="I10">
-        <v>245</v>
-      </c>
-      <c r="J10">
-        <v>173</v>
-      </c>
-      <c r="K10">
-        <v>150</v>
-      </c>
-      <c r="L10">
-        <v>131</v>
-      </c>
-      <c r="M10">
-        <v>88</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3226,33 +3509,18 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
         <v>4</v>
       </c>
     </row>
@@ -3261,109 +3529,82 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
       <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3371,40 +3612,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3412,346 +3653,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
         <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7522,7 +7457,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7585,20 +7520,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7606,164 +7562,208 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
         <v>11</v>
       </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
         <v>18</v>
       </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
       <c r="K7">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>29</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
+      <c r="K8">
+        <v>25</v>
+      </c>
+      <c r="L8">
         <v>22</v>
       </c>
-      <c r="D8">
-        <v>26</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
       <c r="M8">
-        <v>7</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>70</v>
+      </c>
+      <c r="D9">
+        <v>58</v>
+      </c>
+      <c r="E9">
+        <v>63</v>
+      </c>
+      <c r="F9">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>58</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>73</v>
+      </c>
+      <c r="L9">
+        <v>66</v>
+      </c>
+      <c r="M9">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -10006,7 +10006,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10069,29 +10069,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -10101,157 +10104,206 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>60</v>
-      </c>
-      <c r="F6">
-        <v>43</v>
-      </c>
       <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>62</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>28</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>65</v>
-      </c>
-      <c r="F7">
-        <v>49</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>19</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>16</v>
+      <c r="B9">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>76</v>
+      </c>
+      <c r="E9">
+        <v>67</v>
+      </c>
+      <c r="F9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9">
+        <v>56</v>
+      </c>
+      <c r="I9">
+        <v>63</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>73</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -12742,7 +12794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12805,35 +12857,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12843,38 +12886,26 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12884,162 +12915,131 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="I4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
         <v>26</v>
-      </c>
-      <c r="C7">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
         <v>16</v>
       </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B8">
-        <v>42</v>
-      </c>
-      <c r="C8">
-        <v>62</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>28</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>70</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>76</v>
-      </c>
-      <c r="E9">
-        <v>67</v>
-      </c>
-      <c r="F9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>60</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
-      </c>
-      <c r="I9">
-        <v>63</v>
-      </c>
-      <c r="J9">
-        <v>41</v>
-      </c>
-      <c r="K9">
-        <v>64</v>
-      </c>
-      <c r="L9">
-        <v>73</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13578,230 +13578,6 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14073,7 +13849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14286,6 +14062,230 @@
       </c>
       <c r="M6">
         <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -15413,66 +15413,57 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="D3">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
+      <c r="K4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15480,40 +15471,34 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
         <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15521,40 +15506,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15562,40 +15547,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>26</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
         <v>13</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>15</v>
       </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -17737,7 +17722,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17800,174 +17785,221 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <v>9</v>
       </c>
-      <c r="B6">
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="F6">
+      <c r="I6">
         <v>11</v>
       </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>59</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>13</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>15</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
+      <c r="B8">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>73</v>
+      </c>
+      <c r="F8">
+        <v>44</v>
+      </c>
+      <c r="G8">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>35</v>
+      </c>
+      <c r="J8">
+        <v>32</v>
+      </c>
+      <c r="K8">
+        <v>39</v>
+      </c>
+      <c r="L8">
+        <v>38</v>
+      </c>
+      <c r="M8">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -19825,27 +19857,15 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -19853,35 +19873,20 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -19891,27 +19896,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="J4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -19920,39 +19913,33 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -19961,40 +19948,37 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>22</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -20002,40 +19986,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -21729,20 +21713,17 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21750,37 +21731,37 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -21789,34 +21770,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21824,22 +21811,25 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -21848,13 +21838,13 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -21862,40 +21852,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
         <v>14</v>
       </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
       <c r="D8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>14</v>
       </c>
       <c r="L8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -23512,7 +23502,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23575,37 +23565,55 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -23613,141 +23621,133 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+      <c r="F7">
+        <v>49</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
         <v>19</v>
       </c>
-      <c r="C7">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
       <c r="L7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="M7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>14</v>
-      </c>
-      <c r="D8">
-        <v>11</v>
-      </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>22</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8">
-        <v>9</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,24 +9,24 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="4" r:id="rId4"/>
-    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
-    <sheet name="Rogers Park" sheetId="6" r:id="rId6"/>
-    <sheet name="Douglas" sheetId="7" r:id="rId7"/>
-    <sheet name="Jefferson Park" sheetId="8" r:id="rId8"/>
-    <sheet name="West Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
-    <sheet name="Albany Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Grand Boulevard" sheetId="12" r:id="rId12"/>
-    <sheet name="Belmont Cragin" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
-    <sheet name="Austin" sheetId="16" r:id="rId16"/>
-    <sheet name="South Shore" sheetId="17" r:id="rId17"/>
-    <sheet name="Mount Greenwood" sheetId="18" r:id="rId18"/>
-    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
-    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
+    <sheet name="West Town" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="5" r:id="rId5"/>
+    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
+    <sheet name="Rogers Park" sheetId="7" r:id="rId7"/>
+    <sheet name="Douglas" sheetId="8" r:id="rId8"/>
+    <sheet name="Jefferson Park" sheetId="9" r:id="rId9"/>
+    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="Austin" sheetId="12" r:id="rId12"/>
+    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="14" r:id="rId14"/>
+    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
+    <sheet name="Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
+    <sheet name="Mount Greenwood" sheetId="19" r:id="rId19"/>
+    <sheet name="Gage Park" sheetId="20" r:id="rId20"/>
     <sheet name="West Loop" sheetId="21" r:id="rId21"/>
     <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
     <sheet name="Humboldt Park" sheetId="23" r:id="rId23"/>
@@ -48,9 +48,9 @@
     <sheet name="Roseland" sheetId="39" r:id="rId39"/>
     <sheet name="Woodlawn" sheetId="40" r:id="rId40"/>
     <sheet name="Fuller Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Little Italy, UIC" sheetId="42" r:id="rId42"/>
-    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
-    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
+    <sheet name="O'Hare" sheetId="42" r:id="rId42"/>
+    <sheet name="Little Italy, UIC" sheetId="43" r:id="rId43"/>
+    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
     <sheet name="Bucktown" sheetId="45" r:id="rId45"/>
     <sheet name="Calumet Heights" sheetId="46" r:id="rId46"/>
     <sheet name="Edgewater" sheetId="47" r:id="rId47"/>
@@ -69,30 +69,30 @@
     <sheet name="Avalon Park" sheetId="60" r:id="rId60"/>
     <sheet name="Brighton Park" sheetId="61" r:id="rId61"/>
     <sheet name="Lincoln Park" sheetId="62" r:id="rId62"/>
-    <sheet name="West Pullman" sheetId="63" r:id="rId63"/>
-    <sheet name="West Lawn" sheetId="64" r:id="rId64"/>
-    <sheet name="Little Village" sheetId="65" r:id="rId65"/>
-    <sheet name="Ukrainian Village" sheetId="66" r:id="rId66"/>
-    <sheet name="Archer Heights" sheetId="67" r:id="rId67"/>
-    <sheet name="Montclare" sheetId="68" r:id="rId68"/>
-    <sheet name="Old Town" sheetId="69" r:id="rId69"/>
-    <sheet name="Grant Park" sheetId="70" r:id="rId70"/>
-    <sheet name="Logan Square" sheetId="71" r:id="rId71"/>
-    <sheet name="West Elsdon" sheetId="72" r:id="rId72"/>
-    <sheet name="East Side" sheetId="73" r:id="rId73"/>
-    <sheet name="South Deering" sheetId="74" r:id="rId74"/>
-    <sheet name="Hermosa" sheetId="75" r:id="rId75"/>
-    <sheet name="Morgan Park" sheetId="76" r:id="rId76"/>
-    <sheet name="Boystown" sheetId="77" r:id="rId77"/>
-    <sheet name="Streeterville" sheetId="78" r:id="rId78"/>
-    <sheet name="Portage Park" sheetId="79" r:id="rId79"/>
-    <sheet name="Irving Park" sheetId="80" r:id="rId80"/>
-    <sheet name="West Ridge" sheetId="81" r:id="rId81"/>
-    <sheet name="Dunning" sheetId="82" r:id="rId82"/>
-    <sheet name="Clearing" sheetId="83" r:id="rId83"/>
-    <sheet name="Millenium Park" sheetId="84" r:id="rId84"/>
-    <sheet name="North Park" sheetId="85" r:id="rId85"/>
-    <sheet name="Printers Row" sheetId="86" r:id="rId86"/>
+    <sheet name="Printers Row" sheetId="63" r:id="rId63"/>
+    <sheet name="West Pullman" sheetId="64" r:id="rId64"/>
+    <sheet name="West Lawn" sheetId="65" r:id="rId65"/>
+    <sheet name="Little Village" sheetId="66" r:id="rId66"/>
+    <sheet name="Ukrainian Village" sheetId="67" r:id="rId67"/>
+    <sheet name="Archer Heights" sheetId="68" r:id="rId68"/>
+    <sheet name="Montclare" sheetId="69" r:id="rId69"/>
+    <sheet name="Old Town" sheetId="70" r:id="rId70"/>
+    <sheet name="Grant Park" sheetId="71" r:id="rId71"/>
+    <sheet name="Logan Square" sheetId="72" r:id="rId72"/>
+    <sheet name="West Elsdon" sheetId="73" r:id="rId73"/>
+    <sheet name="East Side" sheetId="74" r:id="rId74"/>
+    <sheet name="South Deering" sheetId="75" r:id="rId75"/>
+    <sheet name="Hermosa" sheetId="76" r:id="rId76"/>
+    <sheet name="Morgan Park" sheetId="77" r:id="rId77"/>
+    <sheet name="Boystown" sheetId="78" r:id="rId78"/>
+    <sheet name="Streeterville" sheetId="79" r:id="rId79"/>
+    <sheet name="Portage Park" sheetId="80" r:id="rId80"/>
+    <sheet name="Irving Park" sheetId="81" r:id="rId81"/>
+    <sheet name="West Ridge" sheetId="82" r:id="rId82"/>
+    <sheet name="Dunning" sheetId="83" r:id="rId83"/>
+    <sheet name="Clearing" sheetId="84" r:id="rId84"/>
+    <sheet name="Millenium Park" sheetId="85" r:id="rId85"/>
+    <sheet name="North Park" sheetId="86" r:id="rId86"/>
     <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
     <sheet name="Pullman" sheetId="88" r:id="rId88"/>
     <sheet name="Galewood" sheetId="89" r:id="rId89"/>
@@ -890,16 +890,16 @@
         <v>65</v>
       </c>
       <c r="H2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2">
         <v>102</v>
@@ -913,10 +913,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>96</v>
@@ -931,13 +931,13 @@
         <v>87</v>
       </c>
       <c r="H3">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I3">
         <v>144</v>
       </c>
       <c r="J3">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K3">
         <v>155</v>
@@ -1117,40 +1117,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C9">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D9">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E9">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F9">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G9">
         <v>350</v>
       </c>
       <c r="H9">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I9">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J9">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K9">
         <v>357</v>
       </c>
       <c r="L9">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M9">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1158,40 +1158,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C10">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="D10">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="E10">
-        <v>1531</v>
+        <v>1538</v>
       </c>
       <c r="F10">
-        <v>1560</v>
+        <v>1571</v>
       </c>
       <c r="G10">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="H10">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="I10">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J10">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K10">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L10">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M10">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1199,40 +1199,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C11">
-        <v>1536</v>
+        <v>1541</v>
       </c>
       <c r="D11">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="E11">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="F11">
-        <v>2111</v>
+        <v>2124</v>
       </c>
       <c r="G11">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="H11">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="I11">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="J11">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="K11">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="L11">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="M11">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -1241,6 +1241,322 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>25</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>70</v>
+      </c>
+      <c r="D9">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>63</v>
+      </c>
+      <c r="F9">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>58</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>73</v>
+      </c>
+      <c r="L9">
+        <v>66</v>
+      </c>
+      <c r="M9">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1416,7 +1732,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -1434,7 +1750,7 @@
         <v>13</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1498,7 +1814,7 @@
         <v>37</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8">
         <v>31</v>
@@ -1516,7 +1832,7 @@
         <v>39</v>
       </c>
       <c r="L8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M8">
         <v>17</v>
@@ -1527,7 +1843,317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>28</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>58</v>
+      </c>
+      <c r="G8">
+        <v>51</v>
+      </c>
+      <c r="H8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>53</v>
+      </c>
+      <c r="C9">
+        <v>75</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>93</v>
+      </c>
+      <c r="G9">
+        <v>74</v>
+      </c>
+      <c r="H9">
+        <v>58</v>
+      </c>
+      <c r="I9">
+        <v>51</v>
+      </c>
+      <c r="J9">
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>49</v>
+      </c>
+      <c r="L9">
+        <v>38</v>
+      </c>
+      <c r="M9">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1612,6 +2238,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>1</v>
       </c>
@@ -1717,7 +2346,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -1758,7 +2387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2007,7 +2636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2192,7 +2821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2429,7 +3058,7 @@
         <v>42</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8">
         <v>63</v>
@@ -2444,7 +3073,7 @@
         <v>32</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2461,10 +3090,10 @@
         <v>364</v>
       </c>
       <c r="E9">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F9">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G9">
         <v>139</v>
@@ -2473,13 +3102,13 @@
         <v>68</v>
       </c>
       <c r="I9">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J9">
         <v>85</v>
       </c>
       <c r="K9">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L9">
         <v>59</v>
@@ -2502,31 +3131,31 @@
         <v>422</v>
       </c>
       <c r="E10">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F10">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="G10">
         <v>201</v>
       </c>
       <c r="H10">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I10">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J10">
         <v>173</v>
       </c>
       <c r="K10">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L10">
         <v>131</v>
       </c>
       <c r="M10">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2534,7 +3163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2769,7 +3398,7 @@
         <v>20</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7">
         <v>11</v>
@@ -2810,7 +3439,7 @@
         <v>39</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8">
         <v>27</v>
@@ -2827,317 +3456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>27</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>40</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>51</v>
-      </c>
-      <c r="H8">
-        <v>23</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>17</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>52</v>
-      </c>
-      <c r="C9">
-        <v>74</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>93</v>
-      </c>
-      <c r="G9">
-        <v>74</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
-      </c>
-      <c r="I9">
-        <v>51</v>
-      </c>
-      <c r="J9">
-        <v>45</v>
-      </c>
-      <c r="K9">
-        <v>49</v>
-      </c>
-      <c r="L9">
-        <v>38</v>
-      </c>
-      <c r="M9">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3390,7 +3709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3436,257 +3755,6 @@
       </c>
       <c r="C4">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>26</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3760,7 +3828,7 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -3947,7 +4015,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -3976,10 +4044,10 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8">
         <v>42</v>
@@ -3994,7 +4062,7 @@
         <v>74</v>
       </c>
       <c r="H8">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I8">
         <v>51</v>
@@ -4079,7 +4147,7 @@
         <v>11</v>
       </c>
       <c r="J10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -4367,7 +4435,7 @@
         <v>37</v>
       </c>
       <c r="F19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19">
         <v>31</v>
@@ -4385,7 +4453,7 @@
         <v>39</v>
       </c>
       <c r="L19">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M19">
         <v>17</v>
@@ -4519,7 +4587,7 @@
         <v>33</v>
       </c>
       <c r="B23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23">
         <v>13</v>
@@ -4546,7 +4614,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L23">
         <v>12</v>
@@ -4597,6 +4665,9 @@
       <c r="F25">
         <v>4</v>
       </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
       <c r="K25">
         <v>2</v>
       </c>
@@ -4647,7 +4718,7 @@
         <v>20</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27">
         <v>14</v>
@@ -4685,13 +4756,13 @@
         <v>76</v>
       </c>
       <c r="E28">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F28">
         <v>86</v>
       </c>
       <c r="G28">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H28">
         <v>56</v>
@@ -4764,7 +4835,7 @@
         <v>22</v>
       </c>
       <c r="D30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E30">
         <v>26</v>
@@ -4779,7 +4850,7 @@
         <v>3</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>8</v>
@@ -4834,10 +4905,10 @@
         <v>75</v>
       </c>
       <c r="E32">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F32">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G32">
         <v>88</v>
@@ -4849,7 +4920,7 @@
         <v>73</v>
       </c>
       <c r="J32">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K32">
         <v>58</v>
@@ -4965,13 +5036,13 @@
         <v>70</v>
       </c>
       <c r="D36">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36">
         <v>63</v>
       </c>
       <c r="F36">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G36">
         <v>34</v>
@@ -5137,13 +5208,13 @@
         <v>17</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>10</v>
@@ -5175,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F42">
         <v>6</v>
@@ -5222,7 +5293,7 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43">
         <v>4</v>
@@ -5237,7 +5308,7 @@
         <v>6</v>
       </c>
       <c r="L43">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M43">
         <v>8</v>
@@ -5301,7 +5372,7 @@
         <v>12</v>
       </c>
       <c r="I45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J45">
         <v>8</v>
@@ -5386,7 +5457,7 @@
         <v>39</v>
       </c>
       <c r="J47">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K47">
         <v>27</v>
@@ -5471,7 +5542,7 @@
         <v>8</v>
       </c>
       <c r="K49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L49">
         <v>6</v>
@@ -5617,31 +5688,31 @@
         <v>422</v>
       </c>
       <c r="E53">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F53">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="G53">
         <v>201</v>
       </c>
       <c r="H53">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I53">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J53">
         <v>173</v>
       </c>
       <c r="K53">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L53">
         <v>131</v>
       </c>
       <c r="M53">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5879,7 +5950,7 @@
         <v>18</v>
       </c>
       <c r="E61">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F61">
         <v>34</v>
@@ -5926,7 +5997,7 @@
         <v>19</v>
       </c>
       <c r="G62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H62">
         <v>7</v>
@@ -6052,7 +6123,7 @@
         <v>15</v>
       </c>
       <c r="I65">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J65">
         <v>8</v>
@@ -6116,13 +6187,13 @@
         <v>10</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D67">
         <v>6</v>
       </c>
       <c r="E67">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F67">
         <v>13</v>
@@ -6166,7 +6237,7 @@
         <v>19</v>
       </c>
       <c r="F68">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -6333,7 +6404,7 @@
         <v>5</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -6391,7 +6462,7 @@
         <v>26</v>
       </c>
       <c r="K74">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L74">
         <v>12</v>
@@ -6407,6 +6478,9 @@
       <c r="B75">
         <v>1</v>
       </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
       <c r="D75">
         <v>1</v>
       </c>
@@ -6455,7 +6529,7 @@
         <v>32</v>
       </c>
       <c r="H76">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I76">
         <v>35</v>
@@ -6490,10 +6564,10 @@
         <v>52</v>
       </c>
       <c r="F77">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G77">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H77">
         <v>38</v>
@@ -6519,7 +6593,7 @@
         <v>88</v>
       </c>
       <c r="B78">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C78">
         <v>23</v>
@@ -6589,7 +6663,7 @@
         <v>13</v>
       </c>
       <c r="H80">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I80">
         <v>15</v>
@@ -6615,7 +6689,7 @@
         <v>19</v>
       </c>
       <c r="C81">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D81">
         <v>6</v>
@@ -6843,7 +6917,7 @@
         <v>25</v>
       </c>
       <c r="C87">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D87">
         <v>15</v>
@@ -6852,7 +6926,7 @@
         <v>24</v>
       </c>
       <c r="F87">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G87">
         <v>32</v>
@@ -6864,7 +6938,7 @@
         <v>18</v>
       </c>
       <c r="J87">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K87">
         <v>21</v>
@@ -6887,7 +6961,7 @@
         <v>11</v>
       </c>
       <c r="D88">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E88">
         <v>10</v>
@@ -7036,7 +7110,7 @@
         <v>14</v>
       </c>
       <c r="D92">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E92">
         <v>23</v>
@@ -7159,7 +7233,7 @@
         <v>40</v>
       </c>
       <c r="E95">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F95">
         <v>49</v>
@@ -7168,7 +7242,7 @@
         <v>12</v>
       </c>
       <c r="H95">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I95">
         <v>15</v>
@@ -7241,7 +7315,7 @@
         <v>16</v>
       </c>
       <c r="E97">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F97">
         <v>17</v>
@@ -7314,40 +7388,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C99">
-        <v>1536</v>
+        <v>1541</v>
       </c>
       <c r="D99">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="E99">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="F99">
-        <v>2111</v>
+        <v>2124</v>
       </c>
       <c r="G99">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="H99">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="I99">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="J99">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="K99">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="L99">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="M99">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -7457,7 +7531,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7520,41 +7594,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7562,208 +7615,164 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>70</v>
-      </c>
-      <c r="D9">
-        <v>58</v>
-      </c>
-      <c r="E9">
-        <v>63</v>
-      </c>
-      <c r="F9">
-        <v>65</v>
-      </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <v>58</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>73</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7972,7 +7981,7 @@
         <v>12</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>19</v>
@@ -8013,7 +8022,7 @@
         <v>14</v>
       </c>
       <c r="D9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9">
         <v>23</v>
@@ -8274,7 +8283,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -8315,7 +8324,7 @@
         <v>15</v>
       </c>
       <c r="I8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J8">
         <v>8</v>
@@ -8523,13 +8532,13 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -8564,13 +8573,13 @@
         <v>17</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -8718,7 +8727,7 @@
         <v>7</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3">
         <v>12</v>
@@ -8798,7 +8807,7 @@
         <v>23</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7">
         <v>19</v>
@@ -8824,10 +8833,10 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8">
         <v>45</v>
@@ -8865,10 +8874,10 @@
         <v>75</v>
       </c>
       <c r="E9">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F9">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G9">
         <v>88</v>
@@ -8880,7 +8889,7 @@
         <v>73</v>
       </c>
       <c r="J9">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K9">
         <v>58</v>
@@ -9058,7 +9067,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -9099,7 +9108,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>23</v>
@@ -10006,7 +10015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10069,32 +10078,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -10104,206 +10110,157 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>6</v>
       </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>7</v>
       </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>61</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
       <c r="G6">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>66</v>
+      </c>
+      <c r="F7">
+        <v>49</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
+      <c r="K7">
+        <v>19</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7">
         <v>16</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>23</v>
-      </c>
-      <c r="H7">
-        <v>22</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>42</v>
-      </c>
-      <c r="C8">
-        <v>62</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>28</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>70</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>76</v>
-      </c>
-      <c r="E9">
-        <v>67</v>
-      </c>
-      <c r="F9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>60</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
-      </c>
-      <c r="I9">
-        <v>63</v>
-      </c>
-      <c r="J9">
-        <v>41</v>
-      </c>
-      <c r="K9">
-        <v>64</v>
-      </c>
-      <c r="L9">
-        <v>73</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -11328,6 +11285,9 @@
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
       <c r="H5">
         <v>4</v>
       </c>
@@ -11352,7 +11312,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -11393,13 +11353,13 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>13</v>
@@ -11518,7 +11478,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -11681,7 +11641,7 @@
         <v>26</v>
       </c>
       <c r="K7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>12</v>
@@ -11779,7 +11739,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -11858,7 +11818,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -11905,7 +11865,7 @@
         <v>16</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>13</v>
@@ -11937,7 +11897,7 @@
         <v>25</v>
       </c>
       <c r="C9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>15</v>
@@ -11946,7 +11906,7 @@
         <v>24</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9">
         <v>32</v>
@@ -11958,7 +11918,7 @@
         <v>18</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9">
         <v>21</v>
@@ -12366,7 +12326,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -12445,7 +12405,7 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -12681,7 +12641,7 @@
         <v>13</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>11</v>
@@ -12725,7 +12685,7 @@
         <v>30</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9">
         <v>19</v>
@@ -12763,10 +12723,10 @@
         <v>52</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10">
         <v>38</v>
@@ -12794,7 +12754,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12857,26 +12817,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12886,26 +12855,38 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12915,131 +12896,162 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="I7">
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>15</v>
       </c>
-      <c r="J7">
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K7">
+      <c r="B8">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>62</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
         <v>8</v>
       </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>76</v>
+      </c>
+      <c r="E9">
+        <v>68</v>
+      </c>
+      <c r="F9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>56</v>
+      </c>
+      <c r="I9">
+        <v>63</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>73</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13229,7 +13241,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -13270,7 +13282,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -13578,6 +13590,230 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13849,7 +14085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13958,7 +14194,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -14037,7 +14273,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -14062,230 +14298,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -14846,7 +14858,7 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -14887,7 +14899,7 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8">
         <v>14</v>
@@ -15413,57 +15425,66 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>1</v>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15471,34 +15492,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
         <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15506,40 +15533,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15547,40 +15574,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
         <v>9</v>
       </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
+      <c r="K7">
         <v>8</v>
       </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>13</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
       <c r="L7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -16117,7 +16144,7 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -16158,7 +16185,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -16548,7 +16575,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -16586,7 +16613,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -16950,7 +16977,7 @@
         <v>15</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -16991,7 +17018,7 @@
         <v>19</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -17624,7 +17651,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -17685,7 +17712,7 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -17722,7 +17749,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17785,221 +17812,174 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
       <c r="L3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
       <c r="J6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>31</v>
-      </c>
       <c r="C7">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B8">
-        <v>33</v>
-      </c>
-      <c r="C8">
-        <v>52</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>73</v>
-      </c>
-      <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>32</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>35</v>
-      </c>
-      <c r="J8">
-        <v>32</v>
-      </c>
-      <c r="K8">
-        <v>39</v>
-      </c>
-      <c r="L8">
-        <v>38</v>
-      </c>
-      <c r="M8">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -18671,7 +18651,13 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
       <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>2</v>
       </c>
     </row>
@@ -18680,21 +18666,18 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>1</v>
       </c>
     </row>
@@ -18703,28 +18686,28 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -18741,34 +18724,37 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -18776,40 +18762,40 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>29</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
         <v>8</v>
       </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
       <c r="L6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18818,6 +18804,217 @@
 </file>
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18939,7 +19136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19152,7 +19349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19302,7 +19499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19439,7 +19636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19526,261 +19723,6 @@
       </c>
       <c r="F5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>13</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>12</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>17</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>38</v>
-      </c>
-      <c r="F6">
-        <v>71</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>18</v>
-      </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>47</v>
-      </c>
-      <c r="F7">
-        <v>89</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
-      </c>
-      <c r="I7">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>13</v>
-      </c>
-      <c r="K7">
-        <v>21</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -19857,15 +19799,27 @@
         <v>2</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -19873,20 +19827,35 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -19896,15 +19865,27 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -19913,33 +19894,39 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -19948,37 +19935,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -19986,40 +19976,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="L8">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -20028,6 +20018,261 @@
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>12</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>71</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>47</v>
+      </c>
+      <c r="F7">
+        <v>89</v>
+      </c>
+      <c r="G7">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20186,7 +20431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20449,7 +20694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20637,9 +20882,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -20650,9 +20895,10 @@
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20672,13 +20918,16 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
         <v>2024</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -20689,7 +20938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -20700,21 +20949,24 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -20728,7 +20980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -20748,9 +21000,12 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>2</v>
       </c>
     </row>
@@ -20759,7 +21014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20956,7 +21211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21076,7 +21331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21235,7 +21490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21321,7 +21576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21472,174 +21727,6 @@
         <v>4</v>
       </c>
       <c r="J7">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -21713,17 +21800,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21731,37 +21821,37 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -21770,40 +21860,34 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21811,25 +21895,22 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -21838,13 +21919,13 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -21852,40 +21933,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
       <c r="G8">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
         <v>12</v>
       </c>
-      <c r="I8">
-        <v>9</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
       <c r="M8">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -21894,6 +21975,174 @@
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22075,22 +22324,22 @@
         <v>8</v>
       </c>
       <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
         <v>8</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -22116,7 +22365,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -22131,7 +22380,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -22142,7 +22391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22317,7 +22566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22415,7 +22664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22624,7 +22873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22743,7 +22992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22915,9 +23164,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -22931,11 +23180,9 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22958,314 +23205,109 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>2</v>
       </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
       <c r="F5">
-        <v>22</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>3</v>
       </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>6</v>
       </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -23502,7 +23544,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23565,55 +23607,40 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -23621,133 +23648,141 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
         <v>22</v>
       </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>65</v>
-      </c>
-      <c r="F7">
-        <v>49</v>
-      </c>
-      <c r="G7">
+      <c r="H8">
         <v>12</v>
       </c>
-      <c r="H7">
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
         <v>11</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>19</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,24 +9,24 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="West Town" sheetId="3" r:id="rId3"/>
-    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="5" r:id="rId5"/>
-    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
-    <sheet name="Rogers Park" sheetId="7" r:id="rId7"/>
-    <sheet name="Douglas" sheetId="8" r:id="rId8"/>
-    <sheet name="Jefferson Park" sheetId="9" r:id="rId9"/>
-    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
-    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
-    <sheet name="Austin" sheetId="12" r:id="rId12"/>
-    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
-    <sheet name="Grand Boulevard" sheetId="14" r:id="rId14"/>
-    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
-    <sheet name="Loop" sheetId="16" r:id="rId16"/>
-    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
-    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
-    <sheet name="Mount Greenwood" sheetId="19" r:id="rId19"/>
-    <sheet name="Gage Park" sheetId="20" r:id="rId20"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="4" r:id="rId4"/>
+    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
+    <sheet name="Rogers Park" sheetId="6" r:id="rId6"/>
+    <sheet name="Douglas" sheetId="7" r:id="rId7"/>
+    <sheet name="Jefferson Park" sheetId="8" r:id="rId8"/>
+    <sheet name="West Town" sheetId="9" r:id="rId9"/>
+    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
+    <sheet name="Albany Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Grand Boulevard" sheetId="12" r:id="rId12"/>
+    <sheet name="Belmont Cragin" sheetId="13" r:id="rId13"/>
+    <sheet name="Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
+    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="South Shore" sheetId="17" r:id="rId17"/>
+    <sheet name="Mount Greenwood" sheetId="18" r:id="rId18"/>
+    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
+    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
     <sheet name="West Loop" sheetId="21" r:id="rId21"/>
     <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
     <sheet name="Humboldt Park" sheetId="23" r:id="rId23"/>
@@ -48,9 +48,9 @@
     <sheet name="Roseland" sheetId="39" r:id="rId39"/>
     <sheet name="Woodlawn" sheetId="40" r:id="rId40"/>
     <sheet name="Fuller Park" sheetId="41" r:id="rId41"/>
-    <sheet name="O'Hare" sheetId="42" r:id="rId42"/>
-    <sheet name="Little Italy, UIC" sheetId="43" r:id="rId43"/>
-    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Little Italy, UIC" sheetId="42" r:id="rId42"/>
+    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
+    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
     <sheet name="Bucktown" sheetId="45" r:id="rId45"/>
     <sheet name="Calumet Heights" sheetId="46" r:id="rId46"/>
     <sheet name="Edgewater" sheetId="47" r:id="rId47"/>
@@ -1242,322 +1242,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>18</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>32</v>
-      </c>
-      <c r="E8">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>25</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>70</v>
-      </c>
-      <c r="D9">
-        <v>59</v>
-      </c>
-      <c r="E9">
-        <v>63</v>
-      </c>
-      <c r="F9">
-        <v>66</v>
-      </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <v>58</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>73</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1843,7 +1527,1310 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>14</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
+        <v>9</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>13</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>24</v>
+      </c>
+      <c r="J3">
+        <v>24</v>
+      </c>
+      <c r="K3">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>42</v>
+      </c>
+      <c r="H8">
+        <v>41</v>
+      </c>
+      <c r="I8">
+        <v>63</v>
+      </c>
+      <c r="J8">
+        <v>44</v>
+      </c>
+      <c r="K8">
+        <v>38</v>
+      </c>
+      <c r="L8">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>120</v>
+      </c>
+      <c r="C9">
+        <v>208</v>
+      </c>
+      <c r="D9">
+        <v>364</v>
+      </c>
+      <c r="E9">
+        <v>445</v>
+      </c>
+      <c r="F9">
+        <v>419</v>
+      </c>
+      <c r="G9">
+        <v>139</v>
+      </c>
+      <c r="H9">
+        <v>68</v>
+      </c>
+      <c r="I9">
+        <v>146</v>
+      </c>
+      <c r="J9">
+        <v>85</v>
+      </c>
+      <c r="K9">
+        <v>77</v>
+      </c>
+      <c r="L9">
+        <v>59</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>156</v>
+      </c>
+      <c r="C10">
+        <v>249</v>
+      </c>
+      <c r="D10">
+        <v>422</v>
+      </c>
+      <c r="E10">
+        <v>501</v>
+      </c>
+      <c r="F10">
+        <v>474</v>
+      </c>
+      <c r="G10">
+        <v>201</v>
+      </c>
+      <c r="H10">
+        <v>127</v>
+      </c>
+      <c r="I10">
+        <v>246</v>
+      </c>
+      <c r="J10">
+        <v>173</v>
+      </c>
+      <c r="K10">
+        <v>152</v>
+      </c>
+      <c r="L10">
+        <v>131</v>
+      </c>
+      <c r="M10">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>54</v>
+      </c>
+      <c r="D8">
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>49</v>
+      </c>
+      <c r="F8">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>47</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>39</v>
+      </c>
+      <c r="J8">
+        <v>29</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>29</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2153,243 +3140,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>9</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -2452,23 +3205,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -2484,20 +3237,32 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -2505,130 +3270,122 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
         <v>6</v>
       </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
       <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
         <v>11</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>14</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2636,184 +3393,52 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2821,349 +3446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
-      </c>
-      <c r="L2">
-        <v>13</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>41</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
-      </c>
-      <c r="H8">
-        <v>41</v>
-      </c>
-      <c r="I8">
-        <v>63</v>
-      </c>
-      <c r="J8">
-        <v>44</v>
-      </c>
-      <c r="K8">
-        <v>38</v>
-      </c>
-      <c r="L8">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>120</v>
-      </c>
-      <c r="C9">
-        <v>208</v>
-      </c>
-      <c r="D9">
-        <v>364</v>
-      </c>
-      <c r="E9">
-        <v>445</v>
-      </c>
-      <c r="F9">
-        <v>419</v>
-      </c>
-      <c r="G9">
-        <v>139</v>
-      </c>
-      <c r="H9">
-        <v>68</v>
-      </c>
-      <c r="I9">
-        <v>146</v>
-      </c>
-      <c r="J9">
-        <v>85</v>
-      </c>
-      <c r="K9">
-        <v>77</v>
-      </c>
-      <c r="L9">
-        <v>59</v>
-      </c>
-      <c r="M9">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>156</v>
-      </c>
-      <c r="C10">
-        <v>249</v>
-      </c>
-      <c r="D10">
-        <v>422</v>
-      </c>
-      <c r="E10">
-        <v>501</v>
-      </c>
-      <c r="F10">
-        <v>474</v>
-      </c>
-      <c r="G10">
-        <v>201</v>
-      </c>
-      <c r="H10">
-        <v>127</v>
-      </c>
-      <c r="I10">
-        <v>246</v>
-      </c>
-      <c r="J10">
-        <v>173</v>
-      </c>
-      <c r="K10">
-        <v>152</v>
-      </c>
-      <c r="L10">
-        <v>131</v>
-      </c>
-      <c r="M10">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3229,33 +3512,18 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
         <v>4</v>
       </c>
     </row>
@@ -3264,109 +3532,82 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
       <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3374,40 +3615,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3415,346 +3656,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
         <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7531,7 +7466,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7594,20 +7529,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7615,164 +7571,208 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
         <v>11</v>
       </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
         <v>18</v>
       </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
       <c r="K7">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
+      <c r="K8">
+        <v>25</v>
+      </c>
+      <c r="L8">
         <v>22</v>
       </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
       <c r="M8">
-        <v>7</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>70</v>
+      </c>
+      <c r="D9">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>63</v>
+      </c>
+      <c r="F9">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>58</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>73</v>
+      </c>
+      <c r="L9">
+        <v>66</v>
+      </c>
+      <c r="M9">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -10015,7 +10015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10078,29 +10078,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -10110,157 +10113,206 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>61</v>
-      </c>
-      <c r="F6">
-        <v>43</v>
-      </c>
       <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>62</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>66</v>
-      </c>
-      <c r="F7">
-        <v>49</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>19</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>16</v>
+      <c r="B9">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>76</v>
+      </c>
+      <c r="E9">
+        <v>68</v>
+      </c>
+      <c r="F9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>56</v>
+      </c>
+      <c r="I9">
+        <v>63</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>73</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -12754,7 +12806,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12817,35 +12869,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12855,38 +12898,26 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12896,162 +12927,131 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="I4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
         <v>26</v>
-      </c>
-      <c r="C7">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
         <v>16</v>
       </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B8">
-        <v>42</v>
-      </c>
-      <c r="C8">
-        <v>62</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>70</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>76</v>
-      </c>
-      <c r="E9">
-        <v>68</v>
-      </c>
-      <c r="F9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>61</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
-      </c>
-      <c r="I9">
-        <v>63</v>
-      </c>
-      <c r="J9">
-        <v>41</v>
-      </c>
-      <c r="K9">
-        <v>64</v>
-      </c>
-      <c r="L9">
-        <v>73</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13590,230 +13590,6 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>31</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14085,7 +13861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14298,6 +14074,230 @@
       </c>
       <c r="M6">
         <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -15425,66 +15425,57 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="D3">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
+      <c r="K4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15492,40 +15483,34 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15533,40 +15518,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15574,40 +15559,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>26</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
       <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
         <v>11</v>
       </c>
-      <c r="I7">
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
         <v>15</v>
       </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -17749,7 +17734,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17812,174 +17797,221 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <v>9</v>
       </c>
-      <c r="B6">
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="F6">
+      <c r="I6">
         <v>11</v>
       </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>59</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>15</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
+      <c r="B8">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>73</v>
+      </c>
+      <c r="F8">
+        <v>44</v>
+      </c>
+      <c r="G8">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>31</v>
+      </c>
+      <c r="I8">
+        <v>35</v>
+      </c>
+      <c r="J8">
+        <v>32</v>
+      </c>
+      <c r="K8">
+        <v>39</v>
+      </c>
+      <c r="L8">
+        <v>38</v>
+      </c>
+      <c r="M8">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -19799,27 +19831,15 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -19827,35 +19847,20 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -19865,27 +19870,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="J4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -19894,39 +19887,33 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -19935,40 +19922,37 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>22</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -19976,40 +19960,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -21800,20 +21784,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>2</v>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21821,37 +21805,37 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -21860,34 +21844,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21895,22 +21885,25 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -21919,13 +21912,13 @@
         <v>4</v>
       </c>
       <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
         <v>8</v>
       </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -21933,40 +21926,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
         <v>15</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>13</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
         <v>11</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -23544,7 +23537,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23607,40 +23600,55 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -23648,141 +23656,133 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>61</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>66</v>
+      </c>
+      <c r="F7">
+        <v>49</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
         <v>19</v>
       </c>
-      <c r="C7">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
       <c r="L7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="M7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>14</v>
-      </c>
-      <c r="D8">
-        <v>11</v>
-      </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>22</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,24 +9,24 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="4" r:id="rId4"/>
-    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
-    <sheet name="Rogers Park" sheetId="6" r:id="rId6"/>
-    <sheet name="Douglas" sheetId="7" r:id="rId7"/>
-    <sheet name="Jefferson Park" sheetId="8" r:id="rId8"/>
-    <sheet name="West Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
-    <sheet name="Albany Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Grand Boulevard" sheetId="12" r:id="rId12"/>
-    <sheet name="Belmont Cragin" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
-    <sheet name="Austin" sheetId="16" r:id="rId16"/>
-    <sheet name="South Shore" sheetId="17" r:id="rId17"/>
-    <sheet name="Mount Greenwood" sheetId="18" r:id="rId18"/>
-    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
-    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
+    <sheet name="West Town" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="5" r:id="rId5"/>
+    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
+    <sheet name="Rogers Park" sheetId="7" r:id="rId7"/>
+    <sheet name="Douglas" sheetId="8" r:id="rId8"/>
+    <sheet name="Jefferson Park" sheetId="9" r:id="rId9"/>
+    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="Austin" sheetId="12" r:id="rId12"/>
+    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="14" r:id="rId14"/>
+    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
+    <sheet name="Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
+    <sheet name="Mount Greenwood" sheetId="19" r:id="rId19"/>
+    <sheet name="Gage Park" sheetId="20" r:id="rId20"/>
     <sheet name="West Loop" sheetId="21" r:id="rId21"/>
     <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
     <sheet name="Humboldt Park" sheetId="23" r:id="rId23"/>
@@ -48,9 +48,9 @@
     <sheet name="Roseland" sheetId="39" r:id="rId39"/>
     <sheet name="Woodlawn" sheetId="40" r:id="rId40"/>
     <sheet name="Fuller Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Little Italy, UIC" sheetId="42" r:id="rId42"/>
-    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
-    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
+    <sheet name="O'Hare" sheetId="42" r:id="rId42"/>
+    <sheet name="Little Italy, UIC" sheetId="43" r:id="rId43"/>
+    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
     <sheet name="Bucktown" sheetId="45" r:id="rId45"/>
     <sheet name="Calumet Heights" sheetId="46" r:id="rId46"/>
     <sheet name="Edgewater" sheetId="47" r:id="rId47"/>
@@ -1242,6 +1242,322 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>25</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>70</v>
+      </c>
+      <c r="D9">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>63</v>
+      </c>
+      <c r="F9">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>58</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>73</v>
+      </c>
+      <c r="L9">
+        <v>66</v>
+      </c>
+      <c r="M9">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1527,7 +1843,317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>28</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>58</v>
+      </c>
+      <c r="G8">
+        <v>51</v>
+      </c>
+      <c r="H8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>53</v>
+      </c>
+      <c r="C9">
+        <v>75</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>93</v>
+      </c>
+      <c r="G9">
+        <v>74</v>
+      </c>
+      <c r="H9">
+        <v>58</v>
+      </c>
+      <c r="I9">
+        <v>51</v>
+      </c>
+      <c r="J9">
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>49</v>
+      </c>
+      <c r="L9">
+        <v>38</v>
+      </c>
+      <c r="M9">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1761,7 +2387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2010,7 +2636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2195,7 +2821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2537,7 +3163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2830,317 +3456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>28</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>31</v>
-      </c>
-      <c r="C8">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>51</v>
-      </c>
-      <c r="H8">
-        <v>23</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>17</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>53</v>
-      </c>
-      <c r="C9">
-        <v>75</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>93</v>
-      </c>
-      <c r="G9">
-        <v>74</v>
-      </c>
-      <c r="H9">
-        <v>58</v>
-      </c>
-      <c r="I9">
-        <v>51</v>
-      </c>
-      <c r="J9">
-        <v>45</v>
-      </c>
-      <c r="K9">
-        <v>49</v>
-      </c>
-      <c r="L9">
-        <v>38</v>
-      </c>
-      <c r="M9">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3393,7 +3709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3439,257 +3755,6 @@
       </c>
       <c r="C4">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7466,7 +7531,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7529,41 +7594,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7571,208 +7615,164 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>70</v>
-      </c>
-      <c r="D9">
-        <v>59</v>
-      </c>
-      <c r="E9">
-        <v>63</v>
-      </c>
-      <c r="F9">
-        <v>66</v>
-      </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <v>58</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>73</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -10015,7 +10015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10078,32 +10078,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -10113,206 +10110,157 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>6</v>
       </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>7</v>
       </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>61</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
       <c r="G6">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>66</v>
+      </c>
+      <c r="F7">
+        <v>49</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
+      <c r="K7">
+        <v>19</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7">
         <v>16</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>23</v>
-      </c>
-      <c r="H7">
-        <v>22</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>42</v>
-      </c>
-      <c r="C8">
-        <v>62</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>70</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>76</v>
-      </c>
-      <c r="E9">
-        <v>68</v>
-      </c>
-      <c r="F9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>61</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
-      </c>
-      <c r="I9">
-        <v>63</v>
-      </c>
-      <c r="J9">
-        <v>41</v>
-      </c>
-      <c r="K9">
-        <v>64</v>
-      </c>
-      <c r="L9">
-        <v>73</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -12806,7 +12754,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12869,26 +12817,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12898,26 +12855,38 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12927,131 +12896,162 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>15</v>
       </c>
-      <c r="J7">
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K7">
+      <c r="B8">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>62</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
         <v>8</v>
       </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>76</v>
+      </c>
+      <c r="E9">
+        <v>68</v>
+      </c>
+      <c r="F9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>56</v>
+      </c>
+      <c r="I9">
+        <v>63</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>73</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13590,6 +13590,230 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13861,7 +14085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14074,230 +14298,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>31</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -15425,57 +15425,66 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>1</v>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15483,34 +15492,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
       </c>
       <c r="L5">
         <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15518,40 +15533,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15559,40 +15574,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
         <v>9</v>
       </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
+      <c r="K7">
         <v>8</v>
       </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
       <c r="L7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -17734,7 +17749,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17797,221 +17812,174 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
       <c r="L3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
       <c r="J6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>31</v>
-      </c>
       <c r="C7">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B8">
-        <v>33</v>
-      </c>
-      <c r="C8">
-        <v>52</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>73</v>
-      </c>
-      <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>32</v>
-      </c>
-      <c r="H8">
-        <v>31</v>
-      </c>
-      <c r="I8">
-        <v>35</v>
-      </c>
-      <c r="J8">
-        <v>32</v>
-      </c>
-      <c r="K8">
-        <v>39</v>
-      </c>
-      <c r="L8">
-        <v>38</v>
-      </c>
-      <c r="M8">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -19831,15 +19799,27 @@
         <v>2</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -19847,20 +19827,35 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -19870,15 +19865,27 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -19887,33 +19894,39 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -19922,37 +19935,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -19960,40 +19976,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L8">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -21784,20 +21800,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="K2">
-        <v>1</v>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21805,37 +21821,37 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -21844,40 +21860,34 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21885,25 +21895,22 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -21912,13 +21919,13 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -21926,40 +21933,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
       <c r="G8">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
         <v>12</v>
       </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
       <c r="M8">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -23537,7 +23544,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23600,55 +23607,40 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -23656,133 +23648,141 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
         <v>22</v>
       </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>66</v>
-      </c>
-      <c r="F7">
-        <v>49</v>
-      </c>
-      <c r="G7">
+      <c r="H8">
         <v>12</v>
       </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
         <v>15</v>
       </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>19</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>16</v>
+      <c r="M8">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,24 +9,24 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="4" r:id="rId4"/>
-    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
-    <sheet name="Rogers Park" sheetId="6" r:id="rId6"/>
-    <sheet name="Douglas" sheetId="7" r:id="rId7"/>
-    <sheet name="Jefferson Park" sheetId="8" r:id="rId8"/>
-    <sheet name="West Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
-    <sheet name="Albany Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Grand Boulevard" sheetId="12" r:id="rId12"/>
-    <sheet name="Belmont Cragin" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
-    <sheet name="Austin" sheetId="16" r:id="rId16"/>
-    <sheet name="South Shore" sheetId="17" r:id="rId17"/>
-    <sheet name="Mount Greenwood" sheetId="18" r:id="rId18"/>
-    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
-    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
+    <sheet name="West Town" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="5" r:id="rId5"/>
+    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
+    <sheet name="Rogers Park" sheetId="7" r:id="rId7"/>
+    <sheet name="Douglas" sheetId="8" r:id="rId8"/>
+    <sheet name="Jefferson Park" sheetId="9" r:id="rId9"/>
+    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="Austin" sheetId="12" r:id="rId12"/>
+    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="14" r:id="rId14"/>
+    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
+    <sheet name="Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
+    <sheet name="Mount Greenwood" sheetId="19" r:id="rId19"/>
+    <sheet name="Gage Park" sheetId="20" r:id="rId20"/>
     <sheet name="West Loop" sheetId="21" r:id="rId21"/>
     <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
     <sheet name="Humboldt Park" sheetId="23" r:id="rId23"/>
@@ -48,9 +48,9 @@
     <sheet name="Roseland" sheetId="39" r:id="rId39"/>
     <sheet name="Woodlawn" sheetId="40" r:id="rId40"/>
     <sheet name="Fuller Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Little Italy, UIC" sheetId="42" r:id="rId42"/>
-    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
-    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
+    <sheet name="O'Hare" sheetId="42" r:id="rId42"/>
+    <sheet name="Little Italy, UIC" sheetId="43" r:id="rId43"/>
+    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
     <sheet name="Bucktown" sheetId="45" r:id="rId45"/>
     <sheet name="Calumet Heights" sheetId="46" r:id="rId46"/>
     <sheet name="Edgewater" sheetId="47" r:id="rId47"/>
@@ -881,7 +881,7 @@
         <v>65</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>63</v>
@@ -899,13 +899,13 @@
         <v>84</v>
       </c>
       <c r="K2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L2">
         <v>102</v>
       </c>
       <c r="M2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -916,7 +916,7 @@
         <v>60</v>
       </c>
       <c r="C3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3">
         <v>96</v>
@@ -928,22 +928,22 @@
         <v>93</v>
       </c>
       <c r="G3">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H3">
         <v>95</v>
       </c>
       <c r="I3">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J3">
         <v>148</v>
       </c>
       <c r="K3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L3">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M3">
         <v>147</v>
@@ -1117,40 +1117,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C9">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D9">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E9">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F9">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G9">
         <v>350</v>
       </c>
       <c r="H9">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I9">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J9">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K9">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L9">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="M9">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1158,37 +1158,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C10">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="D10">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="E10">
-        <v>1538</v>
+        <v>1544</v>
       </c>
       <c r="F10">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="G10">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H10">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="I10">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J10">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K10">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L10">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M10">
         <v>356</v>
@@ -1199,40 +1199,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C11">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="D11">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="E11">
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="F11">
-        <v>2124</v>
+        <v>2136</v>
       </c>
       <c r="G11">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="H11">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="I11">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="J11">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="K11">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="L11">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="M11">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -1241,6 +1241,322 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>26</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>70</v>
+      </c>
+      <c r="D9">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>64</v>
+      </c>
+      <c r="F9">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>58</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>74</v>
+      </c>
+      <c r="L9">
+        <v>66</v>
+      </c>
+      <c r="M9">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1475,7 +1791,7 @@
         <v>15</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1516,7 +1832,7 @@
         <v>39</v>
       </c>
       <c r="L8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M8">
         <v>17</v>
@@ -1527,7 +1843,317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>28</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>58</v>
+      </c>
+      <c r="G8">
+        <v>51</v>
+      </c>
+      <c r="H8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>53</v>
+      </c>
+      <c r="C9">
+        <v>75</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>93</v>
+      </c>
+      <c r="G9">
+        <v>74</v>
+      </c>
+      <c r="H9">
+        <v>58</v>
+      </c>
+      <c r="I9">
+        <v>51</v>
+      </c>
+      <c r="J9">
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>49</v>
+      </c>
+      <c r="L9">
+        <v>38</v>
+      </c>
+      <c r="M9">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1761,7 +2387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2010,7 +2636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2074,6 +2700,9 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
@@ -2187,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2195,7 +2824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2323,7 +2952,7 @@
         <v>10</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3">
         <v>24</v>
@@ -2423,7 +3052,7 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8">
         <v>41</v>
@@ -2435,7 +3064,7 @@
         <v>41</v>
       </c>
       <c r="I8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8">
         <v>44</v>
@@ -2444,7 +3073,7 @@
         <v>38</v>
       </c>
       <c r="L8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M8">
         <v>20</v>
@@ -2458,16 +3087,16 @@
         <v>120</v>
       </c>
       <c r="C9">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E9">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F9">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G9">
         <v>139</v>
@@ -2482,7 +3111,7 @@
         <v>85</v>
       </c>
       <c r="K9">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L9">
         <v>59</v>
@@ -2499,16 +3128,16 @@
         <v>156</v>
       </c>
       <c r="C10">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D10">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E10">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F10">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G10">
         <v>201</v>
@@ -2517,16 +3146,16 @@
         <v>127</v>
       </c>
       <c r="I10">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J10">
         <v>173</v>
       </c>
       <c r="K10">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L10">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M10">
         <v>89</v>
@@ -2537,7 +3166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2830,317 +3459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>28</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>31</v>
-      </c>
-      <c r="C8">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>51</v>
-      </c>
-      <c r="H8">
-        <v>23</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>17</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>53</v>
-      </c>
-      <c r="C9">
-        <v>75</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>93</v>
-      </c>
-      <c r="G9">
-        <v>74</v>
-      </c>
-      <c r="H9">
-        <v>58</v>
-      </c>
-      <c r="I9">
-        <v>51</v>
-      </c>
-      <c r="J9">
-        <v>45</v>
-      </c>
-      <c r="K9">
-        <v>49</v>
-      </c>
-      <c r="L9">
-        <v>38</v>
-      </c>
-      <c r="M9">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3393,7 +3712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3439,257 +3758,6 @@
       </c>
       <c r="C4">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3868,7 +3936,7 @@
         <v>14</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
         <v>13</v>
@@ -3880,7 +3948,7 @@
         <v>23</v>
       </c>
       <c r="J5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5">
         <v>18</v>
@@ -3927,7 +3995,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -4067,7 +4135,7 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F10">
         <v>14</v>
@@ -4129,7 +4197,7 @@
         <v>2</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4267,6 +4335,9 @@
       <c r="C16">
         <v>4</v>
       </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
       <c r="E16">
         <v>5</v>
       </c>
@@ -4388,7 +4459,7 @@
         <v>39</v>
       </c>
       <c r="L19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M19">
         <v>17</v>
@@ -4458,7 +4529,7 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21">
         <v>23</v>
@@ -4467,7 +4538,7 @@
         <v>13</v>
       </c>
       <c r="K21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L21">
         <v>22</v>
@@ -4543,7 +4614,7 @@
         <v>4</v>
       </c>
       <c r="I23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -4656,7 +4727,7 @@
         <v>20</v>
       </c>
       <c r="G27">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27">
         <v>14</v>
@@ -4685,7 +4756,7 @@
         <v>70</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D28">
         <v>76</v>
@@ -4706,7 +4777,7 @@
         <v>63</v>
       </c>
       <c r="J28">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K28">
         <v>64</v>
@@ -4735,7 +4806,7 @@
         <v>16</v>
       </c>
       <c r="F29">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G29">
         <v>11</v>
@@ -4753,7 +4824,7 @@
         <v>20</v>
       </c>
       <c r="L29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M29">
         <v>11</v>
@@ -4843,7 +4914,7 @@
         <v>94</v>
       </c>
       <c r="F32">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G32">
         <v>88</v>
@@ -4861,7 +4932,7 @@
         <v>58</v>
       </c>
       <c r="L32">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M32">
         <v>46</v>
@@ -4974,7 +5045,7 @@
         <v>59</v>
       </c>
       <c r="E36">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F36">
         <v>66</v>
@@ -4983,7 +5054,7 @@
         <v>34</v>
       </c>
       <c r="H36">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I36">
         <v>58</v>
@@ -4992,7 +5063,7 @@
         <v>40</v>
       </c>
       <c r="K36">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L36">
         <v>66</v>
@@ -5137,7 +5208,7 @@
         <v>19</v>
       </c>
       <c r="D41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E41">
         <v>17</v>
@@ -5225,7 +5296,7 @@
         <v>12</v>
       </c>
       <c r="F43">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G43">
         <v>13</v>
@@ -5234,7 +5305,7 @@
         <v>4</v>
       </c>
       <c r="I43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J43">
         <v>5</v>
@@ -5301,7 +5372,7 @@
         <v>15</v>
       </c>
       <c r="G45">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45">
         <v>12</v>
@@ -5453,7 +5524,7 @@
         <v>4</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49">
         <v>7</v>
@@ -5500,7 +5571,7 @@
         <v>23</v>
       </c>
       <c r="E50">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F50">
         <v>50</v>
@@ -5515,7 +5586,7 @@
         <v>15</v>
       </c>
       <c r="J50">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K50">
         <v>30</v>
@@ -5617,16 +5688,16 @@
         <v>156</v>
       </c>
       <c r="C53">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D53">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E53">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F53">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G53">
         <v>201</v>
@@ -5635,16 +5706,16 @@
         <v>127</v>
       </c>
       <c r="I53">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J53">
         <v>173</v>
       </c>
       <c r="K53">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L53">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M53">
         <v>89</v>
@@ -5988,10 +6059,10 @@
         <v>6</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6052,7 +6123,7 @@
         <v>52</v>
       </c>
       <c r="G65">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H65">
         <v>15</v>
@@ -6239,19 +6310,19 @@
         <v>47</v>
       </c>
       <c r="F70">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G70">
         <v>32</v>
       </c>
       <c r="H70">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I70">
         <v>24</v>
       </c>
       <c r="J70">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70">
         <v>21</v>
@@ -6318,7 +6389,7 @@
         <v>11</v>
       </c>
       <c r="F72">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G72">
         <v>6</v>
@@ -6382,7 +6453,7 @@
         <v>61</v>
       </c>
       <c r="F74">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G74">
         <v>28</v>
@@ -6411,7 +6482,7 @@
         <v>85</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6446,7 +6517,7 @@
         <v>86</v>
       </c>
       <c r="B76">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C76">
         <v>52</v>
@@ -6455,10 +6526,10 @@
         <v>42</v>
       </c>
       <c r="E76">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F76">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G76">
         <v>32</v>
@@ -6476,7 +6547,7 @@
         <v>39</v>
       </c>
       <c r="L76">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M76">
         <v>24</v>
@@ -6499,7 +6570,7 @@
         <v>52</v>
       </c>
       <c r="F77">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G77">
         <v>37</v>
@@ -6546,7 +6617,7 @@
         <v>22</v>
       </c>
       <c r="H78">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I78">
         <v>18</v>
@@ -6648,7 +6719,7 @@
         <v>7</v>
       </c>
       <c r="K81">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L81">
         <v>15</v>
@@ -6744,7 +6815,7 @@
         <v>7</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -6852,7 +6923,7 @@
         <v>25</v>
       </c>
       <c r="C87">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D87">
         <v>15</v>
@@ -6923,7 +6994,7 @@
         <v>2</v>
       </c>
       <c r="M88">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7019,7 +7090,7 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E91">
         <v>3</v>
@@ -7066,13 +7137,13 @@
         <v>19</v>
       </c>
       <c r="K92">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L92">
         <v>17</v>
       </c>
       <c r="M92">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7186,7 +7257,7 @@
         <v>8</v>
       </c>
       <c r="K95">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L95">
         <v>20</v>
@@ -7212,7 +7283,7 @@
         <v>26</v>
       </c>
       <c r="F96">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G96">
         <v>7</v>
@@ -7274,7 +7345,7 @@
         <v>4</v>
       </c>
       <c r="M97">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7323,40 +7394,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C99">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="D99">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="E99">
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="F99">
-        <v>2124</v>
+        <v>2136</v>
       </c>
       <c r="G99">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="H99">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="I99">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="J99">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="K99">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="L99">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="M99">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -7466,7 +7537,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7529,41 +7600,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7571,208 +7621,164 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>70</v>
-      </c>
-      <c r="D9">
-        <v>59</v>
-      </c>
-      <c r="E9">
-        <v>63</v>
-      </c>
-      <c r="F9">
-        <v>66</v>
-      </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <v>58</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>73</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7896,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -7967,7 +7973,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -8043,13 +8049,13 @@
         <v>19</v>
       </c>
       <c r="K9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L9">
         <v>17</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8176,7 +8182,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -8318,7 +8324,7 @@
         <v>52</v>
       </c>
       <c r="G8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8">
         <v>15</v>
@@ -8526,7 +8532,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>13</v>
@@ -8567,7 +8573,7 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>17</v>
@@ -8795,7 +8801,7 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7">
         <v>35</v>
@@ -8813,7 +8819,7 @@
         <v>19</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -8877,7 +8883,7 @@
         <v>94</v>
       </c>
       <c r="F9">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G9">
         <v>88</v>
@@ -8895,7 +8901,7 @@
         <v>58</v>
       </c>
       <c r="L9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M9">
         <v>46</v>
@@ -9085,7 +9091,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -9126,7 +9132,7 @@
         <v>22</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7">
         <v>18</v>
@@ -9412,7 +9418,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9437,6 +9443,9 @@
       <c r="K4">
         <v>1</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -9511,10 +9520,10 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9897,7 +9906,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -10002,7 +10011,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -10015,7 +10024,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10078,32 +10087,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -10113,206 +10119,157 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>6</v>
       </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>7</v>
       </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>61</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
       <c r="G6">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>66</v>
+      </c>
+      <c r="F7">
+        <v>49</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7">
         <v>16</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>23</v>
-      </c>
-      <c r="H7">
-        <v>22</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>42</v>
-      </c>
-      <c r="C8">
-        <v>62</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>70</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>76</v>
-      </c>
-      <c r="E9">
-        <v>68</v>
-      </c>
-      <c r="F9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>61</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
-      </c>
-      <c r="I9">
-        <v>63</v>
-      </c>
-      <c r="J9">
-        <v>41</v>
-      </c>
-      <c r="K9">
-        <v>64</v>
-      </c>
-      <c r="L9">
-        <v>73</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -11637,7 +11594,7 @@
         <v>57</v>
       </c>
       <c r="F6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>16</v>
@@ -11678,7 +11635,7 @@
         <v>61</v>
       </c>
       <c r="F7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7">
         <v>28</v>
@@ -11807,6 +11764,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
@@ -11949,7 +11909,7 @@
         <v>25</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>15</v>
@@ -12152,7 +12112,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -12181,7 +12141,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -12222,7 +12182,7 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -12234,7 +12194,7 @@
         <v>23</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>18</v>
@@ -12332,7 +12292,7 @@
         <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -12481,7 +12441,7 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>15</v>
@@ -12693,7 +12653,7 @@
         <v>13</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <v>11</v>
@@ -12775,7 +12735,7 @@
         <v>52</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10">
         <v>37</v>
@@ -12806,7 +12766,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12869,26 +12829,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12898,26 +12867,38 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12927,131 +12908,162 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>15</v>
       </c>
-      <c r="J7">
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K7">
+      <c r="B8">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>63</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
         <v>8</v>
       </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>102</v>
+      </c>
+      <c r="D9">
+        <v>76</v>
+      </c>
+      <c r="E9">
+        <v>68</v>
+      </c>
+      <c r="F9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>56</v>
+      </c>
+      <c r="I9">
+        <v>63</v>
+      </c>
+      <c r="J9">
+        <v>42</v>
+      </c>
+      <c r="K9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>73</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13172,7 +13184,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13306,7 +13318,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -13495,7 +13507,7 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -13518,7 +13530,7 @@
         <v>11</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -13559,7 +13571,7 @@
         <v>16</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9">
         <v>11</v>
@@ -13577,7 +13589,7 @@
         <v>20</v>
       </c>
       <c r="L9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M9">
         <v>11</v>
@@ -13589,6 +13601,230 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13762,7 +13998,7 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>14</v>
@@ -13788,7 +14024,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6">
         <v>27</v>
@@ -13829,7 +14065,7 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>50</v>
@@ -13844,7 +14080,7 @@
         <v>15</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>30</v>
@@ -13861,7 +14097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14081,233 +14317,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>31</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -14321,9 +14333,10 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14334,70 +14347,73 @@
         <v>2016</v>
       </c>
       <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
         <v>2018</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="F2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -14408,31 +14424,34 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -14443,27 +14462,30 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
       <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
         <v>6</v>
       </c>
     </row>
@@ -14769,7 +14791,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -14902,7 +14924,7 @@
         <v>20</v>
       </c>
       <c r="G8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8">
         <v>14</v>
@@ -15425,57 +15447,66 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>1</v>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15483,34 +15514,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
       </c>
       <c r="L5">
         <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15518,40 +15555,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15559,40 +15596,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
         <v>9</v>
       </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
+      <c r="K7">
         <v>8</v>
       </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
       <c r="L7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -16536,7 +16573,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -16574,7 +16611,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -17175,7 +17212,7 @@
         <v>22</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -17216,7 +17253,7 @@
         <v>26</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -17420,7 +17457,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -17452,7 +17489,7 @@
         <v>3</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -17493,7 +17530,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9">
         <v>23</v>
@@ -17502,7 +17539,7 @@
         <v>13</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9">
         <v>22</v>
@@ -17614,7 +17651,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17724,7 +17761,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -17734,7 +17771,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17797,221 +17834,174 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
       <c r="L3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
       <c r="J6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>31</v>
-      </c>
       <c r="C7">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B8">
-        <v>33</v>
-      </c>
-      <c r="C8">
-        <v>52</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>73</v>
-      </c>
-      <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>32</v>
-      </c>
-      <c r="H8">
-        <v>31</v>
-      </c>
-      <c r="I8">
-        <v>35</v>
-      </c>
-      <c r="J8">
-        <v>32</v>
-      </c>
-      <c r="K8">
-        <v>39</v>
-      </c>
-      <c r="L8">
-        <v>38</v>
-      </c>
-      <c r="M8">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -18768,7 +18758,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -18806,7 +18796,7 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -19108,7 +19098,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -19148,7 +19138,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -19831,15 +19821,27 @@
         <v>2</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -19847,20 +19849,35 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -19870,15 +19887,27 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -19887,33 +19916,39 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -19922,37 +19957,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -19960,40 +19998,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L8">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -20186,19 +20224,19 @@
         <v>38</v>
       </c>
       <c r="F6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>20</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -20227,19 +20265,19 @@
         <v>47</v>
       </c>
       <c r="F7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7">
         <v>32</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7">
         <v>24</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7">
         <v>21</v>
@@ -21661,7 +21699,7 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -21690,7 +21728,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -21784,20 +21822,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="K2">
-        <v>1</v>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21805,37 +21843,37 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -21844,40 +21882,34 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21885,25 +21917,22 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -21912,13 +21941,13 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -21926,40 +21955,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
       <c r="G8">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
       <c r="J8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -22314,7 +22343,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -22323,7 +22352,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -22355,7 +22384,7 @@
         <v>12</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -22364,7 +22393,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -23237,7 +23266,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -23274,7 +23303,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -23537,7 +23566,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23600,55 +23629,40 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -23656,133 +23670,141 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>66</v>
-      </c>
-      <c r="F7">
-        <v>49</v>
-      </c>
-      <c r="G7">
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>23</v>
+      </c>
+      <c r="H8">
         <v>12</v>
       </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
         <v>15</v>
       </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>19</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>16</v>
+      <c r="M8">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,24 +9,24 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="West Town" sheetId="3" r:id="rId3"/>
-    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="5" r:id="rId5"/>
-    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
-    <sheet name="Rogers Park" sheetId="7" r:id="rId7"/>
-    <sheet name="Douglas" sheetId="8" r:id="rId8"/>
-    <sheet name="Jefferson Park" sheetId="9" r:id="rId9"/>
-    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
-    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
-    <sheet name="Austin" sheetId="12" r:id="rId12"/>
-    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
-    <sheet name="Grand Boulevard" sheetId="14" r:id="rId14"/>
-    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
-    <sheet name="Loop" sheetId="16" r:id="rId16"/>
-    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
-    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
-    <sheet name="Mount Greenwood" sheetId="19" r:id="rId19"/>
-    <sheet name="Gage Park" sheetId="20" r:id="rId20"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="4" r:id="rId4"/>
+    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
+    <sheet name="Rogers Park" sheetId="6" r:id="rId6"/>
+    <sheet name="Douglas" sheetId="7" r:id="rId7"/>
+    <sheet name="Jefferson Park" sheetId="8" r:id="rId8"/>
+    <sheet name="West Town" sheetId="9" r:id="rId9"/>
+    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
+    <sheet name="Albany Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Grand Boulevard" sheetId="12" r:id="rId12"/>
+    <sheet name="Belmont Cragin" sheetId="13" r:id="rId13"/>
+    <sheet name="Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
+    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="South Shore" sheetId="17" r:id="rId17"/>
+    <sheet name="Mount Greenwood" sheetId="18" r:id="rId18"/>
+    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
+    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
     <sheet name="West Loop" sheetId="21" r:id="rId21"/>
     <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
     <sheet name="Humboldt Park" sheetId="23" r:id="rId23"/>
@@ -48,9 +48,9 @@
     <sheet name="Roseland" sheetId="39" r:id="rId39"/>
     <sheet name="Woodlawn" sheetId="40" r:id="rId40"/>
     <sheet name="Fuller Park" sheetId="41" r:id="rId41"/>
-    <sheet name="O'Hare" sheetId="42" r:id="rId42"/>
-    <sheet name="Little Italy, UIC" sheetId="43" r:id="rId43"/>
-    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Little Italy, UIC" sheetId="42" r:id="rId42"/>
+    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
+    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
     <sheet name="Bucktown" sheetId="45" r:id="rId45"/>
     <sheet name="Calumet Heights" sheetId="46" r:id="rId46"/>
     <sheet name="Edgewater" sheetId="47" r:id="rId47"/>
@@ -1242,322 +1242,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <v>14</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>18</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>32</v>
-      </c>
-      <c r="E8">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>26</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>70</v>
-      </c>
-      <c r="D9">
-        <v>59</v>
-      </c>
-      <c r="E9">
-        <v>64</v>
-      </c>
-      <c r="F9">
-        <v>66</v>
-      </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>58</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>74</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1843,7 +1527,1313 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>14</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
+        <v>9</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>13</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>24</v>
+      </c>
+      <c r="K3">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>46</v>
+      </c>
+      <c r="F8">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>42</v>
+      </c>
+      <c r="H8">
+        <v>41</v>
+      </c>
+      <c r="I8">
+        <v>64</v>
+      </c>
+      <c r="J8">
+        <v>44</v>
+      </c>
+      <c r="K8">
+        <v>38</v>
+      </c>
+      <c r="L8">
+        <v>34</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>120</v>
+      </c>
+      <c r="C9">
+        <v>209</v>
+      </c>
+      <c r="D9">
+        <v>365</v>
+      </c>
+      <c r="E9">
+        <v>448</v>
+      </c>
+      <c r="F9">
+        <v>420</v>
+      </c>
+      <c r="G9">
+        <v>139</v>
+      </c>
+      <c r="H9">
+        <v>68</v>
+      </c>
+      <c r="I9">
+        <v>146</v>
+      </c>
+      <c r="J9">
+        <v>85</v>
+      </c>
+      <c r="K9">
+        <v>78</v>
+      </c>
+      <c r="L9">
+        <v>59</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>156</v>
+      </c>
+      <c r="C10">
+        <v>250</v>
+      </c>
+      <c r="D10">
+        <v>423</v>
+      </c>
+      <c r="E10">
+        <v>505</v>
+      </c>
+      <c r="F10">
+        <v>475</v>
+      </c>
+      <c r="G10">
+        <v>201</v>
+      </c>
+      <c r="H10">
+        <v>127</v>
+      </c>
+      <c r="I10">
+        <v>248</v>
+      </c>
+      <c r="J10">
+        <v>173</v>
+      </c>
+      <c r="K10">
+        <v>153</v>
+      </c>
+      <c r="L10">
+        <v>133</v>
+      </c>
+      <c r="M10">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>54</v>
+      </c>
+      <c r="D8">
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>49</v>
+      </c>
+      <c r="F8">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>47</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>39</v>
+      </c>
+      <c r="J8">
+        <v>29</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>29</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2153,243 +3143,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>9</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -2452,23 +3208,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -2484,20 +3240,32 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -2505,130 +3273,122 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
         <v>6</v>
       </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
       <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
         <v>11</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>14</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2636,187 +3396,52 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2824,349 +3449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
-      </c>
-      <c r="L2">
-        <v>13</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>46</v>
-      </c>
-      <c r="F8">
-        <v>41</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
-      </c>
-      <c r="H8">
-        <v>41</v>
-      </c>
-      <c r="I8">
-        <v>64</v>
-      </c>
-      <c r="J8">
-        <v>44</v>
-      </c>
-      <c r="K8">
-        <v>38</v>
-      </c>
-      <c r="L8">
-        <v>34</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>120</v>
-      </c>
-      <c r="C9">
-        <v>209</v>
-      </c>
-      <c r="D9">
-        <v>365</v>
-      </c>
-      <c r="E9">
-        <v>448</v>
-      </c>
-      <c r="F9">
-        <v>420</v>
-      </c>
-      <c r="G9">
-        <v>139</v>
-      </c>
-      <c r="H9">
-        <v>68</v>
-      </c>
-      <c r="I9">
-        <v>146</v>
-      </c>
-      <c r="J9">
-        <v>85</v>
-      </c>
-      <c r="K9">
-        <v>78</v>
-      </c>
-      <c r="L9">
-        <v>59</v>
-      </c>
-      <c r="M9">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>156</v>
-      </c>
-      <c r="C10">
-        <v>250</v>
-      </c>
-      <c r="D10">
-        <v>423</v>
-      </c>
-      <c r="E10">
-        <v>505</v>
-      </c>
-      <c r="F10">
-        <v>475</v>
-      </c>
-      <c r="G10">
-        <v>201</v>
-      </c>
-      <c r="H10">
-        <v>127</v>
-      </c>
-      <c r="I10">
-        <v>248</v>
-      </c>
-      <c r="J10">
-        <v>173</v>
-      </c>
-      <c r="K10">
-        <v>153</v>
-      </c>
-      <c r="L10">
-        <v>133</v>
-      </c>
-      <c r="M10">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3232,33 +3515,18 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
         <v>4</v>
       </c>
     </row>
@@ -3267,109 +3535,82 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
       <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3377,40 +3618,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3418,346 +3659,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
         <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7472,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7600,20 +7535,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7621,164 +7577,208 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
         <v>11</v>
       </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
+      <c r="H7">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
         <v>18</v>
       </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
       <c r="K7">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
+      <c r="K8">
+        <v>26</v>
+      </c>
+      <c r="L8">
         <v>22</v>
       </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
       <c r="M8">
-        <v>7</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>70</v>
+      </c>
+      <c r="D9">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>64</v>
+      </c>
+      <c r="F9">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>58</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>74</v>
+      </c>
+      <c r="L9">
+        <v>66</v>
+      </c>
+      <c r="M9">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -10024,7 +10024,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10087,29 +10087,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -10119,157 +10122,206 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>61</v>
-      </c>
-      <c r="F6">
-        <v>43</v>
-      </c>
       <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>63</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>66</v>
-      </c>
-      <c r="F7">
-        <v>49</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>20</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>16</v>
+      <c r="B9">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>102</v>
+      </c>
+      <c r="D9">
+        <v>76</v>
+      </c>
+      <c r="E9">
+        <v>68</v>
+      </c>
+      <c r="F9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>56</v>
+      </c>
+      <c r="I9">
+        <v>63</v>
+      </c>
+      <c r="J9">
+        <v>42</v>
+      </c>
+      <c r="K9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>73</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -12766,7 +12818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12829,35 +12881,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12867,38 +12910,26 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12908,162 +12939,131 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="I4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
         <v>26</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
         <v>16</v>
       </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B8">
-        <v>42</v>
-      </c>
-      <c r="C8">
-        <v>63</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>70</v>
-      </c>
-      <c r="C9">
-        <v>102</v>
-      </c>
-      <c r="D9">
-        <v>76</v>
-      </c>
-      <c r="E9">
-        <v>68</v>
-      </c>
-      <c r="F9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>61</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
-      </c>
-      <c r="I9">
-        <v>63</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>64</v>
-      </c>
-      <c r="L9">
-        <v>73</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13602,230 +13602,6 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>31</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14097,7 +13873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14310,6 +14086,230 @@
       </c>
       <c r="M6">
         <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -15447,66 +15447,57 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="D3">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
+      <c r="K4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15514,40 +15505,34 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15555,40 +15540,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15596,40 +15581,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>26</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
       <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
         <v>11</v>
       </c>
-      <c r="I7">
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
         <v>15</v>
       </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -17771,7 +17756,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17834,174 +17819,221 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
       <c r="D6">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
         <v>11</v>
       </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>59</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>15</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
+      <c r="B8">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>74</v>
+      </c>
+      <c r="F8">
+        <v>45</v>
+      </c>
+      <c r="G8">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>31</v>
+      </c>
+      <c r="I8">
+        <v>35</v>
+      </c>
+      <c r="J8">
+        <v>32</v>
+      </c>
+      <c r="K8">
+        <v>39</v>
+      </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -19821,27 +19853,15 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -19849,35 +19869,20 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -19887,27 +19892,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="J4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -19916,39 +19909,33 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -19957,40 +19944,37 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>22</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -19998,40 +19982,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -21822,20 +21806,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>2</v>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21843,37 +21827,37 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -21882,34 +21866,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21917,22 +21907,25 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -21941,13 +21934,13 @@
         <v>4</v>
       </c>
       <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
         <v>8</v>
       </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -21955,40 +21948,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
         <v>15</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>13</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
         <v>15</v>
       </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
       <c r="M8">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -23566,7 +23559,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23629,40 +23622,55 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -23670,141 +23678,133 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>61</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="M7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>14</v>
-      </c>
-      <c r="D8">
-        <v>11</v>
-      </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>23</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -70,13 +70,13 @@
     <sheet name="Brighton Park" sheetId="61" r:id="rId61"/>
     <sheet name="Lincoln Park" sheetId="62" r:id="rId62"/>
     <sheet name="Printers Row" sheetId="63" r:id="rId63"/>
-    <sheet name="West Pullman" sheetId="64" r:id="rId64"/>
-    <sheet name="West Lawn" sheetId="65" r:id="rId65"/>
-    <sheet name="Little Village" sheetId="66" r:id="rId66"/>
-    <sheet name="Ukrainian Village" sheetId="67" r:id="rId67"/>
-    <sheet name="Archer Heights" sheetId="68" r:id="rId68"/>
-    <sheet name="Montclare" sheetId="69" r:id="rId69"/>
-    <sheet name="Old Town" sheetId="70" r:id="rId70"/>
+    <sheet name="Old Town" sheetId="64" r:id="rId64"/>
+    <sheet name="West Pullman" sheetId="65" r:id="rId65"/>
+    <sheet name="West Lawn" sheetId="66" r:id="rId66"/>
+    <sheet name="Little Village" sheetId="67" r:id="rId67"/>
+    <sheet name="Ukrainian Village" sheetId="68" r:id="rId68"/>
+    <sheet name="Archer Heights" sheetId="69" r:id="rId69"/>
+    <sheet name="Montclare" sheetId="70" r:id="rId70"/>
     <sheet name="Grant Park" sheetId="71" r:id="rId71"/>
     <sheet name="Logan Square" sheetId="72" r:id="rId72"/>
     <sheet name="West Elsdon" sheetId="73" r:id="rId73"/>
@@ -890,7 +890,7 @@
         <v>65</v>
       </c>
       <c r="H2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>82</v>
@@ -899,7 +899,7 @@
         <v>84</v>
       </c>
       <c r="K2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L2">
         <v>102</v>
@@ -919,7 +919,7 @@
         <v>63</v>
       </c>
       <c r="D3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3">
         <v>99</v>
@@ -940,13 +940,13 @@
         <v>148</v>
       </c>
       <c r="K3">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L3">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M3">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1030,7 +1030,7 @@
         <v>16</v>
       </c>
       <c r="K6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6">
         <v>16</v>
@@ -1123,10 +1123,10 @@
         <v>343</v>
       </c>
       <c r="D9">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E9">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F9">
         <v>390</v>
@@ -1135,22 +1135,22 @@
         <v>350</v>
       </c>
       <c r="H9">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I9">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J9">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K9">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="L9">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M9">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1158,40 +1158,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C10">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="D10">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="E10">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="F10">
-        <v>1581</v>
+        <v>1587</v>
       </c>
       <c r="G10">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="H10">
         <v>387</v>
       </c>
       <c r="I10">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J10">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K10">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L10">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M10">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1199,40 +1199,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="C11">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="D11">
-        <v>1726</v>
+        <v>1731</v>
       </c>
       <c r="E11">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="F11">
-        <v>2136</v>
+        <v>2142</v>
       </c>
       <c r="G11">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="H11">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="I11">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="J11">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="K11">
-        <v>1155</v>
+        <v>1164</v>
       </c>
       <c r="L11">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="M11">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1437,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1448,7 +1448,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>23</v>
@@ -1489,7 +1489,7 @@
         <v>36</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>43</v>
@@ -1519,7 +1519,7 @@
         <v>30</v>
       </c>
       <c r="M8">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2426,7 +2426,7 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8">
         <v>41</v>
@@ -2435,10 +2435,10 @@
         <v>42</v>
       </c>
       <c r="H8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J8">
         <v>44</v>
@@ -2458,19 +2458,19 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C9">
         <v>209</v>
       </c>
       <c r="D9">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E9">
         <v>448</v>
       </c>
       <c r="F9">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G9">
         <v>139</v>
@@ -2485,13 +2485,13 @@
         <v>85</v>
       </c>
       <c r="K9">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L9">
         <v>59</v>
       </c>
       <c r="M9">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2499,40 +2499,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C10">
         <v>250</v>
       </c>
       <c r="D10">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E10">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F10">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G10">
         <v>201</v>
       </c>
       <c r="H10">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I10">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J10">
         <v>173</v>
       </c>
       <c r="K10">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L10">
         <v>133</v>
       </c>
       <c r="M10">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2973,7 +2973,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3047,7 +3047,7 @@
         <v>14</v>
       </c>
       <c r="K7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7">
         <v>11</v>
@@ -3064,7 +3064,7 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>20</v>
@@ -3073,7 +3073,7 @@
         <v>40</v>
       </c>
       <c r="F8">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>51</v>
@@ -3105,7 +3105,7 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D9">
         <v>42</v>
@@ -3114,7 +3114,7 @@
         <v>73</v>
       </c>
       <c r="F9">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G9">
         <v>74</v>
@@ -3129,13 +3129,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L9">
         <v>38</v>
       </c>
       <c r="M9">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3344,7 +3344,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -3385,7 +3385,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>11</v>
@@ -3877,7 +3877,7 @@
         <v>13</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5">
         <v>23</v>
@@ -3950,7 +3950,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -3985,7 +3985,7 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8">
         <v>42</v>
@@ -3994,7 +3994,7 @@
         <v>73</v>
       </c>
       <c r="F8">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G8">
         <v>74</v>
@@ -4009,13 +4009,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L8">
         <v>38</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4367,7 +4367,7 @@
         <v>36</v>
       </c>
       <c r="C19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19">
         <v>43</v>
@@ -4397,7 +4397,7 @@
         <v>30</v>
       </c>
       <c r="M19">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4514,7 +4514,7 @@
         <v>3</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -4688,13 +4688,13 @@
         <v>38</v>
       </c>
       <c r="B28">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D28">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E28">
         <v>68</v>
@@ -4709,7 +4709,7 @@
         <v>56</v>
       </c>
       <c r="I28">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J28">
         <v>42</v>
@@ -4718,7 +4718,7 @@
         <v>64</v>
       </c>
       <c r="L28">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M28">
         <v>34</v>
@@ -4843,13 +4843,13 @@
         <v>65</v>
       </c>
       <c r="D32">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E32">
         <v>94</v>
       </c>
       <c r="F32">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G32">
         <v>88</v>
@@ -4864,7 +4864,7 @@
         <v>53</v>
       </c>
       <c r="K32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L32">
         <v>48</v>
@@ -4974,7 +4974,7 @@
         <v>44</v>
       </c>
       <c r="C36">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D36">
         <v>59</v>
@@ -4989,7 +4989,7 @@
         <v>34</v>
       </c>
       <c r="H36">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I36">
         <v>58</v>
@@ -5208,7 +5208,7 @@
         <v>3</v>
       </c>
       <c r="L42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>3</v>
@@ -5246,7 +5246,7 @@
         <v>5</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L43">
         <v>12</v>
@@ -5322,7 +5322,7 @@
         <v>14</v>
       </c>
       <c r="L45">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M45">
         <v>11</v>
@@ -5506,7 +5506,7 @@
         <v>23</v>
       </c>
       <c r="E50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50">
         <v>50</v>
@@ -5524,10 +5524,10 @@
         <v>22</v>
       </c>
       <c r="K50">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L50">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M50">
         <v>18</v>
@@ -5620,40 +5620,40 @@
         <v>63</v>
       </c>
       <c r="B53">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C53">
         <v>250</v>
       </c>
       <c r="D53">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E53">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F53">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G53">
         <v>201</v>
       </c>
       <c r="H53">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I53">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J53">
         <v>173</v>
       </c>
       <c r="K53">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L53">
         <v>133</v>
       </c>
       <c r="M53">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5685,7 +5685,7 @@
         <v>8</v>
       </c>
       <c r="J54">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K54">
         <v>6</v>
@@ -5950,7 +5950,7 @@
         <v>11</v>
       </c>
       <c r="K62">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L62">
         <v>8</v>
@@ -5973,7 +5973,7 @@
         <v>5</v>
       </c>
       <c r="E63">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63">
         <v>9</v>
@@ -6061,7 +6061,7 @@
         <v>38</v>
       </c>
       <c r="H65">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I65">
         <v>28</v>
@@ -6236,19 +6236,19 @@
         <v>18</v>
       </c>
       <c r="C70">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D70">
         <v>36</v>
       </c>
       <c r="E70">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F70">
         <v>90</v>
       </c>
       <c r="G70">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H70">
         <v>18</v>
@@ -6260,13 +6260,13 @@
         <v>14</v>
       </c>
       <c r="K70">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L70">
         <v>11</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -6376,16 +6376,16 @@
         <v>84</v>
       </c>
       <c r="B74">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C74">
         <v>28</v>
       </c>
       <c r="D74">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E74">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F74">
         <v>74</v>
@@ -6511,13 +6511,13 @@
         <v>37</v>
       </c>
       <c r="H77">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I77">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J77">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K77">
         <v>47</v>
@@ -6537,7 +6537,7 @@
         <v>29</v>
       </c>
       <c r="C78">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D78">
         <v>46</v>
@@ -6561,7 +6561,7 @@
         <v>13</v>
       </c>
       <c r="K78">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L78">
         <v>12</v>
@@ -6589,7 +6589,7 @@
         <v>8</v>
       </c>
       <c r="C80">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D80">
         <v>22</v>
@@ -6616,7 +6616,7 @@
         <v>8</v>
       </c>
       <c r="L80">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M80">
         <v>9</v>
@@ -6736,7 +6736,7 @@
         <v>10</v>
       </c>
       <c r="L83">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M83">
         <v>11</v>
@@ -6864,7 +6864,7 @@
         <v>15</v>
       </c>
       <c r="E87">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F87">
         <v>21</v>
@@ -7025,7 +7025,7 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E91">
         <v>3</v>
@@ -7165,7 +7165,7 @@
         <v>105</v>
       </c>
       <c r="B95">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C95">
         <v>22</v>
@@ -7174,10 +7174,10 @@
         <v>40</v>
       </c>
       <c r="E95">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F95">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G95">
         <v>12</v>
@@ -7256,7 +7256,7 @@
         <v>16</v>
       </c>
       <c r="E97">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F97">
         <v>17</v>
@@ -7329,40 +7329,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="C99">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="D99">
-        <v>1726</v>
+        <v>1731</v>
       </c>
       <c r="E99">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="F99">
-        <v>2136</v>
+        <v>2142</v>
       </c>
       <c r="G99">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="H99">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="I99">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="J99">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="K99">
-        <v>1155</v>
+        <v>1164</v>
       </c>
       <c r="L99">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="M99">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -7681,7 +7681,7 @@
         <v>11</v>
       </c>
       <c r="H7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7">
         <v>13</v>
@@ -7707,7 +7707,7 @@
         <v>25</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -7748,7 +7748,7 @@
         <v>44</v>
       </c>
       <c r="C9">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>59</v>
@@ -7763,7 +7763,7 @@
         <v>34</v>
       </c>
       <c r="H9">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I9">
         <v>58</v>
@@ -8147,7 +8147,7 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -8327,7 +8327,7 @@
         <v>38</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8">
         <v>28</v>
@@ -8715,7 +8715,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -8816,7 +8816,7 @@
         <v>21</v>
       </c>
       <c r="K7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7">
         <v>24</v>
@@ -8842,7 +8842,7 @@
         <v>57</v>
       </c>
       <c r="F8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G8">
         <v>45</v>
@@ -8877,13 +8877,13 @@
         <v>65</v>
       </c>
       <c r="D9">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9">
         <v>94</v>
       </c>
       <c r="F9">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G9">
         <v>88</v>
@@ -8898,7 +8898,7 @@
         <v>53</v>
       </c>
       <c r="K9">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L9">
         <v>48</v>
@@ -9062,7 +9062,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <v>3</v>
@@ -9076,7 +9076,7 @@
         <v>25</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>42</v>
@@ -9117,7 +9117,7 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>46</v>
@@ -9141,7 +9141,7 @@
         <v>13</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>12</v>
@@ -9432,7 +9432,7 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -9499,7 +9499,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -10247,13 +10247,13 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>45</v>
@@ -10268,7 +10268,7 @@
         <v>19</v>
       </c>
       <c r="I8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J8">
         <v>20</v>
@@ -10277,7 +10277,7 @@
         <v>22</v>
       </c>
       <c r="L8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -10288,13 +10288,13 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9">
         <v>68</v>
@@ -10309,7 +10309,7 @@
         <v>56</v>
       </c>
       <c r="I9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J9">
         <v>42</v>
@@ -10318,7 +10318,7 @@
         <v>64</v>
       </c>
       <c r="L9">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M9">
         <v>34</v>
@@ -10500,7 +10500,7 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -10541,7 +10541,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -11634,16 +11634,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6">
         <v>23</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6">
         <v>64</v>
@@ -11675,16 +11675,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>28</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>74</v>
@@ -11926,7 +11926,7 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>14</v>
@@ -11967,7 +11967,7 @@
         <v>15</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>21</v>
@@ -12158,7 +12158,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -12240,7 +12240,7 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7">
         <v>23</v>
@@ -12711,13 +12711,13 @@
         <v>11</v>
       </c>
       <c r="H8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8">
         <v>21</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K8">
         <v>14</v>
@@ -12755,7 +12755,7 @@
         <v>19</v>
       </c>
       <c r="I9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9">
         <v>26</v>
@@ -12793,13 +12793,13 @@
         <v>37</v>
       </c>
       <c r="H10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J10">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K10">
         <v>47</v>
@@ -12978,7 +12978,7 @@
         <v>3</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -12992,7 +12992,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>19</v>
@@ -13033,7 +13033,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>22</v>
@@ -13060,7 +13060,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -13212,7 +13212,7 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -13294,7 +13294,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -13681,7 +13681,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -13800,7 +13800,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>27</v>
@@ -13821,7 +13821,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -13841,7 +13841,7 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>50</v>
@@ -13859,10 +13859,10 @@
         <v>22</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M7">
         <v>18</v>
@@ -13965,7 +13965,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -14082,7 +14082,7 @@
         <v>3</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -16148,7 +16148,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -16189,7 +16189,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -16955,7 +16955,7 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -17037,7 +17037,7 @@
         <v>11</v>
       </c>
       <c r="K8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -18859,6 +18859,261 @@
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>39</v>
+      </c>
+      <c r="F6">
+        <v>72</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>48</v>
+      </c>
+      <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>22</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -19068,7 +19323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19130,7 +19385,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -19170,7 +19425,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -19190,7 +19445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19403,7 +19658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19553,7 +19808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19683,100 +19938,6 @@
       </c>
       <c r="I7">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -20025,7 +20186,7 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -20034,16 +20195,9 @@
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20057,220 +20211,66 @@
         <v>2017</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>13</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>12</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>17</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>38</v>
-      </c>
-      <c r="F6">
-        <v>72</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>18</v>
-      </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>47</v>
-      </c>
-      <c r="F7">
-        <v>90</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>21</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -21896,7 +21896,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -21978,7 +21978,7 @@
         <v>14</v>
       </c>
       <c r="L8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M8">
         <v>11</v>
@@ -22266,6 +22266,9 @@
       <c r="I3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
       <c r="L3">
         <v>1</v>
       </c>
@@ -22392,7 +22395,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>12</v>
@@ -22778,6 +22781,9 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -22874,7 +22880,7 @@
         <v>3</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -23730,7 +23736,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>18</v>
@@ -23739,10 +23745,10 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -23771,7 +23777,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>22</v>
@@ -23780,10 +23786,10 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>12</v>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,24 +9,24 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="4" r:id="rId4"/>
-    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
-    <sheet name="Rogers Park" sheetId="6" r:id="rId6"/>
-    <sheet name="Douglas" sheetId="7" r:id="rId7"/>
-    <sheet name="Jefferson Park" sheetId="8" r:id="rId8"/>
-    <sheet name="West Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
-    <sheet name="Albany Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Grand Boulevard" sheetId="12" r:id="rId12"/>
-    <sheet name="Belmont Cragin" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
-    <sheet name="Austin" sheetId="16" r:id="rId16"/>
-    <sheet name="South Shore" sheetId="17" r:id="rId17"/>
-    <sheet name="Mount Greenwood" sheetId="18" r:id="rId18"/>
-    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
-    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
+    <sheet name="West Town" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="5" r:id="rId5"/>
+    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
+    <sheet name="Rogers Park" sheetId="7" r:id="rId7"/>
+    <sheet name="Douglas" sheetId="8" r:id="rId8"/>
+    <sheet name="Jefferson Park" sheetId="9" r:id="rId9"/>
+    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="Austin" sheetId="12" r:id="rId12"/>
+    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Boulevard" sheetId="14" r:id="rId14"/>
+    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
+    <sheet name="Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
+    <sheet name="Mount Greenwood" sheetId="19" r:id="rId19"/>
+    <sheet name="Gage Park" sheetId="20" r:id="rId20"/>
     <sheet name="West Loop" sheetId="21" r:id="rId21"/>
     <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
     <sheet name="Humboldt Park" sheetId="23" r:id="rId23"/>
@@ -48,9 +48,9 @@
     <sheet name="Roseland" sheetId="39" r:id="rId39"/>
     <sheet name="Woodlawn" sheetId="40" r:id="rId40"/>
     <sheet name="Fuller Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Little Italy, UIC" sheetId="42" r:id="rId42"/>
-    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
-    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
+    <sheet name="O'Hare" sheetId="42" r:id="rId42"/>
+    <sheet name="Little Italy, UIC" sheetId="43" r:id="rId43"/>
+    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
     <sheet name="Bucktown" sheetId="45" r:id="rId45"/>
     <sheet name="Calumet Heights" sheetId="46" r:id="rId46"/>
     <sheet name="Edgewater" sheetId="47" r:id="rId47"/>
@@ -1242,6 +1242,322 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>42</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>26</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>71</v>
+      </c>
+      <c r="D9">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>64</v>
+      </c>
+      <c r="F9">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>43</v>
+      </c>
+      <c r="I9">
+        <v>58</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>74</v>
+      </c>
+      <c r="L9">
+        <v>66</v>
+      </c>
+      <c r="M9">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1527,7 +1843,317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>28</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>42</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>59</v>
+      </c>
+      <c r="G8">
+        <v>51</v>
+      </c>
+      <c r="H8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>53</v>
+      </c>
+      <c r="C9">
+        <v>76</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>94</v>
+      </c>
+      <c r="G9">
+        <v>74</v>
+      </c>
+      <c r="H9">
+        <v>58</v>
+      </c>
+      <c r="I9">
+        <v>51</v>
+      </c>
+      <c r="J9">
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9">
+        <v>38</v>
+      </c>
+      <c r="M9">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1761,7 +2387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2010,7 +2636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2198,7 +2824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2540,7 +3166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2833,317 +3459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>28</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>31</v>
-      </c>
-      <c r="C8">
-        <v>42</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>59</v>
-      </c>
-      <c r="G8">
-        <v>51</v>
-      </c>
-      <c r="H8">
-        <v>23</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>17</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>53</v>
-      </c>
-      <c r="C9">
-        <v>76</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>94</v>
-      </c>
-      <c r="G9">
-        <v>74</v>
-      </c>
-      <c r="H9">
-        <v>58</v>
-      </c>
-      <c r="I9">
-        <v>51</v>
-      </c>
-      <c r="J9">
-        <v>45</v>
-      </c>
-      <c r="K9">
-        <v>50</v>
-      </c>
-      <c r="L9">
-        <v>38</v>
-      </c>
-      <c r="M9">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3396,7 +3712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3442,257 +3758,6 @@
       </c>
       <c r="C4">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7472,7 +7537,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7535,41 +7600,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7577,208 +7621,164 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>71</v>
-      </c>
-      <c r="D9">
-        <v>59</v>
-      </c>
-      <c r="E9">
-        <v>64</v>
-      </c>
-      <c r="F9">
-        <v>66</v>
-      </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>43</v>
-      </c>
-      <c r="I9">
-        <v>58</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>74</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -10024,7 +10024,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10087,32 +10087,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -10122,206 +10119,157 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>6</v>
       </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>62</v>
+      </c>
+      <c r="F6">
+        <v>44</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>67</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7">
         <v>16</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>23</v>
-      </c>
-      <c r="H7">
-        <v>22</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>44</v>
-      </c>
-      <c r="C8">
-        <v>64</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>30</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>72</v>
-      </c>
-      <c r="C9">
-        <v>103</v>
-      </c>
-      <c r="D9">
-        <v>77</v>
-      </c>
-      <c r="E9">
-        <v>68</v>
-      </c>
-      <c r="F9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>61</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
-      </c>
-      <c r="I9">
-        <v>64</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>64</v>
-      </c>
-      <c r="L9">
-        <v>74</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -12818,7 +12766,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12881,26 +12829,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12910,26 +12867,38 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
       <c r="D3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12939,131 +12908,162 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>15</v>
       </c>
-      <c r="J7">
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K7">
+      <c r="B8">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>64</v>
+      </c>
+      <c r="D8">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
         <v>8</v>
       </c>
-      <c r="L7">
-        <v>17</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>72</v>
+      </c>
+      <c r="C9">
+        <v>103</v>
+      </c>
+      <c r="D9">
+        <v>77</v>
+      </c>
+      <c r="E9">
+        <v>68</v>
+      </c>
+      <c r="F9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>56</v>
+      </c>
+      <c r="I9">
+        <v>64</v>
+      </c>
+      <c r="J9">
+        <v>42</v>
+      </c>
+      <c r="K9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>74</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13602,6 +13602,230 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13873,7 +14097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14086,230 +14310,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>31</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -15447,57 +15447,66 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>1</v>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15505,34 +15514,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15540,40 +15555,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15581,40 +15596,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
         <v>9</v>
       </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
+      <c r="K7">
         <v>8</v>
       </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
       <c r="L7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -17756,7 +17771,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17819,221 +17834,174 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
       <c r="L3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="E6">
+      <c r="J6">
         <v>7</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
       <c r="C7">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B8">
-        <v>34</v>
-      </c>
-      <c r="C8">
-        <v>52</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>45</v>
-      </c>
-      <c r="G8">
-        <v>32</v>
-      </c>
-      <c r="H8">
-        <v>31</v>
-      </c>
-      <c r="I8">
-        <v>35</v>
-      </c>
-      <c r="J8">
-        <v>32</v>
-      </c>
-      <c r="K8">
-        <v>39</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -20014,15 +19982,27 @@
         <v>2</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -20030,20 +20010,35 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -20053,15 +20048,27 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -20070,33 +20077,39 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -20105,37 +20118,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -20143,40 +20159,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L8">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -21806,20 +21822,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="K2">
-        <v>1</v>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21827,37 +21843,37 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -21866,40 +21882,34 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21907,25 +21917,22 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>19</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -21934,13 +21941,13 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -21948,40 +21955,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
       <c r="G8">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
       <c r="J8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -23565,7 +23572,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23628,55 +23635,40 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -23684,133 +23676,141 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
         <v>11</v>
       </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>67</v>
-      </c>
-      <c r="F7">
-        <v>50</v>
-      </c>
-      <c r="G7">
+      <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>23</v>
+      </c>
+      <c r="H8">
         <v>12</v>
       </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
         <v>8</v>
       </c>
-      <c r="K7">
-        <v>20</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
         <v>16</v>
+      </c>
+      <c r="M8">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Austin" sheetId="3" r:id="rId3"/>
-    <sheet name="Loop" sheetId="4" r:id="rId4"/>
-    <sheet name="Old Town" sheetId="5" r:id="rId5"/>
-    <sheet name="Chatham" sheetId="6" r:id="rId6"/>
+    <sheet name="Chatham" sheetId="3" r:id="rId3"/>
+    <sheet name="Austin" sheetId="4" r:id="rId4"/>
+    <sheet name="Loop" sheetId="5" r:id="rId5"/>
+    <sheet name="Old Town" sheetId="6" r:id="rId6"/>
     <sheet name="New City" sheetId="7" r:id="rId7"/>
     <sheet name="Belmont Cragin" sheetId="8" r:id="rId8"/>
     <sheet name="Woodlawn" sheetId="9" r:id="rId9"/>
@@ -875,7 +875,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2">
         <v>65</v>
@@ -893,13 +893,13 @@
         <v>76</v>
       </c>
       <c r="I2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L2">
         <v>102</v>
@@ -913,7 +913,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>63</v>
@@ -925,22 +925,22 @@
         <v>99</v>
       </c>
       <c r="F3">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I3">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J3">
         <v>148</v>
       </c>
       <c r="K3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L3">
         <v>173</v>
@@ -1074,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1123,28 +1123,28 @@
         <v>343</v>
       </c>
       <c r="D9">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E9">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F9">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G9">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H9">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I9">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J9">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K9">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="L9">
         <v>336</v>
@@ -1158,40 +1158,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="C10">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="D10">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="E10">
-        <v>1550</v>
+        <v>1556</v>
       </c>
       <c r="F10">
-        <v>1587</v>
+        <v>1593</v>
       </c>
       <c r="G10">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H10">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I10">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J10">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K10">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L10">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M10">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1199,40 +1199,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="C11">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="D11">
-        <v>1731</v>
+        <v>1737</v>
       </c>
       <c r="E11">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="F11">
-        <v>2142</v>
+        <v>2150</v>
       </c>
       <c r="G11">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="H11">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="I11">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="J11">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="K11">
-        <v>1164</v>
+        <v>1175</v>
       </c>
       <c r="L11">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="M11">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -1438,7 +1438,7 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <v>26</v>
@@ -1479,7 +1479,7 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>33</v>
@@ -1661,7 +1661,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -1699,7 +1699,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>11</v>
@@ -1800,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1906,7 +1906,7 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -1953,7 +1953,7 @@
         <v>13</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -1979,7 +1979,7 @@
         <v>25</v>
       </c>
       <c r="C9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>15</v>
@@ -1988,13 +1988,13 @@
         <v>25</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9">
         <v>32</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>18</v>
@@ -2098,7 +2098,7 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -2214,7 +2214,7 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -2290,13 +2290,13 @@
         <v>29</v>
       </c>
       <c r="I8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8">
         <v>29</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L8">
         <v>29</v>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -2583,7 +2583,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8">
         <v>16</v>
@@ -3724,7 +3724,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -3742,7 +3742,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>8</v>
@@ -3762,7 +3762,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>13</v>
@@ -3783,7 +3783,7 @@
         <v>12</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>15</v>
@@ -3983,10 +3983,10 @@
         <v>23</v>
       </c>
       <c r="J5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L5">
         <v>25</v>
@@ -4041,7 +4041,7 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -4097,7 +4097,7 @@
         <v>94</v>
       </c>
       <c r="G8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8">
         <v>58</v>
@@ -4473,7 +4473,7 @@
         <v>43</v>
       </c>
       <c r="E19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19">
         <v>38</v>
@@ -4497,7 +4497,7 @@
         <v>30</v>
       </c>
       <c r="M19">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="I21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J21">
         <v>13</v>
@@ -4596,7 +4596,7 @@
         <v>13</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22">
         <v>3</v>
@@ -4631,7 +4631,7 @@
         <v>15</v>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>13</v>
@@ -4652,7 +4652,7 @@
         <v>12</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -4788,7 +4788,7 @@
         <v>38</v>
       </c>
       <c r="B28">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28">
         <v>103</v>
@@ -4797,13 +4797,13 @@
         <v>77</v>
       </c>
       <c r="E28">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F28">
         <v>86</v>
       </c>
       <c r="G28">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H28">
         <v>56</v>
@@ -4815,7 +4815,7 @@
         <v>42</v>
       </c>
       <c r="K28">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L28">
         <v>74</v>
@@ -4856,7 +4856,7 @@
         <v>20</v>
       </c>
       <c r="K29">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L29">
         <v>27</v>
@@ -4949,13 +4949,13 @@
         <v>94</v>
       </c>
       <c r="F32">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G32">
         <v>88</v>
       </c>
       <c r="H32">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I32">
         <v>73</v>
@@ -5071,7 +5071,7 @@
         <v>46</v>
       </c>
       <c r="B36">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36">
         <v>71</v>
@@ -5083,16 +5083,16 @@
         <v>64</v>
       </c>
       <c r="F36">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36">
         <v>34</v>
       </c>
       <c r="H36">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I36">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J36">
         <v>40</v>
@@ -5104,7 +5104,7 @@
         <v>66</v>
       </c>
       <c r="M36">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5337,7 +5337,7 @@
         <v>13</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>10</v>
@@ -5407,7 +5407,7 @@
         <v>15</v>
       </c>
       <c r="G45">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H45">
         <v>12</v>
@@ -5495,13 +5495,13 @@
         <v>29</v>
       </c>
       <c r="I47">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J47">
         <v>29</v>
       </c>
       <c r="K47">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L47">
         <v>29</v>
@@ -5603,7 +5603,7 @@
         <v>14</v>
       </c>
       <c r="D50">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E50">
         <v>32</v>
@@ -5624,7 +5624,7 @@
         <v>22</v>
       </c>
       <c r="K50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L50">
         <v>33</v>
@@ -5720,19 +5720,19 @@
         <v>63</v>
       </c>
       <c r="B53">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C53">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D53">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E53">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F53">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G53">
         <v>201</v>
@@ -5741,7 +5741,7 @@
         <v>129</v>
       </c>
       <c r="I53">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J53">
         <v>173</v>
@@ -5826,7 +5826,7 @@
         <v>3</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55">
         <v>4</v>
@@ -6064,7 +6064,7 @@
         <v>73</v>
       </c>
       <c r="B63">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>8</v>
       </c>
       <c r="K65">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L65">
         <v>16</v>
@@ -6211,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="K66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66">
         <v>1</v>
@@ -6342,7 +6342,7 @@
         <v>36</v>
       </c>
       <c r="E70">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F70">
         <v>90</v>
@@ -6360,7 +6360,7 @@
         <v>14</v>
       </c>
       <c r="K70">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L70">
         <v>11</v>
@@ -6418,7 +6418,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E72">
         <v>11</v>
@@ -6485,13 +6485,13 @@
         <v>59</v>
       </c>
       <c r="E74">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F74">
         <v>74</v>
       </c>
       <c r="G74">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H74">
         <v>15</v>
@@ -6558,7 +6558,7 @@
         <v>52</v>
       </c>
       <c r="D76">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E76">
         <v>74</v>
@@ -6567,7 +6567,7 @@
         <v>45</v>
       </c>
       <c r="G76">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H76">
         <v>31</v>
@@ -6576,7 +6576,7 @@
         <v>35</v>
       </c>
       <c r="J76">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K76">
         <v>39</v>
@@ -6605,22 +6605,22 @@
         <v>52</v>
       </c>
       <c r="F77">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G77">
         <v>37</v>
       </c>
       <c r="H77">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I77">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J77">
         <v>52</v>
       </c>
       <c r="K77">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L77">
         <v>33</v>
@@ -6634,7 +6634,7 @@
         <v>88</v>
       </c>
       <c r="B78">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C78">
         <v>24</v>
@@ -6958,7 +6958,7 @@
         <v>25</v>
       </c>
       <c r="C87">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D87">
         <v>15</v>
@@ -6967,13 +6967,13 @@
         <v>25</v>
       </c>
       <c r="F87">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G87">
         <v>32</v>
       </c>
       <c r="H87">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I87">
         <v>18</v>
@@ -7067,7 +7067,7 @@
         <v>7</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M89">
         <v>14</v>
@@ -7148,7 +7148,7 @@
         <v>17</v>
       </c>
       <c r="C92">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D92">
         <v>33</v>
@@ -7189,7 +7189,7 @@
         <v>13</v>
       </c>
       <c r="C93">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D93">
         <v>4</v>
@@ -7350,10 +7350,10 @@
         <v>23</v>
       </c>
       <c r="C97">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D97">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E97">
         <v>17</v>
@@ -7374,7 +7374,7 @@
         <v>12</v>
       </c>
       <c r="K97">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L97">
         <v>4</v>
@@ -7415,7 +7415,7 @@
         <v>4</v>
       </c>
       <c r="K98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L98">
         <v>2</v>
@@ -7429,40 +7429,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="C99">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="D99">
-        <v>1731</v>
+        <v>1737</v>
       </c>
       <c r="E99">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="F99">
-        <v>2142</v>
+        <v>2150</v>
       </c>
       <c r="G99">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="H99">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="I99">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="J99">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="K99">
-        <v>1164</v>
+        <v>1175</v>
       </c>
       <c r="L99">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="M99">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -8245,7 +8245,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -8286,7 +8286,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -8475,7 +8475,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7">
         <v>18</v>
@@ -8557,7 +8557,7 @@
         <v>20</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9">
         <v>27</v>
@@ -8687,7 +8687,7 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -8782,7 +8782,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7">
         <v>33</v>
@@ -8796,7 +8796,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8">
         <v>64</v>
@@ -8805,7 +8805,7 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8">
         <v>47</v>
@@ -8837,7 +8837,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9">
         <v>103</v>
@@ -8846,13 +8846,13 @@
         <v>77</v>
       </c>
       <c r="E9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9">
         <v>86</v>
       </c>
       <c r="G9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H9">
         <v>56</v>
@@ -8864,7 +8864,7 @@
         <v>42</v>
       </c>
       <c r="K9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L9">
         <v>74</v>
@@ -9165,6 +9165,9 @@
       <c r="I2">
         <v>3</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
         <v>2</v>
       </c>
@@ -9261,7 +9264,7 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -9293,7 +9296,7 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>59</v>
@@ -9311,7 +9314,7 @@
         <v>18</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -9334,7 +9337,7 @@
         <v>52</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>74</v>
@@ -9343,7 +9346,7 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8">
         <v>31</v>
@@ -9352,7 +9355,7 @@
         <v>35</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K8">
         <v>39</v>
@@ -9525,7 +9528,7 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5">
         <v>9</v>
@@ -9560,7 +9563,7 @@
         <v>49</v>
       </c>
       <c r="E6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6">
         <v>64</v>
@@ -9601,13 +9604,13 @@
         <v>59</v>
       </c>
       <c r="E7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7">
         <v>74</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7">
         <v>15</v>
@@ -9867,13 +9870,13 @@
         <v>57</v>
       </c>
       <c r="F8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G8">
         <v>45</v>
       </c>
       <c r="H8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8">
         <v>38</v>
@@ -9908,13 +9911,13 @@
         <v>94</v>
       </c>
       <c r="F9">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G9">
         <v>88</v>
       </c>
       <c r="H9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9">
         <v>73</v>
@@ -10164,10 +10167,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -10227,41 +10230,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10269,202 +10269,182 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
         <v>6</v>
       </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
       <c r="L3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
         <v>7</v>
       </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>13</v>
+      </c>
       <c r="L6">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
         <v>13</v>
       </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
       <c r="H7">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L7">
         <v>11</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>42</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="G8">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H8">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I8">
+        <v>26</v>
+      </c>
+      <c r="J8">
         <v>28</v>
       </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
       <c r="K8">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>53</v>
-      </c>
-      <c r="C9">
-        <v>76</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>94</v>
-      </c>
-      <c r="G9">
-        <v>74</v>
-      </c>
-      <c r="H9">
-        <v>58</v>
-      </c>
-      <c r="I9">
-        <v>51</v>
-      </c>
-      <c r="J9">
-        <v>45</v>
-      </c>
-      <c r="K9">
-        <v>50</v>
-      </c>
-      <c r="L9">
-        <v>38</v>
-      </c>
-      <c r="M9">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -10891,7 +10871,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>11</v>
@@ -10912,7 +10892,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -10973,7 +10953,7 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>32</v>
@@ -10994,7 +10974,7 @@
         <v>22</v>
       </c>
       <c r="K7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7">
         <v>33</v>
@@ -11349,7 +11329,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -11361,7 +11341,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -11429,6 +11409,9 @@
       <c r="L6">
         <v>1</v>
       </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
@@ -11453,10 +11436,10 @@
         <v>11</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <v>18</v>
@@ -11494,7 +11477,7 @@
         <v>15</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8">
         <v>28</v>
@@ -11517,7 +11500,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9">
         <v>71</v>
@@ -11529,16 +11512,16 @@
         <v>64</v>
       </c>
       <c r="F9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>34</v>
       </c>
       <c r="H9">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J9">
         <v>40</v>
@@ -11550,7 +11533,7 @@
         <v>66</v>
       </c>
       <c r="M9">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -12874,7 +12857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12938,40 +12921,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
-      </c>
-      <c r="L2">
-        <v>13</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12979,56 +12962,47 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="M3">
         <v>11</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -13036,177 +13010,154 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
       <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>28</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E8">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F8">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H8">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I8">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="K8">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="L8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="C9">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="D9">
-        <v>366</v>
+        <v>42</v>
       </c>
       <c r="E9">
-        <v>448</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>422</v>
+        <v>94</v>
       </c>
       <c r="G9">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="H9">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I9">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="J9">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="K9">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="L9">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="M9">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>157</v>
-      </c>
-      <c r="C10">
-        <v>250</v>
-      </c>
-      <c r="D10">
-        <v>424</v>
-      </c>
-      <c r="E10">
-        <v>507</v>
-      </c>
-      <c r="F10">
-        <v>477</v>
-      </c>
-      <c r="G10">
-        <v>201</v>
-      </c>
-      <c r="H10">
-        <v>129</v>
-      </c>
-      <c r="I10">
-        <v>249</v>
-      </c>
-      <c r="J10">
-        <v>173</v>
-      </c>
-      <c r="K10">
-        <v>154</v>
-      </c>
-      <c r="L10">
-        <v>133</v>
-      </c>
-      <c r="M10">
-        <v>90</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -14825,7 +14776,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -14834,7 +14785,7 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -14939,16 +14890,16 @@
         <v>31</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9">
         <v>21</v>
       </c>
       <c r="H9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J9">
         <v>26</v>
@@ -14980,22 +14931,22 @@
         <v>52</v>
       </c>
       <c r="F10">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10">
         <v>37</v>
       </c>
       <c r="H10">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I10">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J10">
         <v>52</v>
       </c>
       <c r="K10">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L10">
         <v>33</v>
@@ -15109,6 +15060,9 @@
       <c r="J3">
         <v>1</v>
       </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
       <c r="M3">
         <v>2</v>
       </c>
@@ -15223,7 +15177,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -15410,7 +15364,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -15451,7 +15405,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -15494,10 +15448,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15557,26 +15511,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="I2">
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15584,162 +15553,234 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>39</v>
-      </c>
-      <c r="F6">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>42</v>
+      </c>
+      <c r="H8">
+        <v>43</v>
+      </c>
+      <c r="I8">
+        <v>65</v>
+      </c>
+      <c r="J8">
+        <v>44</v>
+      </c>
+      <c r="K8">
+        <v>38</v>
+      </c>
+      <c r="L8">
+        <v>34</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>123</v>
+      </c>
+      <c r="C9">
+        <v>211</v>
+      </c>
+      <c r="D9">
+        <v>368</v>
+      </c>
+      <c r="E9">
+        <v>451</v>
+      </c>
+      <c r="F9">
+        <v>425</v>
+      </c>
+      <c r="G9">
+        <v>139</v>
+      </c>
+      <c r="H9">
+        <v>68</v>
+      </c>
+      <c r="I9">
+        <v>147</v>
+      </c>
+      <c r="J9">
+        <v>85</v>
+      </c>
+      <c r="K9">
+        <v>79</v>
+      </c>
+      <c r="L9">
+        <v>59</v>
+      </c>
+      <c r="M9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>18</v>
-      </c>
-      <c r="C7">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>48</v>
-      </c>
-      <c r="F7">
+      <c r="B10">
+        <v>159</v>
+      </c>
+      <c r="C10">
+        <v>252</v>
+      </c>
+      <c r="D10">
+        <v>426</v>
+      </c>
+      <c r="E10">
+        <v>510</v>
+      </c>
+      <c r="F10">
+        <v>480</v>
+      </c>
+      <c r="G10">
+        <v>201</v>
+      </c>
+      <c r="H10">
+        <v>129</v>
+      </c>
+      <c r="I10">
+        <v>250</v>
+      </c>
+      <c r="J10">
+        <v>173</v>
+      </c>
+      <c r="K10">
+        <v>154</v>
+      </c>
+      <c r="L10">
+        <v>133</v>
+      </c>
+      <c r="M10">
         <v>90</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>22</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -16930,10 +16971,10 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>14</v>
@@ -17012,10 +17053,10 @@
         <v>23</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7">
         <v>25</v>
@@ -17133,7 +17174,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -17280,7 +17321,7 @@
         <v>14</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9">
         <v>13</v>
@@ -17481,7 +17522,7 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -17522,7 +17563,7 @@
         <v>15</v>
       </c>
       <c r="G8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8">
         <v>12</v>
@@ -17686,7 +17727,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -17721,7 +17762,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -17906,7 +17947,7 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -17988,7 +18029,7 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -18013,10 +18054,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -18076,38 +18117,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18118,179 +18147,159 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
       </c>
       <c r="J5">
         <v>2</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>49</v>
+      </c>
+      <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7">
         <v>34</v>
       </c>
-      <c r="D7">
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
         <v>23</v>
-      </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>11</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
       </c>
       <c r="L7">
         <v>11</v>
       </c>
       <c r="M7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>36</v>
-      </c>
-      <c r="C8">
-        <v>42</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>31</v>
-      </c>
-      <c r="H8">
-        <v>17</v>
-      </c>
-      <c r="I8">
-        <v>26</v>
-      </c>
-      <c r="J8">
-        <v>28</v>
-      </c>
-      <c r="K8">
-        <v>39</v>
-      </c>
-      <c r="L8">
-        <v>30</v>
-      </c>
-      <c r="M8">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -20109,7 +20118,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -20147,7 +20156,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -20493,7 +20502,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20576,7 +20585,7 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -21766,6 +21775,9 @@
       <c r="D6">
         <v>2</v>
       </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
       <c r="I6">
         <v>1</v>
       </c>
@@ -21825,7 +21837,7 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -22403,7 +22415,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>21</v>
@@ -22444,7 +22456,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -22977,6 +22989,9 @@
       <c r="I3">
         <v>3</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>3</v>
       </c>
@@ -23016,7 +23031,7 @@
         <v>3</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -23640,7 +23655,7 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -23706,10 +23721,10 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -23747,10 +23762,10 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>17</v>
@@ -23771,7 +23786,7 @@
         <v>12</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>4</v>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,47 +9,47 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Logan Square" sheetId="3" r:id="rId3"/>
-    <sheet name="Grand Crossing" sheetId="4" r:id="rId4"/>
-    <sheet name="South Shore" sheetId="5" r:id="rId5"/>
-    <sheet name="Loop" sheetId="6" r:id="rId6"/>
-    <sheet name="Austin" sheetId="7" r:id="rId7"/>
-    <sheet name="Avondale" sheetId="8" r:id="rId8"/>
-    <sheet name="Rush &amp; Division" sheetId="9" r:id="rId9"/>
-    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
-    <sheet name="Oakland" sheetId="11" r:id="rId11"/>
-    <sheet name="River North" sheetId="12" r:id="rId12"/>
-    <sheet name="Old Town" sheetId="13" r:id="rId13"/>
-    <sheet name="New City" sheetId="14" r:id="rId14"/>
-    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
-    <sheet name="Woodlawn" sheetId="16" r:id="rId16"/>
-    <sheet name="West Loop" sheetId="17" r:id="rId17"/>
-    <sheet name="Printers Row" sheetId="18" r:id="rId18"/>
-    <sheet name="Uptown" sheetId="19" r:id="rId19"/>
-    <sheet name="Lake View" sheetId="20" r:id="rId20"/>
-    <sheet name="North Lawndale" sheetId="21" r:id="rId21"/>
-    <sheet name="Hyde Park" sheetId="22" r:id="rId22"/>
-    <sheet name="Grand Boulevard" sheetId="23" r:id="rId23"/>
-    <sheet name="West Town" sheetId="24" r:id="rId24"/>
-    <sheet name="Douglas" sheetId="25" r:id="rId25"/>
-    <sheet name="Norwood Park" sheetId="26" r:id="rId26"/>
-    <sheet name="Washington Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Fuller Park" sheetId="28" r:id="rId28"/>
-    <sheet name="Englewood" sheetId="29" r:id="rId29"/>
-    <sheet name="Greektown" sheetId="30" r:id="rId30"/>
-    <sheet name="Rogers Park" sheetId="31" r:id="rId31"/>
-    <sheet name="Garfield Park" sheetId="32" r:id="rId32"/>
-    <sheet name="Lincoln Park" sheetId="33" r:id="rId33"/>
-    <sheet name="Edgewater" sheetId="34" r:id="rId34"/>
-    <sheet name="Little Italy, UIC" sheetId="35" r:id="rId35"/>
-    <sheet name="Albany Park" sheetId="36" r:id="rId36"/>
-    <sheet name="Gage Park" sheetId="37" r:id="rId37"/>
-    <sheet name="Wicker Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Avalon Park" sheetId="39" r:id="rId39"/>
-    <sheet name="Kenwood" sheetId="40" r:id="rId40"/>
-    <sheet name="Humboldt Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Lower West Side" sheetId="42" r:id="rId42"/>
-    <sheet name="Near South Side" sheetId="43" r:id="rId43"/>
+    <sheet name="Near South Side" sheetId="3" r:id="rId3"/>
+    <sheet name="Logan Square" sheetId="4" r:id="rId4"/>
+    <sheet name="Grand Crossing" sheetId="5" r:id="rId5"/>
+    <sheet name="South Shore" sheetId="6" r:id="rId6"/>
+    <sheet name="Loop" sheetId="7" r:id="rId7"/>
+    <sheet name="Austin" sheetId="8" r:id="rId8"/>
+    <sheet name="Avondale" sheetId="9" r:id="rId9"/>
+    <sheet name="Rush &amp; Division" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="Oakland" sheetId="12" r:id="rId12"/>
+    <sheet name="River North" sheetId="13" r:id="rId13"/>
+    <sheet name="Old Town" sheetId="14" r:id="rId14"/>
+    <sheet name="New City" sheetId="15" r:id="rId15"/>
+    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
+    <sheet name="Woodlawn" sheetId="17" r:id="rId17"/>
+    <sheet name="West Loop" sheetId="18" r:id="rId18"/>
+    <sheet name="Printers Row" sheetId="19" r:id="rId19"/>
+    <sheet name="Uptown" sheetId="20" r:id="rId20"/>
+    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
+    <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
+    <sheet name="Hyde Park" sheetId="23" r:id="rId23"/>
+    <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
+    <sheet name="West Town" sheetId="25" r:id="rId25"/>
+    <sheet name="Douglas" sheetId="26" r:id="rId26"/>
+    <sheet name="Norwood Park" sheetId="27" r:id="rId27"/>
+    <sheet name="Washington Park" sheetId="28" r:id="rId28"/>
+    <sheet name="Fuller Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Englewood" sheetId="30" r:id="rId30"/>
+    <sheet name="Greektown" sheetId="31" r:id="rId31"/>
+    <sheet name="Rogers Park" sheetId="32" r:id="rId32"/>
+    <sheet name="Garfield Park" sheetId="33" r:id="rId33"/>
+    <sheet name="Lincoln Park" sheetId="34" r:id="rId34"/>
+    <sheet name="Edgewater" sheetId="35" r:id="rId35"/>
+    <sheet name="Little Italy, UIC" sheetId="36" r:id="rId36"/>
+    <sheet name="Albany Park" sheetId="37" r:id="rId37"/>
+    <sheet name="Gage Park" sheetId="38" r:id="rId38"/>
+    <sheet name="Wicker Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Avalon Park" sheetId="40" r:id="rId40"/>
+    <sheet name="Kenwood" sheetId="41" r:id="rId41"/>
+    <sheet name="Humboldt Park" sheetId="42" r:id="rId42"/>
+    <sheet name="Lower West Side" sheetId="43" r:id="rId43"/>
     <sheet name="North Center" sheetId="44" r:id="rId44"/>
     <sheet name="O'Hare" sheetId="45" r:id="rId45"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="46" r:id="rId46"/>
@@ -875,7 +875,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>68</v>
@@ -925,7 +925,7 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3">
         <v>93</v>
@@ -940,10 +940,10 @@
         <v>151</v>
       </c>
       <c r="K3">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M3">
         <v>150</v>
@@ -1033,7 +1033,7 @@
         <v>18</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6">
         <v>23</v>
@@ -1117,40 +1117,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C9">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D9">
         <v>307</v>
       </c>
       <c r="E9">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F9">
         <v>393</v>
       </c>
       <c r="G9">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H9">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I9">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J9">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K9">
         <v>374</v>
       </c>
       <c r="L9">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M9">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1158,37 +1158,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="C10">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="D10">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="E10">
-        <v>1586</v>
+        <v>1598</v>
       </c>
       <c r="F10">
-        <v>1616</v>
+        <v>1627</v>
       </c>
       <c r="G10">
         <v>773</v>
       </c>
       <c r="H10">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="I10">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J10">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="K10">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L10">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="M10">
         <v>364</v>
@@ -1199,40 +1199,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="C11">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="D11">
-        <v>1758</v>
+        <v>1764</v>
       </c>
       <c r="E11">
-        <v>2064</v>
+        <v>2079</v>
       </c>
       <c r="F11">
-        <v>2176</v>
+        <v>2188</v>
       </c>
       <c r="G11">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="H11">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I11">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="J11">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="K11">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="L11">
-        <v>1125</v>
+        <v>1137</v>
       </c>
       <c r="M11">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -1241,6 +1241,255 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>42</v>
+      </c>
+      <c r="E6">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>46</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1469,10 +1718,10 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7">
         <v>11</v>
@@ -1510,10 +1759,10 @@
         <v>26</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L8">
         <v>30</v>
@@ -1527,7 +1776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1656,7 +1905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1844,7 +2093,7 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6">
         <v>60</v>
@@ -1862,7 +2111,7 @@
         <v>18</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>14</v>
@@ -1885,7 +2134,7 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7">
         <v>64</v>
@@ -1903,7 +2152,7 @@
         <v>33</v>
       </c>
       <c r="J7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7">
         <v>27</v>
@@ -1920,7 +2169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2039,7 +2288,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2164,7 +2413,7 @@
         <v>23</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -2175,7 +2424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2325,7 +2574,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -2363,7 +2612,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -2392,7 +2641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2513,7 +2762,7 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -2551,7 +2800,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -2580,7 +2829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2759,7 +3008,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -2800,7 +3049,7 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>18</v>
@@ -2835,7 +3084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2954,7 +3203,7 @@
         <v>4</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3101,7 +3350,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M9">
         <v>17</v>
@@ -3112,7 +3361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3322,289 +3571,6 @@
       </c>
       <c r="M6">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>13</v>
-      </c>
-      <c r="E8">
-        <v>18</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>13</v>
-      </c>
-      <c r="H8">
-        <v>9</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>9</v>
-      </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>25</v>
-      </c>
-      <c r="C9">
-        <v>33</v>
-      </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
-      <c r="E9">
-        <v>26</v>
-      </c>
-      <c r="F9">
-        <v>23</v>
-      </c>
-      <c r="G9">
-        <v>32</v>
-      </c>
-      <c r="H9">
-        <v>21</v>
-      </c>
-      <c r="I9">
-        <v>18</v>
-      </c>
-      <c r="J9">
-        <v>21</v>
-      </c>
-      <c r="K9">
-        <v>23</v>
-      </c>
-      <c r="L9">
-        <v>22</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3687,7 +3653,7 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -3804,7 +3770,7 @@
         <v>19</v>
       </c>
       <c r="L5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -3818,7 +3784,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -3845,7 +3811,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -3868,7 +3834,7 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -3880,10 +3846,10 @@
         <v>16</v>
       </c>
       <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
         <v>9</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
       </c>
       <c r="L7">
         <v>11</v>
@@ -3903,25 +3869,25 @@
         <v>76</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>74</v>
       </c>
       <c r="F8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8">
         <v>76</v>
       </c>
       <c r="H8">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I8">
         <v>51</v>
       </c>
       <c r="J8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K8">
         <v>51</v>
@@ -4026,7 +3992,7 @@
         <v>5</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -4303,10 +4269,10 @@
         <v>26</v>
       </c>
       <c r="J19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L19">
         <v>30</v>
@@ -4329,7 +4295,7 @@
         <v>15</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20">
         <v>9</v>
@@ -4391,7 +4357,7 @@
         <v>26</v>
       </c>
       <c r="L21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M21">
         <v>7</v>
@@ -4580,7 +4546,7 @@
         <v>15</v>
       </c>
       <c r="H27">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I27">
         <v>14</v>
@@ -4606,13 +4572,13 @@
         <v>74</v>
       </c>
       <c r="C28">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D28">
         <v>77</v>
       </c>
       <c r="E28">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F28">
         <v>87</v>
@@ -4674,7 +4640,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M29">
         <v>11</v>
@@ -4697,7 +4663,7 @@
         <v>26</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -4761,7 +4727,7 @@
         <v>77</v>
       </c>
       <c r="E32">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F32">
         <v>154</v>
@@ -4773,7 +4739,7 @@
         <v>61</v>
       </c>
       <c r="I32">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J32">
         <v>53</v>
@@ -4889,13 +4855,13 @@
         <v>47</v>
       </c>
       <c r="C36">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D36">
         <v>60</v>
       </c>
       <c r="E36">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F36">
         <v>68</v>
@@ -4904,7 +4870,7 @@
         <v>36</v>
       </c>
       <c r="H36">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I36">
         <v>60</v>
@@ -5055,7 +5021,7 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41">
         <v>17</v>
@@ -5064,7 +5030,7 @@
         <v>17</v>
       </c>
       <c r="F41">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G41">
         <v>22</v>
@@ -5134,7 +5100,7 @@
         <v>53</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C43">
         <v>9</v>
@@ -5143,7 +5109,7 @@
         <v>18</v>
       </c>
       <c r="E43">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43">
         <v>12</v>
@@ -5219,13 +5185,13 @@
         <v>15</v>
       </c>
       <c r="F45">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G45">
         <v>24</v>
       </c>
       <c r="H45">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I45">
         <v>10</v>
@@ -5289,16 +5255,16 @@
         <v>57</v>
       </c>
       <c r="B47">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C47">
         <v>56</v>
       </c>
       <c r="D47">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E47">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F47">
         <v>55</v>
@@ -5421,7 +5387,7 @@
         <v>24</v>
       </c>
       <c r="E50">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F50">
         <v>51</v>
@@ -5500,7 +5466,7 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E52">
         <v>23</v>
@@ -5538,16 +5504,16 @@
         <v>166</v>
       </c>
       <c r="C53">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D53">
         <v>433</v>
       </c>
       <c r="E53">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F53">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="G53">
         <v>205</v>
@@ -5562,10 +5528,10 @@
         <v>176</v>
       </c>
       <c r="K53">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L53">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M53">
         <v>92</v>
@@ -5868,10 +5834,10 @@
         <v>17</v>
       </c>
       <c r="L62">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M62">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -5891,7 +5857,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G63">
         <v>6</v>
@@ -5961,10 +5927,10 @@
         <v>27</v>
       </c>
       <c r="C65">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D65">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E65">
         <v>32</v>
@@ -5982,7 +5948,7 @@
         <v>28</v>
       </c>
       <c r="J65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K65">
         <v>21</v>
@@ -6181,7 +6147,7 @@
         <v>23</v>
       </c>
       <c r="L70">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M70">
         <v>7</v>
@@ -6300,7 +6266,7 @@
         <v>29</v>
       </c>
       <c r="D74">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E74">
         <v>64</v>
@@ -6318,7 +6284,7 @@
         <v>33</v>
       </c>
       <c r="J74">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K74">
         <v>27</v>
@@ -6394,13 +6360,13 @@
         <v>36</v>
       </c>
       <c r="J76">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K76">
         <v>39</v>
       </c>
       <c r="L76">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M76">
         <v>24</v>
@@ -6426,13 +6392,13 @@
         <v>45</v>
       </c>
       <c r="G77">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H77">
         <v>41</v>
       </c>
       <c r="I77">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J77">
         <v>53</v>
@@ -6473,7 +6439,7 @@
         <v>12</v>
       </c>
       <c r="I78">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J78">
         <v>13</v>
@@ -6545,7 +6511,7 @@
         <v>91</v>
       </c>
       <c r="B81">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C81">
         <v>10</v>
@@ -6776,7 +6742,7 @@
         <v>97</v>
       </c>
       <c r="B87">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C87">
         <v>33</v>
@@ -6873,7 +6839,7 @@
         <v>10</v>
       </c>
       <c r="G89">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H89">
         <v>9</v>
@@ -6996,7 +6962,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M92">
         <v>17</v>
@@ -7098,7 +7064,7 @@
         <v>68</v>
       </c>
       <c r="F95">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G95">
         <v>13</v>
@@ -7116,7 +7082,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M95">
         <v>16</v>
@@ -7127,7 +7093,7 @@
         <v>106</v>
       </c>
       <c r="B96">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96">
         <v>12</v>
@@ -7174,7 +7140,7 @@
         <v>16</v>
       </c>
       <c r="D97">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E97">
         <v>18</v>
@@ -7250,40 +7216,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="C99">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="D99">
-        <v>1758</v>
+        <v>1764</v>
       </c>
       <c r="E99">
-        <v>2064</v>
+        <v>2079</v>
       </c>
       <c r="F99">
-        <v>2176</v>
+        <v>2188</v>
       </c>
       <c r="G99">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="H99">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I99">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="J99">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="K99">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="L99">
-        <v>1125</v>
+        <v>1137</v>
       </c>
       <c r="M99">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -7393,7 +7359,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7457,85 +7423,79 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -7543,143 +7503,136 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>36</v>
-      </c>
-      <c r="D7">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>18</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>36</v>
-      </c>
-      <c r="C8">
-        <v>56</v>
-      </c>
-      <c r="D8">
-        <v>40</v>
-      </c>
-      <c r="E8">
-        <v>51</v>
-      </c>
-      <c r="F8">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>47</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>40</v>
-      </c>
       <c r="J8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>25</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>26</v>
+      </c>
+      <c r="C9">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>23</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>18</v>
+      </c>
+      <c r="J9">
+        <v>21</v>
+      </c>
+      <c r="K9">
+        <v>23</v>
+      </c>
+      <c r="L9">
+        <v>22</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -7752,41 +7705,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7794,47 +7744,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -7842,49 +7792,61 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="H5">
         <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
+      <c r="I6">
         <v>16</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>14</v>
-      </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -7892,40 +7854,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -7933,40 +7895,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C8">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D8">
+        <v>41</v>
+      </c>
+      <c r="E8">
+        <v>52</v>
+      </c>
+      <c r="F8">
+        <v>55</v>
+      </c>
+      <c r="G8">
+        <v>47</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
         <v>40</v>
       </c>
-      <c r="E8">
-        <v>32</v>
-      </c>
-      <c r="F8">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>38</v>
-      </c>
-      <c r="H8">
-        <v>17</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
       <c r="J8">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K8">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7975,6 +7937,293 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>41</v>
+      </c>
+      <c r="E8">
+        <v>32</v>
+      </c>
+      <c r="F8">
+        <v>52</v>
+      </c>
+      <c r="G8">
+        <v>38</v>
+      </c>
+      <c r="H8">
+        <v>17</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>21</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8194,7 +8443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8443,7 +8692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8556,7 +8805,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -8628,7 +8877,7 @@
         <v>63</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -8669,7 +8918,7 @@
         <v>68</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -8687,7 +8936,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7">
         <v>16</v>
@@ -8698,7 +8947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8930,225 +9179,6 @@
       </c>
       <c r="M8">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9221,17 +9251,8 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -9244,42 +9265,30 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -9287,32 +9296,17 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
       <c r="D5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -9321,7 +9315,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9329,40 +9323,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
         <v>7</v>
       </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
       <c r="H6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9370,40 +9364,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9412,6 +9406,261 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9592,7 +9841,7 @@
         <v>11</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -9674,317 +9923,10 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M9">
         <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>23</v>
-      </c>
-      <c r="H7">
-        <v>22</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>46</v>
-      </c>
-      <c r="C8">
-        <v>65</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>46</v>
-      </c>
-      <c r="F8">
-        <v>48</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>21</v>
-      </c>
-      <c r="I8">
-        <v>30</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>74</v>
-      </c>
-      <c r="C9">
-        <v>104</v>
-      </c>
-      <c r="D9">
-        <v>77</v>
-      </c>
-      <c r="E9">
-        <v>69</v>
-      </c>
-      <c r="F9">
-        <v>87</v>
-      </c>
-      <c r="G9">
-        <v>62</v>
-      </c>
-      <c r="H9">
-        <v>58</v>
-      </c>
-      <c r="I9">
-        <v>66</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>66</v>
-      </c>
-      <c r="L9">
-        <v>74</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -10057,26 +9999,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10086,22 +10022,22 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="G3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -10109,24 +10045,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -10135,40 +10062,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10176,40 +10103,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -10217,40 +10144,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
         <v>19</v>
       </c>
-      <c r="H8">
-        <v>14</v>
-      </c>
-      <c r="I8">
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
         <v>17</v>
       </c>
-      <c r="J8">
-        <v>22</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
       <c r="L8">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -10259,6 +10186,313 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>46</v>
+      </c>
+      <c r="C8">
+        <v>67</v>
+      </c>
+      <c r="D8">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>46</v>
+      </c>
+      <c r="F8">
+        <v>48</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>74</v>
+      </c>
+      <c r="C9">
+        <v>106</v>
+      </c>
+      <c r="D9">
+        <v>77</v>
+      </c>
+      <c r="E9">
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <v>87</v>
+      </c>
+      <c r="G9">
+        <v>62</v>
+      </c>
+      <c r="H9">
+        <v>58</v>
+      </c>
+      <c r="I9">
+        <v>66</v>
+      </c>
+      <c r="J9">
+        <v>42</v>
+      </c>
+      <c r="K9">
+        <v>66</v>
+      </c>
+      <c r="L9">
+        <v>74</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10462,7 +10696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10653,7 +10887,7 @@
         <v>11</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -10694,13 +10928,13 @@
         <v>18</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
         <v>20</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7">
         <v>15</v>
@@ -10735,13 +10969,13 @@
         <v>36</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K8">
         <v>39</v>
       </c>
       <c r="L8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M8">
         <v>24</v>
@@ -10752,7 +10986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10942,7 +11176,7 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>44</v>
@@ -10983,7 +11217,7 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F8">
         <v>101</v>
@@ -10995,7 +11229,7 @@
         <v>22</v>
       </c>
       <c r="I8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J8">
         <v>22</v>
@@ -11024,7 +11258,7 @@
         <v>77</v>
       </c>
       <c r="E9">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F9">
         <v>154</v>
@@ -11036,7 +11270,7 @@
         <v>61</v>
       </c>
       <c r="I9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J9">
         <v>53</v>
@@ -11056,7 +11290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11281,7 +11515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11480,7 +11714,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -11521,7 +11755,7 @@
         <v>15</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8">
         <v>14</v>
@@ -11537,279 +11771,6 @@
       </c>
       <c r="M8">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>12</v>
-      </c>
-      <c r="F5">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
-      <c r="K5">
-        <v>15</v>
-      </c>
-      <c r="L5">
-        <v>10</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>14</v>
-      </c>
-      <c r="D7">
-        <v>24</v>
-      </c>
-      <c r="E7">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>51</v>
-      </c>
-      <c r="G7">
-        <v>22</v>
-      </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>22</v>
-      </c>
-      <c r="K7">
-        <v>33</v>
-      </c>
-      <c r="L7">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -11882,23 +11843,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11906,32 +11873,53 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>1</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -11940,31 +11928,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11972,40 +11969,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12013,40 +12010,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -12055,6 +12052,243 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>13</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12235,7 +12469,7 @@
         <v>18</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -12276,7 +12510,7 @@
         <v>26</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -12305,7 +12539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12439,7 +12673,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -12480,7 +12714,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -12521,7 +12755,273 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>17</v>
+      </c>
+      <c r="J8">
+        <v>22</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12701,326 +13201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <v>19</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>18</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>26</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>31</v>
-      </c>
-      <c r="G8">
-        <v>16</v>
-      </c>
-      <c r="H8">
-        <v>16</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
-      <c r="L8">
-        <v>24</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>47</v>
-      </c>
-      <c r="C9">
-        <v>73</v>
-      </c>
-      <c r="D9">
-        <v>60</v>
-      </c>
-      <c r="E9">
-        <v>64</v>
-      </c>
-      <c r="F9">
-        <v>68</v>
-      </c>
-      <c r="G9">
-        <v>36</v>
-      </c>
-      <c r="H9">
-        <v>47</v>
-      </c>
-      <c r="I9">
-        <v>60</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>75</v>
-      </c>
-      <c r="L9">
-        <v>68</v>
-      </c>
-      <c r="M9">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13203,7 +13384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13385,7 +13566,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>13</v>
@@ -13394,7 +13575,7 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>17</v>
@@ -13426,7 +13607,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -13435,7 +13616,7 @@
         <v>17</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -13464,7 +13645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13686,257 +13867,6 @@
       </c>
       <c r="M6">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
-      </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
-      <c r="K8">
-        <v>17</v>
-      </c>
-      <c r="L8">
-        <v>8</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -15187,10 +15117,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15251,28 +15181,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15280,74 +15222,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
@@ -15356,84 +15271,162 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>14</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>26</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>17</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>24</v>
+      </c>
+      <c r="M8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L6">
-        <v>11</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
+      <c r="B9">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>74</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+      <c r="F9">
+        <v>68</v>
+      </c>
+      <c r="G9">
+        <v>36</v>
+      </c>
+      <c r="H9">
+        <v>49</v>
+      </c>
+      <c r="I9">
+        <v>60</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>75</v>
+      </c>
+      <c r="L9">
+        <v>68</v>
+      </c>
+      <c r="M9">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -15645,13 +15638,13 @@
         <v>7</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8">
         <v>12</v>
       </c>
       <c r="I8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8">
         <v>15</v>
@@ -15727,13 +15720,13 @@
         <v>45</v>
       </c>
       <c r="G10">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10">
         <v>41</v>
       </c>
       <c r="I10">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J10">
         <v>53</v>
@@ -16103,7 +16096,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16172,7 +16165,7 @@
         <v>14</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -16184,7 +16177,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -16213,7 +16206,7 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -16225,10 +16218,10 @@
         <v>16</v>
       </c>
       <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
         <v>9</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
       </c>
       <c r="L7">
         <v>11</v>
@@ -16418,7 +16411,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -16459,7 +16452,7 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -17143,7 +17136,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -17222,7 +17215,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -17475,7 +17468,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -17516,7 +17509,7 @@
         <v>19</v>
       </c>
       <c r="L7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -17705,7 +17698,7 @@
         <v>16</v>
       </c>
       <c r="L7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7">
         <v>3</v>
@@ -17787,7 +17780,7 @@
         <v>26</v>
       </c>
       <c r="L9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M9">
         <v>7</v>
@@ -17800,10 +17793,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17864,40 +17857,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17905,234 +17886,160 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>27</v>
-      </c>
-      <c r="D8">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>50</v>
-      </c>
-      <c r="F8">
-        <v>41</v>
-      </c>
-      <c r="G8">
-        <v>43</v>
-      </c>
-      <c r="H8">
-        <v>44</v>
-      </c>
-      <c r="I8">
-        <v>66</v>
-      </c>
-      <c r="J8">
-        <v>46</v>
-      </c>
-      <c r="K8">
-        <v>38</v>
-      </c>
-      <c r="L8">
-        <v>35</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>130</v>
-      </c>
-      <c r="C9">
-        <v>214</v>
-      </c>
-      <c r="D9">
-        <v>375</v>
-      </c>
-      <c r="E9">
-        <v>459</v>
-      </c>
-      <c r="F9">
-        <v>432</v>
-      </c>
-      <c r="G9">
-        <v>142</v>
-      </c>
-      <c r="H9">
-        <v>70</v>
-      </c>
-      <c r="I9">
-        <v>150</v>
-      </c>
-      <c r="J9">
-        <v>86</v>
-      </c>
-      <c r="K9">
-        <v>79</v>
-      </c>
-      <c r="L9">
-        <v>59</v>
-      </c>
-      <c r="M9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>166</v>
-      </c>
-      <c r="C10">
-        <v>256</v>
-      </c>
-      <c r="D10">
-        <v>433</v>
-      </c>
-      <c r="E10">
-        <v>520</v>
-      </c>
-      <c r="F10">
-        <v>487</v>
-      </c>
-      <c r="G10">
-        <v>205</v>
-      </c>
-      <c r="H10">
-        <v>132</v>
-      </c>
-      <c r="I10">
-        <v>254</v>
-      </c>
-      <c r="J10">
-        <v>176</v>
-      </c>
-      <c r="K10">
-        <v>154</v>
-      </c>
-      <c r="L10">
-        <v>134</v>
-      </c>
-      <c r="M10">
-        <v>92</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -18228,6 +18135,9 @@
       <c r="D3">
         <v>3</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>2</v>
       </c>
@@ -18318,13 +18228,13 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>20</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -18359,13 +18269,13 @@
         <v>15</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G8">
         <v>24</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -18769,7 +18679,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -18778,7 +18688,7 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -18810,7 +18720,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -18819,7 +18729,7 @@
         <v>18</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -20002,7 +19912,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -20066,40 +19976,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20107,47 +20017,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -20155,154 +20074,177 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>1</v>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>2</v>
       </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
       </c>
       <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>29</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>43</v>
+      </c>
+      <c r="H8">
+        <v>44</v>
+      </c>
+      <c r="I8">
+        <v>66</v>
+      </c>
+      <c r="J8">
+        <v>46</v>
+      </c>
+      <c r="K8">
+        <v>38</v>
+      </c>
+      <c r="L8">
+        <v>35</v>
+      </c>
+      <c r="M8">
         <v>20</v>
-      </c>
-      <c r="E8">
-        <v>41</v>
-      </c>
-      <c r="F8">
-        <v>61</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>26</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>18</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>130</v>
+      </c>
+      <c r="C9">
+        <v>215</v>
+      </c>
+      <c r="D9">
+        <v>375</v>
+      </c>
+      <c r="E9">
+        <v>463</v>
+      </c>
+      <c r="F9">
+        <v>436</v>
+      </c>
+      <c r="G9">
+        <v>142</v>
+      </c>
+      <c r="H9">
+        <v>70</v>
+      </c>
+      <c r="I9">
+        <v>150</v>
+      </c>
+      <c r="J9">
+        <v>86</v>
+      </c>
+      <c r="K9">
+        <v>80</v>
+      </c>
+      <c r="L9">
+        <v>61</v>
+      </c>
+      <c r="M9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>54</v>
-      </c>
-      <c r="C9">
-        <v>76</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>74</v>
-      </c>
-      <c r="F9">
-        <v>96</v>
-      </c>
-      <c r="G9">
-        <v>76</v>
-      </c>
-      <c r="H9">
-        <v>62</v>
-      </c>
-      <c r="I9">
-        <v>51</v>
-      </c>
-      <c r="J9">
-        <v>45</v>
-      </c>
-      <c r="K9">
-        <v>51</v>
-      </c>
-      <c r="L9">
-        <v>41</v>
-      </c>
-      <c r="M9">
-        <v>52</v>
+      <c r="B10">
+        <v>166</v>
+      </c>
+      <c r="C10">
+        <v>257</v>
+      </c>
+      <c r="D10">
+        <v>433</v>
+      </c>
+      <c r="E10">
+        <v>524</v>
+      </c>
+      <c r="F10">
+        <v>491</v>
+      </c>
+      <c r="G10">
+        <v>205</v>
+      </c>
+      <c r="H10">
+        <v>132</v>
+      </c>
+      <c r="I10">
+        <v>254</v>
+      </c>
+      <c r="J10">
+        <v>176</v>
+      </c>
+      <c r="K10">
+        <v>155</v>
+      </c>
+      <c r="L10">
+        <v>137</v>
+      </c>
+      <c r="M10">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -21911,7 +21853,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -21975,69 +21917,96 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
@@ -22046,105 +22015,145 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
         <v>7</v>
       </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
       <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>42</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>62</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>18</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
+      <c r="B9">
+        <v>54</v>
+      </c>
+      <c r="C9">
+        <v>76</v>
+      </c>
+      <c r="D9">
+        <v>43</v>
+      </c>
+      <c r="E9">
+        <v>74</v>
+      </c>
+      <c r="F9">
+        <v>97</v>
+      </c>
+      <c r="G9">
+        <v>76</v>
+      </c>
+      <c r="H9">
+        <v>64</v>
+      </c>
+      <c r="I9">
+        <v>51</v>
+      </c>
+      <c r="J9">
+        <v>46</v>
+      </c>
+      <c r="K9">
+        <v>51</v>
+      </c>
+      <c r="L9">
+        <v>41</v>
+      </c>
+      <c r="M9">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -22950,7 +22959,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -23008,7 +23017,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -23060,7 +23069,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -23087,7 +23096,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -23703,59 +23712,59 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -23764,40 +23773,34 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23805,40 +23808,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
         <v>9</v>
       </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
       <c r="L6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23846,40 +23849,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
         <v>25</v>
       </c>
-      <c r="D7">
-        <v>46</v>
-      </c>
       <c r="E7">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,31 +9,31 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
-    <sheet name="South Shore" sheetId="5" r:id="rId5"/>
-    <sheet name="Albany Park" sheetId="6" r:id="rId6"/>
-    <sheet name="Old Town" sheetId="7" r:id="rId7"/>
-    <sheet name="Loop" sheetId="8" r:id="rId8"/>
-    <sheet name="Lincoln Park" sheetId="9" r:id="rId9"/>
-    <sheet name="O'Hare" sheetId="10" r:id="rId10"/>
-    <sheet name="Near South Side" sheetId="11" r:id="rId11"/>
-    <sheet name="Logan Square" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
-    <sheet name="Austin" sheetId="14" r:id="rId14"/>
-    <sheet name="Avondale" sheetId="15" r:id="rId15"/>
-    <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
-    <sheet name="Chatham" sheetId="17" r:id="rId17"/>
-    <sheet name="Oakland" sheetId="18" r:id="rId18"/>
-    <sheet name="River North" sheetId="19" r:id="rId19"/>
-    <sheet name="New City" sheetId="20" r:id="rId20"/>
-    <sheet name="Belmont Cragin" sheetId="21" r:id="rId21"/>
-    <sheet name="Woodlawn" sheetId="22" r:id="rId22"/>
-    <sheet name="West Loop" sheetId="23" r:id="rId23"/>
-    <sheet name="Printers Row" sheetId="24" r:id="rId24"/>
-    <sheet name="Uptown" sheetId="25" r:id="rId25"/>
-    <sheet name="Lake View" sheetId="26" r:id="rId26"/>
-    <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
+    <sheet name="Albany Park" sheetId="3" r:id="rId3"/>
+    <sheet name="Woodlawn" sheetId="4" r:id="rId4"/>
+    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
+    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
+    <sheet name="Roseland" sheetId="7" r:id="rId7"/>
+    <sheet name="South Shore" sheetId="8" r:id="rId8"/>
+    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
+    <sheet name="Loop" sheetId="10" r:id="rId10"/>
+    <sheet name="Lincoln Park" sheetId="11" r:id="rId11"/>
+    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
+    <sheet name="Near South Side" sheetId="13" r:id="rId13"/>
+    <sheet name="Logan Square" sheetId="14" r:id="rId14"/>
+    <sheet name="Grand Crossing" sheetId="15" r:id="rId15"/>
+    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="Avondale" sheetId="17" r:id="rId17"/>
+    <sheet name="Rush &amp; Division" sheetId="18" r:id="rId18"/>
+    <sheet name="Chatham" sheetId="19" r:id="rId19"/>
+    <sheet name="Oakland" sheetId="20" r:id="rId20"/>
+    <sheet name="River North" sheetId="21" r:id="rId21"/>
+    <sheet name="New City" sheetId="22" r:id="rId22"/>
+    <sheet name="Belmont Cragin" sheetId="23" r:id="rId23"/>
+    <sheet name="West Loop" sheetId="24" r:id="rId24"/>
+    <sheet name="Printers Row" sheetId="25" r:id="rId25"/>
+    <sheet name="Uptown" sheetId="26" r:id="rId26"/>
+    <sheet name="Lake View" sheetId="27" r:id="rId27"/>
     <sheet name="Hyde Park" sheetId="28" r:id="rId28"/>
     <sheet name="Grand Boulevard" sheetId="29" r:id="rId29"/>
     <sheet name="West Town" sheetId="30" r:id="rId30"/>
@@ -872,13 +872,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>50</v>
       </c>
       <c r="D2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2">
         <v>51</v>
@@ -887,25 +887,25 @@
         <v>65</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L2">
         <v>105</v>
       </c>
       <c r="M2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -916,7 +916,7 @@
         <v>61</v>
       </c>
       <c r="C3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>99</v>
@@ -925,7 +925,7 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3">
         <v>94</v>
@@ -934,13 +934,13 @@
         <v>99</v>
       </c>
       <c r="I3">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J3">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K3">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L3">
         <v>179</v>
@@ -1030,7 +1030,7 @@
         <v>16</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>17</v>
@@ -1117,40 +1117,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C9">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D9">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E9">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F9">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G9">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H9">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="I9">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J9">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K9">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L9">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M9">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1158,37 +1158,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C10">
-        <v>1144</v>
+        <v>1156</v>
       </c>
       <c r="D10">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="E10">
-        <v>1614</v>
+        <v>1620</v>
       </c>
       <c r="F10">
-        <v>1644</v>
+        <v>1650</v>
       </c>
       <c r="G10">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="H10">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I10">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="J10">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K10">
         <v>533</v>
       </c>
       <c r="L10">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="M10">
         <v>367</v>
@@ -1199,40 +1199,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="C11">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="D11">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="E11">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="F11">
-        <v>2207</v>
+        <v>2215</v>
       </c>
       <c r="G11">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="H11">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="I11">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="J11">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="K11">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="L11">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="M11">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -1242,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1305,23 +1305,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
       <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -1331,132 +1346,235 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
       </c>
       <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>31</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>45</v>
+      </c>
+      <c r="H8">
+        <v>46</v>
+      </c>
+      <c r="I8">
+        <v>67</v>
+      </c>
+      <c r="J8">
+        <v>46</v>
+      </c>
+      <c r="K8">
+        <v>38</v>
+      </c>
+      <c r="L8">
+        <v>35</v>
+      </c>
+      <c r="M8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>130</v>
+      </c>
+      <c r="C9">
+        <v>220</v>
+      </c>
+      <c r="D9">
+        <v>376</v>
+      </c>
+      <c r="E9">
+        <v>465</v>
+      </c>
+      <c r="F9">
+        <v>441</v>
+      </c>
+      <c r="G9">
+        <v>142</v>
+      </c>
+      <c r="H9">
+        <v>70</v>
+      </c>
+      <c r="I9">
+        <v>151</v>
+      </c>
+      <c r="J9">
+        <v>86</v>
+      </c>
+      <c r="K9">
+        <v>80</v>
+      </c>
+      <c r="L9">
+        <v>62</v>
+      </c>
+      <c r="M9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>33</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>16</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
+      <c r="B10">
+        <v>166</v>
+      </c>
+      <c r="C10">
+        <v>262</v>
+      </c>
+      <c r="D10">
+        <v>435</v>
+      </c>
+      <c r="E10">
+        <v>526</v>
+      </c>
+      <c r="F10">
+        <v>496</v>
+      </c>
+      <c r="G10">
+        <v>207</v>
+      </c>
+      <c r="H10">
+        <v>134</v>
+      </c>
+      <c r="I10">
+        <v>257</v>
+      </c>
+      <c r="J10">
+        <v>176</v>
+      </c>
+      <c r="K10">
+        <v>155</v>
+      </c>
+      <c r="L10">
+        <v>138</v>
+      </c>
+      <c r="M10">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1466,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1529,19 +1647,16 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>2</v>
       </c>
     </row>
@@ -1549,17 +1664,14 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>3</v>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1567,147 +1679,127 @@
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="M3">
-        <v>1</v>
+      <c r="L3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
       <c r="D6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
         <v>14</v>
       </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
       <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
         <v>6</v>
       </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
         <v>7</v>
       </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
       <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>20</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
-      </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
-      <c r="K8">
-        <v>17</v>
-      </c>
-      <c r="L8">
-        <v>9</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1780,26 +1872,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1809,92 +1901,47 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
       <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1902,40 +1949,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
         <v>6</v>
       </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
       <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
         <v>8</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1943,40 +1990,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
         <v>21</v>
       </c>
-      <c r="D8">
-        <v>26</v>
-      </c>
       <c r="E8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G8">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>15</v>
       </c>
       <c r="L8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1985,6 +2032,526 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>17</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>22</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2180,7 +2747,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -2251,7 +2818,7 @@
         <v>28</v>
       </c>
       <c r="L8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8">
         <v>11</v>
@@ -2262,7 +2829,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9">
         <v>75</v>
@@ -2292,7 +2859,7 @@
         <v>76</v>
       </c>
       <c r="L9">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M9">
         <v>40</v>
@@ -2303,7 +2870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2387,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>3</v>
@@ -2499,7 +3066,7 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>24</v>
@@ -2508,13 +3075,13 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I7">
         <v>16</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7">
         <v>18</v>
@@ -2543,7 +3110,7 @@
         <v>41</v>
       </c>
       <c r="F8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>52</v>
@@ -2561,7 +3128,7 @@
         <v>18</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M8">
         <v>16</v>
@@ -2581,28 +3148,28 @@
         <v>44</v>
       </c>
       <c r="E9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F9">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G9">
         <v>76</v>
       </c>
       <c r="H9">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I9">
         <v>51</v>
       </c>
       <c r="J9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K9">
         <v>52</v>
       </c>
       <c r="L9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M9">
         <v>52</v>
@@ -2613,7 +3180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2856,7 +3423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3105,7 +3672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3393,399 +3960,6 @@
       </c>
       <c r="M9">
         <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>36</v>
-      </c>
-      <c r="C6">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>52</v>
-      </c>
-      <c r="E6">
-        <v>61</v>
-      </c>
-      <c r="F6">
-        <v>67</v>
-      </c>
-      <c r="G6">
-        <v>17</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>18</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>39</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>62</v>
-      </c>
-      <c r="E7">
-        <v>65</v>
-      </c>
-      <c r="F7">
-        <v>77</v>
-      </c>
-      <c r="G7">
-        <v>30</v>
-      </c>
-      <c r="H7">
-        <v>15</v>
-      </c>
-      <c r="I7">
-        <v>33</v>
-      </c>
-      <c r="J7">
-        <v>29</v>
-      </c>
-      <c r="K7">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3865,7 +4039,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -3892,7 +4066,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3982,7 +4156,7 @@
         <v>23</v>
       </c>
       <c r="K5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5">
         <v>27</v>
@@ -4008,7 +4182,7 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -4087,28 +4261,28 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F8">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G8">
         <v>76</v>
       </c>
       <c r="H8">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I8">
         <v>51</v>
       </c>
       <c r="J8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K8">
         <v>52</v>
       </c>
       <c r="L8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8">
         <v>52</v>
@@ -4134,7 +4308,7 @@
         <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>3</v>
@@ -4347,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <v>2</v>
@@ -4434,7 +4608,7 @@
         <v>3</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -4504,7 +4678,7 @@
         <v>20</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20">
         <v>16</v>
@@ -4755,7 +4929,7 @@
         <v>21</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27">
         <v>15</v>
@@ -4787,10 +4961,10 @@
         <v>74</v>
       </c>
       <c r="C28">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D28">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E28">
         <v>70</v>
@@ -4893,7 +5067,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L30">
         <v>12</v>
@@ -4942,19 +5116,19 @@
         <v>77</v>
       </c>
       <c r="E32">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F32">
         <v>154</v>
       </c>
       <c r="G32">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H32">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I32">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J32">
         <v>53</v>
@@ -5067,7 +5241,7 @@
         <v>46</v>
       </c>
       <c r="B36">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C36">
         <v>75</v>
@@ -5097,7 +5271,7 @@
         <v>76</v>
       </c>
       <c r="L36">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M36">
         <v>40</v>
@@ -5155,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="E38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F38">
         <v>8</v>
@@ -5236,7 +5410,7 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D41">
         <v>17</v>
@@ -5257,7 +5431,7 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K41">
         <v>13</v>
@@ -5295,7 +5469,7 @@
         <v>7</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42">
         <v>12</v>
@@ -5318,7 +5492,7 @@
         <v>9</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43">
         <v>18</v>
@@ -5470,10 +5644,10 @@
         <v>57</v>
       </c>
       <c r="B47">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C47">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D47">
         <v>41</v>
@@ -5500,7 +5674,7 @@
         <v>29</v>
       </c>
       <c r="L47">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M47">
         <v>25</v>
@@ -5567,7 +5741,7 @@
         <v>7</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -5596,7 +5770,7 @@
         <v>22</v>
       </c>
       <c r="C50">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D50">
         <v>24</v>
@@ -5620,10 +5794,10 @@
         <v>24</v>
       </c>
       <c r="K50">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L50">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M50">
         <v>18</v>
@@ -5640,7 +5814,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -5719,25 +5893,25 @@
         <v>166</v>
       </c>
       <c r="C53">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D53">
         <v>435</v>
       </c>
       <c r="E53">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F53">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G53">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H53">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I53">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J53">
         <v>176</v>
@@ -5746,7 +5920,7 @@
         <v>155</v>
       </c>
       <c r="L53">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M53">
         <v>93</v>
@@ -5781,7 +5955,7 @@
         <v>8</v>
       </c>
       <c r="J54">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K54">
         <v>7</v>
@@ -5990,7 +6164,7 @@
         <v>46</v>
       </c>
       <c r="F61">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G61">
         <v>19</v>
@@ -6049,7 +6223,7 @@
         <v>17</v>
       </c>
       <c r="L62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M62">
         <v>12</v>
@@ -6060,13 +6234,13 @@
         <v>73</v>
       </c>
       <c r="B63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C63">
         <v>8</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E63">
         <v>10</v>
@@ -6145,7 +6319,7 @@
         <v>41</v>
       </c>
       <c r="D65">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E65">
         <v>33</v>
@@ -6160,7 +6334,7 @@
         <v>17</v>
       </c>
       <c r="I65">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J65">
         <v>10</v>
@@ -6172,7 +6346,7 @@
         <v>16</v>
       </c>
       <c r="M65">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6224,7 +6398,7 @@
         <v>10</v>
       </c>
       <c r="C67">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D67">
         <v>7</v>
@@ -6274,7 +6448,7 @@
         <v>19</v>
       </c>
       <c r="F68">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -6341,10 +6515,10 @@
         <v>38</v>
       </c>
       <c r="E70">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F70">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G70">
         <v>34</v>
@@ -6484,7 +6658,7 @@
         <v>62</v>
       </c>
       <c r="E74">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F74">
         <v>77</v>
@@ -6560,13 +6734,13 @@
         <v>43</v>
       </c>
       <c r="E76">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F76">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G76">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H76">
         <v>31</v>
@@ -6610,7 +6784,7 @@
         <v>40</v>
       </c>
       <c r="H77">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I77">
         <v>64</v>
@@ -6753,7 +6927,7 @@
         <v>8</v>
       </c>
       <c r="K81">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L81">
         <v>15</v>
@@ -6770,7 +6944,7 @@
         <v>4</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -6808,7 +6982,7 @@
         <v>22</v>
       </c>
       <c r="C83">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D83">
         <v>15</v>
@@ -6925,7 +7099,7 @@
         <v>13</v>
       </c>
       <c r="E86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F86">
         <v>22</v>
@@ -6957,7 +7131,7 @@
         <v>97</v>
       </c>
       <c r="B87">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C87">
         <v>33</v>
@@ -6981,7 +7155,7 @@
         <v>18</v>
       </c>
       <c r="J87">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K87">
         <v>23</v>
@@ -7001,7 +7175,7 @@
         <v>6</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D88">
         <v>10</v>
@@ -7270,7 +7444,7 @@
         <v>11</v>
       </c>
       <c r="C95">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D95">
         <v>40</v>
@@ -7288,10 +7462,10 @@
         <v>12</v>
       </c>
       <c r="I95">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J95">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K95">
         <v>21</v>
@@ -7382,7 +7556,7 @@
         <v>4</v>
       </c>
       <c r="M97">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7431,40 +7605,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="C99">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="D99">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="E99">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="F99">
-        <v>2207</v>
+        <v>2215</v>
       </c>
       <c r="G99">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="H99">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="I99">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="J99">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="K99">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="L99">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="M99">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -7574,7 +7748,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -7586,201 +7760,113 @@
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
       <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
         <v>2</v>
       </c>
     </row>
@@ -7790,197 +7876,6 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8045,19 +7940,31 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -8065,45 +7972,42 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -8112,40 +8016,40 @@
         <v>8</v>
       </c>
       <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="C5">
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8153,40 +8057,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>36</v>
+      </c>
+      <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>52</v>
+      </c>
+      <c r="E6">
+        <v>62</v>
+      </c>
+      <c r="F6">
+        <v>67</v>
+      </c>
+      <c r="G6">
+        <v>17</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
       <c r="K6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8194,40 +8098,260 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D7">
+        <v>62</v>
+      </c>
+      <c r="E7">
+        <v>66</v>
+      </c>
+      <c r="F7">
+        <v>77</v>
+      </c>
+      <c r="G7">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>33</v>
+      </c>
+      <c r="J7">
+        <v>29</v>
+      </c>
+      <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
         <v>19</v>
       </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>18</v>
-      </c>
-      <c r="G7">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H7">
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
         <v>7</v>
       </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
+      <c r="E6">
         <v>10</v>
       </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -8236,6 +8360,197 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8512,7 +8827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8729,7 +9044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8794,6 +9109,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>3</v>
       </c>
@@ -8813,7 +9131,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -8974,7 +9292,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>33</v>
@@ -8998,7 +9316,7 @@
         <v>18</v>
       </c>
       <c r="J9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9">
         <v>23</v>
@@ -9008,302 +9326,6 @@
       </c>
       <c r="M9">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>35</v>
-      </c>
-      <c r="C7">
-        <v>36</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>42</v>
-      </c>
-      <c r="F7">
-        <v>43</v>
-      </c>
-      <c r="G7">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>13</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>37</v>
-      </c>
-      <c r="C8">
-        <v>56</v>
-      </c>
-      <c r="D8">
-        <v>41</v>
-      </c>
-      <c r="E8">
-        <v>53</v>
-      </c>
-      <c r="F8">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>47</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>41</v>
-      </c>
-      <c r="J8">
-        <v>30</v>
-      </c>
-      <c r="K8">
-        <v>29</v>
-      </c>
-      <c r="L8">
-        <v>30</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -9376,41 +9398,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9418,47 +9437,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -9466,49 +9485,61 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="H5">
         <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
+      <c r="I6">
         <v>16</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>14</v>
-      </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9516,40 +9547,40 @@
         <v>9</v>
       </c>
       <c r="B7">
+        <v>37</v>
+      </c>
+      <c r="C7">
+        <v>37</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>43</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
         <v>14</v>
       </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
-      <c r="G7">
-        <v>22</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
       <c r="M7">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9557,40 +9588,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C8">
+        <v>57</v>
+      </c>
+      <c r="D8">
         <v>41</v>
       </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
       <c r="E8">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F8">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K8">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -9681,7 +9712,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -9798,7 +9829,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -10069,7 +10100,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10133,34 +10164,25 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10168,205 +10190,147 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
         <v>7</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>46</v>
-      </c>
-      <c r="C8">
-        <v>68</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>46</v>
-      </c>
-      <c r="F8">
-        <v>48</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>22</v>
-      </c>
-      <c r="I8">
-        <v>31</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>74</v>
-      </c>
-      <c r="C9">
-        <v>107</v>
-      </c>
-      <c r="D9">
-        <v>77</v>
-      </c>
-      <c r="E9">
-        <v>70</v>
-      </c>
-      <c r="F9">
-        <v>87</v>
-      </c>
-      <c r="G9">
-        <v>63</v>
-      </c>
-      <c r="H9">
-        <v>59</v>
-      </c>
-      <c r="I9">
-        <v>67</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>66</v>
-      </c>
-      <c r="L9">
-        <v>74</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -10527,7 +10491,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -10550,7 +10514,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>29</v>
@@ -10571,7 +10535,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>13</v>
@@ -10591,7 +10555,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -10609,10 +10573,10 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>21</v>
@@ -11016,7 +10980,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -11057,7 +11021,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -11720,7 +11684,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -11796,7 +11760,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -11906,7 +11870,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -12004,7 +11968,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -12045,10 +12009,10 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>23</v>
@@ -12086,13 +12050,13 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F8">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H8">
         <v>31</v>
@@ -12320,7 +12284,7 @@
         <v>31</v>
       </c>
       <c r="I7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7">
         <v>21</v>
@@ -12349,19 +12313,19 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F8">
         <v>101</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8">
         <v>22</v>
@@ -12390,19 +12354,19 @@
         <v>77</v>
       </c>
       <c r="E9">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F9">
         <v>154</v>
       </c>
       <c r="G9">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I9">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J9">
         <v>53</v>
@@ -12615,7 +12579,7 @@
         <v>15</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -12656,7 +12620,7 @@
         <v>21</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>15</v>
@@ -12821,7 +12785,7 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -12865,7 +12829,7 @@
         <v>15</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -12879,7 +12843,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>14</v>
@@ -12920,7 +12884,7 @@
         <v>22</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>24</v>
@@ -12944,10 +12908,10 @@
         <v>24</v>
       </c>
       <c r="K7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M7">
         <v>18</v>
@@ -12960,7 +12924,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13026,37 +12990,16 @@
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -13065,204 +13008,168 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
       <c r="J7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
         <v>14</v>
       </c>
-      <c r="C8">
-        <v>12</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8">
-        <v>22</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>36</v>
-      </c>
-      <c r="C9">
-        <v>34</v>
-      </c>
-      <c r="D9">
-        <v>27</v>
-      </c>
-      <c r="E9">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <v>33</v>
-      </c>
-      <c r="G9">
-        <v>23</v>
-      </c>
-      <c r="H9">
-        <v>20</v>
-      </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
-      <c r="J9">
-        <v>28</v>
-      </c>
-      <c r="K9">
-        <v>29</v>
-      </c>
-      <c r="L9">
-        <v>14</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>56</v>
-      </c>
-      <c r="C10">
-        <v>53</v>
-      </c>
-      <c r="D10">
-        <v>39</v>
-      </c>
-      <c r="E10">
-        <v>54</v>
-      </c>
-      <c r="F10">
-        <v>46</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>41</v>
-      </c>
-      <c r="I10">
-        <v>64</v>
-      </c>
-      <c r="J10">
-        <v>54</v>
-      </c>
-      <c r="K10">
-        <v>50</v>
-      </c>
-      <c r="L10">
-        <v>34</v>
-      </c>
-      <c r="M10">
-        <v>26</v>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -13371,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -13507,7 +13414,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8">
         <v>12</v>
@@ -13829,6 +13736,9 @@
       <c r="F4">
         <v>1</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
       </c>
@@ -13894,7 +13804,7 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -14262,7 +14172,7 @@
         <v>4</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>4</v>
@@ -14282,7 +14192,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>13</v>
@@ -14323,7 +14233,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -14344,7 +14254,7 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7">
         <v>13</v>
@@ -14458,6 +14368,9 @@
       <c r="I3">
         <v>3</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>1</v>
       </c>
@@ -14573,7 +14486,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -15363,7 +15276,7 @@
         <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -15404,7 +15317,7 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -15432,10 +15345,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15496,28 +15409,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15525,34 +15450,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
         <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -15560,125 +15485,144 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>14</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
       <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="L6">
-        <v>11</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>53</v>
+      </c>
+      <c r="G8">
+        <v>38</v>
+      </c>
+      <c r="H8">
+        <v>17</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>21</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -16522,7 +16466,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -16563,7 +16507,7 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>16</v>
@@ -16803,7 +16747,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -16895,7 +16839,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -17036,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -17100,7 +17044,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -17210,7 +17154,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -17359,7 +17303,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>15</v>
@@ -17489,7 +17433,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -17623,7 +17567,7 @@
         <v>23</v>
       </c>
       <c r="K7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7">
         <v>27</v>
@@ -17910,7 +17854,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17973,23 +17917,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17997,147 +17953,205 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
         <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
         <v>7</v>
       </c>
       <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
+      <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
+      <c r="B8">
+        <v>46</v>
+      </c>
+      <c r="C8">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>46</v>
+      </c>
+      <c r="F8">
+        <v>48</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>22</v>
+      </c>
+      <c r="I8">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
         <v>9</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>13</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>74</v>
+      </c>
+      <c r="C9">
+        <v>109</v>
+      </c>
+      <c r="D9">
+        <v>78</v>
+      </c>
+      <c r="E9">
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <v>87</v>
+      </c>
+      <c r="G9">
+        <v>63</v>
+      </c>
+      <c r="H9">
+        <v>59</v>
+      </c>
+      <c r="I9">
+        <v>67</v>
+      </c>
+      <c r="J9">
+        <v>42</v>
+      </c>
+      <c r="K9">
+        <v>66</v>
+      </c>
+      <c r="L9">
+        <v>74</v>
+      </c>
+      <c r="M9">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -18780,7 +18794,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>13</v>
@@ -18821,7 +18835,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>18</v>
@@ -19025,7 +19039,7 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -19107,7 +19121,7 @@
         <v>13</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
         <v>22</v>
@@ -19693,7 +19707,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -19731,7 +19745,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -20013,10 +20027,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -20076,17 +20090,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -20095,6 +20121,9 @@
         <v>2</v>
       </c>
       <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -20103,162 +20132,204 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>13</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>31</v>
-      </c>
-      <c r="E6">
-        <v>41</v>
-      </c>
-      <c r="F6">
-        <v>73</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>22</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>34</v>
+      </c>
+      <c r="D9">
+        <v>27</v>
+      </c>
+      <c r="E9">
+        <v>33</v>
+      </c>
+      <c r="F9">
+        <v>33</v>
+      </c>
+      <c r="G9">
+        <v>23</v>
+      </c>
+      <c r="H9">
+        <v>22</v>
+      </c>
+      <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
+        <v>28</v>
+      </c>
+      <c r="K9">
+        <v>29</v>
+      </c>
+      <c r="L9">
+        <v>14</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>38</v>
-      </c>
-      <c r="E7">
-        <v>51</v>
-      </c>
-      <c r="F7">
-        <v>91</v>
-      </c>
-      <c r="G7">
+      <c r="B10">
+        <v>56</v>
+      </c>
+      <c r="C10">
+        <v>53</v>
+      </c>
+      <c r="D10">
+        <v>39</v>
+      </c>
+      <c r="E10">
+        <v>54</v>
+      </c>
+      <c r="F10">
+        <v>46</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>43</v>
+      </c>
+      <c r="I10">
+        <v>64</v>
+      </c>
+      <c r="J10">
+        <v>54</v>
+      </c>
+      <c r="K10">
+        <v>50</v>
+      </c>
+      <c r="L10">
         <v>34</v>
       </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>27</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>23</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+      <c r="M10">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -21072,7 +21143,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -21107,7 +21178,7 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -21870,10 +21941,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -21934,40 +22005,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21975,234 +22034,160 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>27</v>
-      </c>
-      <c r="D8">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>50</v>
-      </c>
-      <c r="F8">
-        <v>41</v>
-      </c>
-      <c r="G8">
-        <v>44</v>
-      </c>
-      <c r="H8">
-        <v>44</v>
-      </c>
-      <c r="I8">
-        <v>67</v>
-      </c>
-      <c r="J8">
-        <v>46</v>
-      </c>
-      <c r="K8">
-        <v>38</v>
-      </c>
-      <c r="L8">
-        <v>35</v>
-      </c>
-      <c r="M8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>130</v>
-      </c>
-      <c r="C9">
-        <v>218</v>
-      </c>
-      <c r="D9">
-        <v>376</v>
-      </c>
-      <c r="E9">
-        <v>464</v>
-      </c>
-      <c r="F9">
-        <v>440</v>
-      </c>
-      <c r="G9">
-        <v>142</v>
-      </c>
-      <c r="H9">
-        <v>70</v>
-      </c>
-      <c r="I9">
-        <v>151</v>
-      </c>
-      <c r="J9">
-        <v>86</v>
-      </c>
-      <c r="K9">
-        <v>80</v>
-      </c>
-      <c r="L9">
-        <v>61</v>
-      </c>
-      <c r="M9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>166</v>
-      </c>
-      <c r="C10">
-        <v>260</v>
-      </c>
-      <c r="D10">
-        <v>435</v>
-      </c>
-      <c r="E10">
-        <v>525</v>
-      </c>
-      <c r="F10">
-        <v>495</v>
-      </c>
-      <c r="G10">
-        <v>206</v>
-      </c>
-      <c r="H10">
-        <v>132</v>
-      </c>
-      <c r="I10">
-        <v>256</v>
-      </c>
-      <c r="J10">
-        <v>176</v>
-      </c>
-      <c r="K10">
-        <v>155</v>
-      </c>
-      <c r="L10">
-        <v>137</v>
-      </c>
-      <c r="M10">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -22688,6 +22673,9 @@
       <c r="G5">
         <v>4</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
       <c r="K5">
         <v>1</v>
       </c>
@@ -22753,7 +22741,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -23053,6 +23041,9 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>3</v>
       </c>
@@ -23127,7 +23118,7 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -23701,7 +23692,7 @@
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -23762,24 +23753,42 @@
         <v>1</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -23787,11 +23796,14 @@
       <c r="H3">
         <v>2</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -23799,7 +23811,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -23809,32 +23821,38 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23842,37 +23860,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>42</v>
+      </c>
+      <c r="F6">
+        <v>73</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
         <v>9</v>
       </c>
-      <c r="C6">
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
+      <c r="K6">
         <v>6</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
       <c r="L6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23880,40 +23901,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,20 +9,20 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Albany Park" sheetId="3" r:id="rId3"/>
-    <sheet name="Woodlawn" sheetId="4" r:id="rId4"/>
+    <sheet name="Austin" sheetId="3" r:id="rId3"/>
+    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
     <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
-    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
-    <sheet name="Roseland" sheetId="7" r:id="rId7"/>
-    <sheet name="South Shore" sheetId="8" r:id="rId8"/>
-    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Loop" sheetId="10" r:id="rId10"/>
-    <sheet name="Lincoln Park" sheetId="11" r:id="rId11"/>
-    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
-    <sheet name="Near South Side" sheetId="13" r:id="rId13"/>
-    <sheet name="Logan Square" sheetId="14" r:id="rId14"/>
-    <sheet name="Grand Crossing" sheetId="15" r:id="rId15"/>
-    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="Albany Park" sheetId="6" r:id="rId6"/>
+    <sheet name="Woodlawn" sheetId="7" r:id="rId7"/>
+    <sheet name="Englewood" sheetId="8" r:id="rId8"/>
+    <sheet name="South Shore" sheetId="9" r:id="rId9"/>
+    <sheet name="Old Town" sheetId="10" r:id="rId10"/>
+    <sheet name="Loop" sheetId="11" r:id="rId11"/>
+    <sheet name="Lincoln Park" sheetId="12" r:id="rId12"/>
+    <sheet name="O'Hare" sheetId="13" r:id="rId13"/>
+    <sheet name="Near South Side" sheetId="14" r:id="rId14"/>
+    <sheet name="Logan Square" sheetId="15" r:id="rId15"/>
+    <sheet name="Grand Crossing" sheetId="16" r:id="rId16"/>
     <sheet name="Avondale" sheetId="17" r:id="rId17"/>
     <sheet name="Rush &amp; Division" sheetId="18" r:id="rId18"/>
     <sheet name="Chatham" sheetId="19" r:id="rId19"/>
@@ -881,7 +881,7 @@
         <v>70</v>
       </c>
       <c r="E2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2">
         <v>65</v>
@@ -896,7 +896,7 @@
         <v>89</v>
       </c>
       <c r="J2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K2">
         <v>105</v>
@@ -919,7 +919,7 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -928,25 +928,25 @@
         <v>96</v>
       </c>
       <c r="G3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I3">
         <v>151</v>
       </c>
       <c r="J3">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K3">
         <v>168</v>
       </c>
       <c r="L3">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M3">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1018,7 +1018,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>11</v>
@@ -1036,7 +1036,7 @@
         <v>17</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1117,10 +1117,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C9">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D9">
         <v>311</v>
@@ -1135,19 +1135,19 @@
         <v>362</v>
       </c>
       <c r="H9">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I9">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J9">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K9">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L9">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M9">
         <v>194</v>
@@ -1158,40 +1158,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="C10">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="D10">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="E10">
-        <v>1620</v>
+        <v>1626</v>
       </c>
       <c r="F10">
-        <v>1650</v>
+        <v>1659</v>
       </c>
       <c r="G10">
         <v>777</v>
       </c>
       <c r="H10">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I10">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="J10">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K10">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L10">
         <v>496</v>
       </c>
       <c r="M10">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1199,40 +1199,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="C11">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="D11">
-        <v>1792</v>
+        <v>1800</v>
       </c>
       <c r="E11">
-        <v>2107</v>
+        <v>2114</v>
       </c>
       <c r="F11">
-        <v>2215</v>
+        <v>2224</v>
       </c>
       <c r="G11">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="H11">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="I11">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="J11">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="K11">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="L11">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="M11">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -1241,6 +1241,261 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>42</v>
+      </c>
+      <c r="F6">
+        <v>73</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>38</v>
+      </c>
+      <c r="E7">
+        <v>52</v>
+      </c>
+      <c r="F7">
+        <v>92</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>23</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1365,7 +1620,7 @@
         <v>14</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>25</v>
@@ -1377,7 +1632,7 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3">
         <v>17</v>
@@ -1486,7 +1741,7 @@
         <v>46</v>
       </c>
       <c r="K8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -1503,31 +1758,31 @@
         <v>130</v>
       </c>
       <c r="C9">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D9">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E9">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F9">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="G9">
         <v>142</v>
       </c>
       <c r="H9">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J9">
         <v>86</v>
       </c>
       <c r="K9">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L9">
         <v>62</v>
@@ -1544,34 +1799,34 @@
         <v>166</v>
       </c>
       <c r="C10">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D10">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E10">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F10">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G10">
         <v>207</v>
       </c>
       <c r="H10">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I10">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J10">
         <v>176</v>
       </c>
       <c r="K10">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L10">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M10">
         <v>93</v>
@@ -1582,7 +1837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1746,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -1787,7 +2042,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -1800,230 +2055,6 @@
       </c>
       <c r="M7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>32</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>34</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>16</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2096,17 +2127,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
       <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -2119,30 +2156,21 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -2150,49 +2178,25 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
       <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2200,19 +2204,19 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -2221,19 +2225,19 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
         <v>9</v>
       </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2241,40 +2245,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
         <v>19</v>
       </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
       <c r="F8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
         <v>7</v>
       </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
       <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
         <v>17</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2347,26 +2351,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2376,22 +2374,22 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="G3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -2399,27 +2397,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -2428,16 +2414,16 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -2446,22 +2432,22 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2469,40 +2455,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2510,40 +2496,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
         <v>17</v>
       </c>
-      <c r="G8">
-        <v>19</v>
-      </c>
-      <c r="H8">
-        <v>14</v>
-      </c>
-      <c r="I8">
-        <v>18</v>
-      </c>
-      <c r="J8">
-        <v>22</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
       <c r="L8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2553,7 +2539,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2616,127 +2602,118 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -2744,125 +2721,84 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>18</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
         <v>11</v>
       </c>
-      <c r="H7">
-        <v>20</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>18</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
       <c r="M7">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
         <v>26</v>
       </c>
-      <c r="C8">
-        <v>45</v>
-      </c>
-      <c r="D8">
-        <v>34</v>
-      </c>
       <c r="E8">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
         <v>18</v>
       </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
       <c r="J8">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K8">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>48</v>
-      </c>
-      <c r="C9">
-        <v>75</v>
-      </c>
-      <c r="D9">
-        <v>61</v>
-      </c>
-      <c r="E9">
-        <v>68</v>
-      </c>
-      <c r="F9">
-        <v>68</v>
-      </c>
-      <c r="G9">
-        <v>36</v>
-      </c>
-      <c r="H9">
-        <v>50</v>
-      </c>
-      <c r="I9">
-        <v>60</v>
-      </c>
-      <c r="J9">
-        <v>41</v>
-      </c>
-      <c r="K9">
-        <v>76</v>
-      </c>
-      <c r="L9">
-        <v>71</v>
-      </c>
-      <c r="M9">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2936,40 +2872,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
         <v>6</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2977,40 +2913,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
         <v>6</v>
       </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
       <c r="H3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>10</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3020,25 +2956,22 @@
       <c r="I4">
         <v>1</v>
       </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3046,9 +2979,21 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
       </c>
       <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -3057,40 +3002,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>25</v>
       </c>
       <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
         <v>15</v>
       </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>18</v>
       </c>
-      <c r="H7">
-        <v>35</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>16</v>
-      </c>
       <c r="K7">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3098,40 +3043,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C8">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G8">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I8">
         <v>28</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L8">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3139,40 +3084,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C9">
+        <v>75</v>
+      </c>
+      <c r="D9">
+        <v>61</v>
+      </c>
+      <c r="E9">
+        <v>68</v>
+      </c>
+      <c r="F9">
+        <v>68</v>
+      </c>
+      <c r="G9">
+        <v>37</v>
+      </c>
+      <c r="H9">
+        <v>50</v>
+      </c>
+      <c r="I9">
+        <v>60</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
         <v>76</v>
       </c>
-      <c r="D9">
-        <v>44</v>
-      </c>
-      <c r="E9">
-        <v>75</v>
-      </c>
-      <c r="F9">
-        <v>99</v>
-      </c>
-      <c r="G9">
-        <v>76</v>
-      </c>
-      <c r="H9">
+      <c r="L9">
         <v>71</v>
       </c>
-      <c r="I9">
-        <v>51</v>
-      </c>
-      <c r="J9">
-        <v>47</v>
-      </c>
-      <c r="K9">
-        <v>52</v>
-      </c>
-      <c r="L9">
-        <v>42</v>
-      </c>
       <c r="M9">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3596,7 +3541,7 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>34</v>
@@ -3637,7 +3582,7 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7">
         <v>38</v>
@@ -3759,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>5</v>
@@ -3906,7 +3851,7 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8">
         <v>12</v>
@@ -3947,10 +3892,10 @@
         <v>18</v>
       </c>
       <c r="I9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K9">
         <v>40</v>
@@ -4214,7 +4159,7 @@
         <v>37</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -4261,7 +4206,7 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8">
         <v>99</v>
@@ -4270,7 +4215,7 @@
         <v>76</v>
       </c>
       <c r="H8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I8">
         <v>51</v>
@@ -4285,7 +4230,7 @@
         <v>42</v>
       </c>
       <c r="M8">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4655,10 +4600,10 @@
         <v>18</v>
       </c>
       <c r="I19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19">
         <v>40</v>
@@ -4766,7 +4711,7 @@
         <v>13</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F22">
         <v>3</v>
@@ -4798,7 +4743,7 @@
         <v>33</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23">
         <v>15</v>
@@ -4926,7 +4871,7 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27">
         <v>21</v>
@@ -4958,13 +4903,13 @@
         <v>38</v>
       </c>
       <c r="B28">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C28">
         <v>109</v>
       </c>
       <c r="D28">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E28">
         <v>70</v>
@@ -4979,7 +4924,7 @@
         <v>59</v>
       </c>
       <c r="I28">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J28">
         <v>42</v>
@@ -5064,7 +5009,7 @@
         <v>7</v>
       </c>
       <c r="J30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>15</v>
@@ -5119,7 +5064,7 @@
         <v>101</v>
       </c>
       <c r="F32">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G32">
         <v>89</v>
@@ -5134,10 +5079,10 @@
         <v>53</v>
       </c>
       <c r="K32">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L32">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M32">
         <v>46</v>
@@ -5241,7 +5186,7 @@
         <v>46</v>
       </c>
       <c r="B36">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36">
         <v>75</v>
@@ -5256,7 +5201,7 @@
         <v>68</v>
       </c>
       <c r="G36">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H36">
         <v>50</v>
@@ -5419,7 +5364,7 @@
         <v>18</v>
       </c>
       <c r="F41">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G41">
         <v>22</v>
@@ -5644,13 +5589,13 @@
         <v>57</v>
       </c>
       <c r="B47">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C47">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D47">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E47">
         <v>53</v>
@@ -5706,7 +5651,7 @@
         <v>4</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J48">
         <v>10</v>
@@ -5785,7 +5730,7 @@
         <v>22</v>
       </c>
       <c r="H50">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I50">
         <v>16</v>
@@ -5893,34 +5838,34 @@
         <v>166</v>
       </c>
       <c r="C53">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D53">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E53">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F53">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G53">
         <v>207</v>
       </c>
       <c r="H53">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I53">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J53">
         <v>176</v>
       </c>
       <c r="K53">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L53">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M53">
         <v>93</v>
@@ -6193,7 +6138,7 @@
         <v>72</v>
       </c>
       <c r="B62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C62">
         <v>18</v>
@@ -6211,7 +6156,7 @@
         <v>10</v>
       </c>
       <c r="H62">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I62">
         <v>19</v>
@@ -6343,10 +6288,10 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M65">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6655,7 +6600,7 @@
         <v>29</v>
       </c>
       <c r="D74">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E74">
         <v>66</v>
@@ -6673,7 +6618,7 @@
         <v>33</v>
       </c>
       <c r="J74">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K74">
         <v>27</v>
@@ -6769,7 +6714,7 @@
         <v>56</v>
       </c>
       <c r="C77">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D77">
         <v>39</v>
@@ -6781,7 +6726,7 @@
         <v>46</v>
       </c>
       <c r="G77">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H77">
         <v>43</v>
@@ -6796,10 +6741,10 @@
         <v>50</v>
       </c>
       <c r="L77">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M77">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6813,7 +6758,7 @@
         <v>25</v>
       </c>
       <c r="D78">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E78">
         <v>38</v>
@@ -6865,7 +6810,7 @@
         <v>20</v>
       </c>
       <c r="D80">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E80">
         <v>27</v>
@@ -6982,7 +6927,7 @@
         <v>22</v>
       </c>
       <c r="C83">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D83">
         <v>15</v>
@@ -7079,7 +7024,7 @@
         <v>3</v>
       </c>
       <c r="L85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M85">
         <v>4</v>
@@ -7131,7 +7076,7 @@
         <v>97</v>
       </c>
       <c r="B87">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C87">
         <v>33</v>
@@ -7140,7 +7085,7 @@
         <v>16</v>
       </c>
       <c r="E87">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F87">
         <v>23</v>
@@ -7149,7 +7094,7 @@
         <v>33</v>
       </c>
       <c r="H87">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I87">
         <v>18</v>
@@ -7240,7 +7185,7 @@
         <v>9</v>
       </c>
       <c r="K89">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L89">
         <v>7</v>
@@ -7465,7 +7410,7 @@
         <v>17</v>
       </c>
       <c r="J95">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K95">
         <v>21</v>
@@ -7494,7 +7439,7 @@
         <v>26</v>
       </c>
       <c r="F96">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G96">
         <v>7</v>
@@ -7573,7 +7518,7 @@
         <v>6</v>
       </c>
       <c r="E98">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F98">
         <v>7</v>
@@ -7605,40 +7550,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="C99">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="D99">
-        <v>1792</v>
+        <v>1800</v>
       </c>
       <c r="E99">
-        <v>2107</v>
+        <v>2114</v>
       </c>
       <c r="F99">
-        <v>2215</v>
+        <v>2224</v>
       </c>
       <c r="G99">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="H99">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="I99">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="J99">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="K99">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="L99">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="M99">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -7988,7 +7933,7 @@
         <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -8063,7 +8008,7 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6">
         <v>62</v>
@@ -8104,7 +8049,7 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7">
         <v>66</v>
@@ -8122,7 +8067,7 @@
         <v>33</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7">
         <v>27</v>
@@ -9228,7 +9173,7 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>4</v>
@@ -9251,7 +9196,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8">
         <v>22</v>
@@ -9260,7 +9205,7 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8">
         <v>15</v>
@@ -9292,7 +9237,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>33</v>
@@ -9301,7 +9246,7 @@
         <v>16</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>23</v>
@@ -9310,7 +9255,7 @@
         <v>33</v>
       </c>
       <c r="H9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9">
         <v>18</v>
@@ -9547,13 +9492,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>42</v>
@@ -9588,13 +9533,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>53</v>
@@ -10100,7 +10045,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10163,26 +10108,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10190,62 +10150,68 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="J5">
         <v>3</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -10253,84 +10219,133 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
       <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>36</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>18</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>42</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>64</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>9</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>13</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
+      <c r="B9">
+        <v>54</v>
+      </c>
+      <c r="C9">
+        <v>76</v>
+      </c>
+      <c r="D9">
+        <v>44</v>
+      </c>
+      <c r="E9">
+        <v>76</v>
+      </c>
+      <c r="F9">
+        <v>99</v>
+      </c>
+      <c r="G9">
+        <v>76</v>
+      </c>
+      <c r="H9">
+        <v>72</v>
+      </c>
+      <c r="I9">
+        <v>51</v>
+      </c>
+      <c r="J9">
+        <v>47</v>
+      </c>
+      <c r="K9">
+        <v>52</v>
+      </c>
+      <c r="L9">
+        <v>42</v>
+      </c>
+      <c r="M9">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -10535,7 +10550,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>13</v>
@@ -10576,7 +10591,7 @@
         <v>17</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>21</v>
@@ -10718,7 +10733,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -10791,7 +10806,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>15</v>
@@ -11259,7 +11274,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -11300,7 +11315,7 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -12290,10 +12305,10 @@
         <v>21</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -12316,7 +12331,7 @@
         <v>61</v>
       </c>
       <c r="F8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G8">
         <v>46</v>
@@ -12357,7 +12372,7 @@
         <v>101</v>
       </c>
       <c r="F9">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G9">
         <v>89</v>
@@ -12372,10 +12387,10 @@
         <v>53</v>
       </c>
       <c r="K9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M9">
         <v>46</v>
@@ -12576,7 +12591,7 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>13</v>
@@ -12617,7 +12632,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -12817,7 +12832,7 @@
         <v>13</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -12899,7 +12914,7 @@
         <v>22</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7">
         <v>16</v>
@@ -12924,7 +12939,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12990,16 +13005,37 @@
       <c r="B2">
         <v>2</v>
       </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
       </c>
       <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -13008,168 +13044,207 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
-      </c>
-      <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>22</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>27</v>
+      </c>
+      <c r="E9">
+        <v>33</v>
+      </c>
+      <c r="F9">
+        <v>33</v>
+      </c>
+      <c r="G9">
+        <v>23</v>
+      </c>
+      <c r="H9">
+        <v>22</v>
+      </c>
+      <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
+        <v>28</v>
+      </c>
+      <c r="K9">
+        <v>29</v>
+      </c>
+      <c r="L9">
+        <v>14</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>23</v>
-      </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>9</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
+      <c r="B10">
+        <v>56</v>
+      </c>
+      <c r="C10">
+        <v>54</v>
+      </c>
+      <c r="D10">
+        <v>39</v>
+      </c>
+      <c r="E10">
+        <v>54</v>
+      </c>
+      <c r="F10">
+        <v>46</v>
+      </c>
+      <c r="G10">
+        <v>41</v>
+      </c>
+      <c r="H10">
+        <v>43</v>
+      </c>
+      <c r="I10">
+        <v>64</v>
+      </c>
+      <c r="J10">
+        <v>54</v>
+      </c>
+      <c r="K10">
+        <v>50</v>
+      </c>
+      <c r="L10">
+        <v>35</v>
+      </c>
+      <c r="M10">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -13329,7 +13404,7 @@
         <v>2</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -13411,7 +13486,7 @@
         <v>7</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>15</v>
@@ -13574,7 +13649,7 @@
         <v>22</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -13615,7 +13690,7 @@
         <v>26</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -14201,7 +14276,7 @@
         <v>14</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>17</v>
@@ -14242,7 +14317,7 @@
         <v>18</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -14848,7 +14923,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>24</v>
@@ -14889,7 +14964,7 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>27</v>
@@ -15477,7 +15552,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -15581,7 +15656,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -15619,10 +15694,10 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -15965,7 +16040,7 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -16006,7 +16081,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -16176,7 +16251,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -16258,7 +16333,7 @@
         <v>37</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -17854,7 +17929,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17918,34 +17993,25 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17953,205 +18019,147 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
         <v>7</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>46</v>
-      </c>
-      <c r="C8">
-        <v>70</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>46</v>
-      </c>
-      <c r="F8">
-        <v>48</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>22</v>
-      </c>
-      <c r="I8">
-        <v>31</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>74</v>
-      </c>
-      <c r="C9">
-        <v>109</v>
-      </c>
-      <c r="D9">
-        <v>78</v>
-      </c>
-      <c r="E9">
-        <v>70</v>
-      </c>
-      <c r="F9">
-        <v>87</v>
-      </c>
-      <c r="G9">
-        <v>63</v>
-      </c>
-      <c r="H9">
-        <v>59</v>
-      </c>
-      <c r="I9">
-        <v>67</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>66</v>
-      </c>
-      <c r="L9">
-        <v>74</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -20027,7 +20035,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -20093,37 +20101,16 @@
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -20132,204 +20119,168 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
       <c r="J7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
         <v>14</v>
       </c>
-      <c r="C8">
-        <v>12</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8">
-        <v>22</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>36</v>
-      </c>
-      <c r="C9">
-        <v>34</v>
-      </c>
-      <c r="D9">
-        <v>27</v>
-      </c>
-      <c r="E9">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <v>33</v>
-      </c>
-      <c r="G9">
-        <v>23</v>
-      </c>
-      <c r="H9">
-        <v>22</v>
-      </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
-      <c r="J9">
-        <v>28</v>
-      </c>
-      <c r="K9">
-        <v>29</v>
-      </c>
-      <c r="L9">
-        <v>14</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>56</v>
-      </c>
-      <c r="C10">
-        <v>53</v>
-      </c>
-      <c r="D10">
-        <v>39</v>
-      </c>
-      <c r="E10">
-        <v>54</v>
-      </c>
-      <c r="F10">
-        <v>46</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>43</v>
-      </c>
-      <c r="I10">
-        <v>64</v>
-      </c>
-      <c r="J10">
-        <v>54</v>
-      </c>
-      <c r="K10">
-        <v>50</v>
-      </c>
-      <c r="L10">
-        <v>34</v>
-      </c>
-      <c r="M10">
-        <v>26</v>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -21857,6 +21808,9 @@
       <c r="I3">
         <v>1</v>
       </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
@@ -21928,7 +21882,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -21941,10 +21895,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -22004,29 +21958,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22037,69 +21997,51 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -22110,84 +22052,147 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>14</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>46</v>
+      </c>
+      <c r="F8">
+        <v>48</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
+      <c r="I8">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
         <v>22</v>
       </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L6">
-        <v>11</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
+      <c r="B9">
+        <v>75</v>
+      </c>
+      <c r="C9">
+        <v>109</v>
+      </c>
+      <c r="D9">
+        <v>79</v>
+      </c>
+      <c r="E9">
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <v>87</v>
+      </c>
+      <c r="G9">
+        <v>63</v>
+      </c>
+      <c r="H9">
+        <v>59</v>
+      </c>
+      <c r="I9">
+        <v>68</v>
+      </c>
+      <c r="J9">
+        <v>42</v>
+      </c>
+      <c r="K9">
+        <v>66</v>
+      </c>
+      <c r="L9">
+        <v>74</v>
+      </c>
+      <c r="M9">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -22482,7 +22487,7 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -22523,7 +22528,7 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -23689,7 +23694,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -23752,26 +23757,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23779,162 +23787,160 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>6</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
       <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>38</v>
-      </c>
-      <c r="E7">
-        <v>52</v>
-      </c>
-      <c r="F7">
-        <v>92</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>27</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>23</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,28 +9,28 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Uptown" sheetId="3" r:id="rId3"/>
-    <sheet name="Riverdale" sheetId="4" r:id="rId4"/>
-    <sheet name="Fuller Park" sheetId="5" r:id="rId5"/>
-    <sheet name="North Lawndale" sheetId="6" r:id="rId6"/>
-    <sheet name="Little Village" sheetId="7" r:id="rId7"/>
-    <sheet name="Chatham" sheetId="8" r:id="rId8"/>
-    <sheet name="West Loop" sheetId="9" r:id="rId9"/>
-    <sheet name="Auburn Gresham" sheetId="10" r:id="rId10"/>
-    <sheet name="Lake View" sheetId="11" r:id="rId11"/>
-    <sheet name="Humboldt Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Austin" sheetId="13" r:id="rId13"/>
-    <sheet name="Roseland" sheetId="14" r:id="rId14"/>
-    <sheet name="Albany Park" sheetId="15" r:id="rId15"/>
-    <sheet name="Woodlawn" sheetId="16" r:id="rId16"/>
-    <sheet name="Englewood" sheetId="17" r:id="rId17"/>
-    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
-    <sheet name="Old Town" sheetId="19" r:id="rId19"/>
-    <sheet name="Loop" sheetId="20" r:id="rId20"/>
-    <sheet name="Lincoln Park" sheetId="21" r:id="rId21"/>
-    <sheet name="O'Hare" sheetId="22" r:id="rId22"/>
-    <sheet name="Near South Side" sheetId="23" r:id="rId23"/>
-    <sheet name="Logan Square" sheetId="24" r:id="rId24"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Uptown" sheetId="4" r:id="rId4"/>
+    <sheet name="Loop" sheetId="5" r:id="rId5"/>
+    <sheet name="Logan Square" sheetId="6" r:id="rId6"/>
+    <sheet name="Riverdale" sheetId="7" r:id="rId7"/>
+    <sheet name="Fuller Park" sheetId="8" r:id="rId8"/>
+    <sheet name="North Lawndale" sheetId="9" r:id="rId9"/>
+    <sheet name="Little Village" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="West Loop" sheetId="12" r:id="rId12"/>
+    <sheet name="Auburn Gresham" sheetId="13" r:id="rId13"/>
+    <sheet name="Lake View" sheetId="14" r:id="rId14"/>
+    <sheet name="Humboldt Park" sheetId="15" r:id="rId15"/>
+    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="Roseland" sheetId="17" r:id="rId17"/>
+    <sheet name="Albany Park" sheetId="18" r:id="rId18"/>
+    <sheet name="Woodlawn" sheetId="19" r:id="rId19"/>
+    <sheet name="South Shore" sheetId="20" r:id="rId20"/>
+    <sheet name="Old Town" sheetId="21" r:id="rId21"/>
+    <sheet name="Lincoln Park" sheetId="22" r:id="rId22"/>
+    <sheet name="O'Hare" sheetId="23" r:id="rId23"/>
+    <sheet name="Near South Side" sheetId="24" r:id="rId24"/>
     <sheet name="Grand Crossing" sheetId="25" r:id="rId25"/>
     <sheet name="Avondale" sheetId="26" r:id="rId26"/>
     <sheet name="Rush &amp; Division" sheetId="27" r:id="rId27"/>
@@ -884,7 +884,7 @@
         <v>52</v>
       </c>
       <c r="F2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>66</v>
@@ -899,13 +899,13 @@
         <v>88</v>
       </c>
       <c r="K2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L2">
         <v>105</v>
       </c>
       <c r="M2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -928,22 +928,22 @@
         <v>99</v>
       </c>
       <c r="G3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H3">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J3">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K3">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="M3">
         <v>155</v>
@@ -1117,40 +1117,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C9">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D9">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E9">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F9">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G9">
         <v>367</v>
       </c>
       <c r="H9">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I9">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J9">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K9">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L9">
         <v>354</v>
       </c>
       <c r="M9">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1158,40 +1158,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C10">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D10">
-        <v>1332</v>
+        <v>1343</v>
       </c>
       <c r="E10">
-        <v>1650</v>
+        <v>1655</v>
       </c>
       <c r="F10">
-        <v>1683</v>
+        <v>1687</v>
       </c>
       <c r="G10">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="H10">
         <v>431</v>
       </c>
       <c r="I10">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="J10">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K10">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L10">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M10">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1199,40 +1199,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="C11">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="D11">
-        <v>1828</v>
+        <v>1841</v>
       </c>
       <c r="E11">
-        <v>2146</v>
+        <v>2152</v>
       </c>
       <c r="F11">
-        <v>2258</v>
+        <v>2264</v>
       </c>
       <c r="G11">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="H11">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="I11">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="J11">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="K11">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="L11">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="M11">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -1308,28 +1308,13 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -1338,35 +1323,23 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -1375,40 +1348,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1416,40 +1377,37 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="L6">
         <v>6</v>
       </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1457,40 +1415,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1499,6 +1457,836 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>13</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>24</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
+      <c r="K8">
+        <v>16</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>42</v>
+      </c>
+      <c r="D9">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>39</v>
+      </c>
+      <c r="F9">
+        <v>42</v>
+      </c>
+      <c r="G9">
+        <v>31</v>
+      </c>
+      <c r="H9">
+        <v>18</v>
+      </c>
+      <c r="I9">
+        <v>27</v>
+      </c>
+      <c r="J9">
+        <v>32</v>
+      </c>
+      <c r="K9">
+        <v>40</v>
+      </c>
+      <c r="L9">
+        <v>30</v>
+      </c>
+      <c r="M9">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>17</v>
+      </c>
+      <c r="J8">
+        <v>16</v>
+      </c>
+      <c r="K8">
+        <v>11</v>
+      </c>
+      <c r="L8">
+        <v>9</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>23</v>
+      </c>
+      <c r="F9">
+        <v>42</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>26</v>
+      </c>
+      <c r="J9">
+        <v>19</v>
+      </c>
+      <c r="K9">
+        <v>22</v>
+      </c>
+      <c r="L9">
+        <v>19</v>
+      </c>
+      <c r="M9">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>38</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>26</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1739,7 +2527,7 @@
         <v>21</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>14</v>
@@ -1780,7 +2568,7 @@
         <v>30</v>
       </c>
       <c r="K8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L8">
         <v>31</v>
@@ -1794,7 +2582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1997,7 +2785,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -2038,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7">
         <v>13</v>
@@ -2055,7 +2843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2148,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -2192,7 +2980,7 @@
         <v>10</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3">
         <v>11</v>
@@ -2251,7 +3039,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>24</v>
@@ -2304,7 +3092,7 @@
         <v>28</v>
       </c>
       <c r="I8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J8">
         <v>16</v>
@@ -2333,7 +3121,7 @@
         <v>45</v>
       </c>
       <c r="E9">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -2345,16 +3133,16 @@
         <v>76</v>
       </c>
       <c r="I9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J9">
         <v>50</v>
       </c>
       <c r="K9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M9">
         <v>53</v>
@@ -2365,7 +3153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2598,7 +3386,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9">
         <v>35</v>
@@ -2639,7 +3427,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>55</v>
@@ -2680,7 +3468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2920,7 +3708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3018,7 +3806,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -3055,7 +3843,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -3076,7 +3864,7 @@
         <v>4</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -3137,7 +3925,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -3149,7 +3937,7 @@
         <v>18</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -3158,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3168,824 +3956,6 @@
       </c>
       <c r="M7">
         <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>14</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>15</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>30</v>
-      </c>
-      <c r="G7">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>22</v>
-      </c>
-      <c r="I7">
-        <v>17</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>28</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>48</v>
-      </c>
-      <c r="C8">
-        <v>71</v>
-      </c>
-      <c r="D8">
-        <v>45</v>
-      </c>
-      <c r="E8">
-        <v>46</v>
-      </c>
-      <c r="F8">
-        <v>49</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>24</v>
-      </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>77</v>
-      </c>
-      <c r="C9">
-        <v>110</v>
-      </c>
-      <c r="D9">
-        <v>81</v>
-      </c>
-      <c r="E9">
-        <v>71</v>
-      </c>
-      <c r="F9">
-        <v>90</v>
-      </c>
-      <c r="G9">
-        <v>64</v>
-      </c>
-      <c r="H9">
-        <v>62</v>
-      </c>
-      <c r="I9">
-        <v>70</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>68</v>
-      </c>
-      <c r="L9">
-        <v>74</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>28</v>
-      </c>
-      <c r="D6">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>15</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>11</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>14</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>31</v>
-      </c>
-      <c r="E6">
-        <v>42</v>
-      </c>
-      <c r="F6">
-        <v>73</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>38</v>
-      </c>
-      <c r="E7">
-        <v>53</v>
-      </c>
-      <c r="F7">
-        <v>93</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>27</v>
-      </c>
-      <c r="J7">
-        <v>17</v>
-      </c>
-      <c r="K7">
-        <v>24</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4176,7 +4146,7 @@
         <v>14</v>
       </c>
       <c r="I5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5">
         <v>23</v>
@@ -4217,10 +4187,10 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -4287,7 +4257,7 @@
         <v>45</v>
       </c>
       <c r="E8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -4299,16 +4269,16 @@
         <v>76</v>
       </c>
       <c r="I8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J8">
         <v>50</v>
       </c>
       <c r="K8">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8">
         <v>53</v>
@@ -4369,7 +4339,7 @@
         <v>16</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -4666,13 +4636,13 @@
         <v>42</v>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E19">
         <v>39</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G19">
         <v>31</v>
@@ -4701,7 +4671,7 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20">
         <v>14</v>
@@ -4996,13 +4966,13 @@
         <v>81</v>
       </c>
       <c r="E28">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F28">
         <v>90</v>
       </c>
       <c r="G28">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H28">
         <v>62</v>
@@ -5017,10 +4987,10 @@
         <v>68</v>
       </c>
       <c r="L28">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M28">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -5090,7 +5060,7 @@
         <v>3</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>9</v>
@@ -5145,7 +5115,7 @@
         <v>78</v>
       </c>
       <c r="E32">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F32">
         <v>156</v>
@@ -5160,7 +5130,7 @@
         <v>78</v>
       </c>
       <c r="J32">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K32">
         <v>64</v>
@@ -5466,7 +5436,7 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K41">
         <v>13</v>
@@ -5600,7 +5570,7 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D45">
         <v>14</v>
@@ -5609,7 +5579,7 @@
         <v>16</v>
       </c>
       <c r="F45">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G45">
         <v>25</v>
@@ -5706,7 +5676,7 @@
         <v>30</v>
       </c>
       <c r="K47">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L47">
         <v>31</v>
@@ -5802,7 +5772,7 @@
         <v>60</v>
       </c>
       <c r="B50">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C50">
         <v>17</v>
@@ -5870,7 +5840,7 @@
         <v>3</v>
       </c>
       <c r="K51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51">
         <v>8</v>
@@ -5890,7 +5860,7 @@
         <v>24</v>
       </c>
       <c r="D52">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E52">
         <v>24</v>
@@ -5917,7 +5887,7 @@
         <v>20</v>
       </c>
       <c r="M52">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -5928,37 +5898,37 @@
         <v>167</v>
       </c>
       <c r="C53">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D53">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E53">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F53">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G53">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H53">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I53">
         <v>264</v>
       </c>
       <c r="J53">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K53">
         <v>162</v>
       </c>
       <c r="L53">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M53">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6144,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -6196,7 +6166,7 @@
         <v>18</v>
       </c>
       <c r="E61">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F61">
         <v>36</v>
@@ -6249,7 +6219,7 @@
         <v>8</v>
       </c>
       <c r="I62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J62">
         <v>11</v>
@@ -6541,7 +6511,7 @@
         <v>80</v>
       </c>
       <c r="B70">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C70">
         <v>26</v>
@@ -6568,7 +6538,7 @@
         <v>17</v>
       </c>
       <c r="K70">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L70">
         <v>12</v>
@@ -6641,7 +6611,7 @@
         <v>4</v>
       </c>
       <c r="I72">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J72">
         <v>7</v>
@@ -6690,19 +6660,19 @@
         <v>30</v>
       </c>
       <c r="D74">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E74">
         <v>67</v>
       </c>
       <c r="F74">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G74">
         <v>30</v>
       </c>
       <c r="H74">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I74">
         <v>33</v>
@@ -6763,7 +6733,7 @@
         <v>86</v>
       </c>
       <c r="B76">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C76">
         <v>57</v>
@@ -6772,7 +6742,7 @@
         <v>44</v>
       </c>
       <c r="E76">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F76">
         <v>49</v>
@@ -6804,7 +6774,7 @@
         <v>87</v>
       </c>
       <c r="B77">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C77">
         <v>55</v>
@@ -6927,7 +6897,7 @@
         <v>9</v>
       </c>
       <c r="L80">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M80">
         <v>9</v>
@@ -7023,7 +6993,7 @@
         <v>28</v>
       </c>
       <c r="D83">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E83">
         <v>16</v>
@@ -7128,7 +7098,7 @@
         <v>96</v>
       </c>
       <c r="B86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C86">
         <v>18</v>
@@ -7175,7 +7145,7 @@
         <v>33</v>
       </c>
       <c r="D87">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E87">
         <v>27</v>
@@ -7202,7 +7172,7 @@
         <v>23</v>
       </c>
       <c r="M87">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -7377,7 +7347,7 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H92">
         <v>17</v>
@@ -7392,7 +7362,7 @@
         <v>22</v>
       </c>
       <c r="L92">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M92">
         <v>18</v>
@@ -7526,7 +7496,7 @@
         <v>13</v>
       </c>
       <c r="C96">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D96">
         <v>23</v>
@@ -7541,7 +7511,7 @@
         <v>7</v>
       </c>
       <c r="H96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I96">
         <v>13</v>
@@ -7567,7 +7537,7 @@
         <v>23</v>
       </c>
       <c r="C97">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D97">
         <v>19</v>
@@ -7579,7 +7549,7 @@
         <v>18</v>
       </c>
       <c r="G97">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H97">
         <v>7</v>
@@ -7588,7 +7558,7 @@
         <v>16</v>
       </c>
       <c r="J97">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K97">
         <v>10</v>
@@ -7617,7 +7587,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G98">
         <v>7</v>
@@ -7646,40 +7616,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="C99">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="D99">
-        <v>1828</v>
+        <v>1841</v>
       </c>
       <c r="E99">
-        <v>2146</v>
+        <v>2152</v>
       </c>
       <c r="F99">
-        <v>2258</v>
+        <v>2264</v>
       </c>
       <c r="G99">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="H99">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="I99">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="J99">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="K99">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="L99">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="M99">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -7789,10 +7759,10 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -7853,40 +7823,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7894,237 +7852,160 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>28</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>27</v>
-      </c>
-      <c r="D8">
-        <v>34</v>
-      </c>
-      <c r="E8">
-        <v>51</v>
-      </c>
-      <c r="F8">
-        <v>43</v>
-      </c>
-      <c r="G8">
-        <v>46</v>
-      </c>
-      <c r="H8">
-        <v>47</v>
-      </c>
-      <c r="I8">
-        <v>68</v>
-      </c>
-      <c r="J8">
-        <v>47</v>
-      </c>
-      <c r="K8">
-        <v>40</v>
-      </c>
-      <c r="L8">
-        <v>36</v>
-      </c>
-      <c r="M8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>131</v>
-      </c>
-      <c r="C9">
-        <v>226</v>
-      </c>
-      <c r="D9">
-        <v>382</v>
-      </c>
-      <c r="E9">
-        <v>476</v>
-      </c>
-      <c r="F9">
-        <v>453</v>
-      </c>
-      <c r="G9">
-        <v>142</v>
-      </c>
-      <c r="H9">
-        <v>72</v>
-      </c>
-      <c r="I9">
-        <v>157</v>
-      </c>
-      <c r="J9">
-        <v>88</v>
-      </c>
-      <c r="K9">
-        <v>83</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>167</v>
-      </c>
-      <c r="C10">
-        <v>268</v>
-      </c>
-      <c r="D10">
-        <v>442</v>
-      </c>
-      <c r="E10">
-        <v>538</v>
-      </c>
-      <c r="F10">
-        <v>511</v>
-      </c>
-      <c r="G10">
-        <v>208</v>
-      </c>
-      <c r="H10">
-        <v>140</v>
-      </c>
-      <c r="I10">
-        <v>264</v>
-      </c>
-      <c r="J10">
-        <v>179</v>
-      </c>
-      <c r="K10">
-        <v>162</v>
-      </c>
-      <c r="L10">
-        <v>144</v>
-      </c>
-      <c r="M10">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -8133,6 +8014,261 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>42</v>
+      </c>
+      <c r="F6">
+        <v>73</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>38</v>
+      </c>
+      <c r="E7">
+        <v>53</v>
+      </c>
+      <c r="F7">
+        <v>93</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>17</v>
+      </c>
+      <c r="K7">
+        <v>26</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8350,233 +8486,6 @@
       </c>
       <c r="M7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>33</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>35</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>16</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8649,17 +8558,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
       <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -8672,30 +8587,24 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -8703,49 +8612,25 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
       <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8753,40 +8638,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
         <v>6</v>
       </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
       <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
         <v>9</v>
       </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -8794,40 +8679,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
         <v>21</v>
       </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-      <c r="D8">
+      <c r="E8">
         <v>19</v>
       </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
       <c r="F8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
         <v>8</v>
       </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
       <c r="K8">
+        <v>16</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
         <v>17</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -8900,26 +8785,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8929,22 +8808,22 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="G3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -8952,27 +8831,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -8981,16 +8848,16 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -8999,22 +8866,22 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9022,40 +8889,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
         <v>17</v>
       </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
       <c r="E7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>9</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9063,40 +8930,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
         <v>17</v>
       </c>
-      <c r="G8">
-        <v>19</v>
-      </c>
-      <c r="H8">
-        <v>14</v>
-      </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>23</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
       <c r="L8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -9596,7 +9463,7 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -9637,7 +9504,7 @@
         <v>16</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -10151,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -10232,13 +10099,13 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>63</v>
       </c>
       <c r="F6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>17</v>
@@ -10273,19 +10140,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7">
         <v>67</v>
       </c>
       <c r="F7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7">
         <v>30</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7">
         <v>33</v>
@@ -10373,73 +10240,73 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
       <c r="G2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -10447,17 +10314,32 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -10465,7 +10347,10 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -10474,40 +10359,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -10515,40 +10400,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C8">
+        <v>71</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>47</v>
+      </c>
+      <c r="F8">
+        <v>49</v>
+      </c>
+      <c r="G8">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
         <v>22</v>
       </c>
-      <c r="D8">
-        <v>13</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>13</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
+      <c r="L8">
+        <v>23</v>
+      </c>
+      <c r="M8">
         <v>9</v>
-      </c>
-      <c r="L8">
-        <v>13</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -10556,40 +10441,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="G9">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="I9">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J9">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="L9">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -11167,7 +11052,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -11205,7 +11090,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -12781,10 +12666,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -12796,9 +12681,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12821,119 +12707,245 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="B8">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>13</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>27</v>
+      </c>
+      <c r="F9">
+        <v>23</v>
+      </c>
+      <c r="G9">
+        <v>33</v>
+      </c>
+      <c r="H9">
+        <v>23</v>
+      </c>
+      <c r="I9">
+        <v>18</v>
+      </c>
+      <c r="J9">
+        <v>22</v>
+      </c>
+      <c r="K9">
+        <v>23</v>
+      </c>
+      <c r="L9">
+        <v>23</v>
+      </c>
+      <c r="M9">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -13312,7 +13324,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -13362,7 +13374,7 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>34</v>
@@ -13394,7 +13406,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>57</v>
@@ -13403,7 +13415,7 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8">
         <v>49</v>
@@ -13666,7 +13678,7 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F8">
         <v>103</v>
@@ -13681,7 +13693,7 @@
         <v>41</v>
       </c>
       <c r="J8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8">
         <v>25</v>
@@ -13707,7 +13719,7 @@
         <v>78</v>
       </c>
       <c r="E9">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9">
         <v>156</v>
@@ -13722,7 +13734,7 @@
         <v>78</v>
       </c>
       <c r="J9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9">
         <v>64</v>
@@ -14193,7 +14205,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -14234,7 +14246,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -14424,7 +14436,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -14506,7 +14518,7 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -14640,7 +14652,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -14663,7 +14675,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>22</v>
@@ -14704,7 +14716,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>23</v>
@@ -14719,7 +14731,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>13</v>
@@ -15342,10 +15354,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15405,23 +15417,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15429,184 +15459,237 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>9</v>
-      </c>
-      <c r="G7">
         <v>7</v>
       </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
       <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>131</v>
+      </c>
+      <c r="C9">
+        <v>227</v>
+      </c>
+      <c r="D9">
+        <v>387</v>
+      </c>
+      <c r="E9">
+        <v>477</v>
+      </c>
+      <c r="F9">
+        <v>454</v>
+      </c>
+      <c r="G9">
+        <v>143</v>
+      </c>
+      <c r="H9">
+        <v>72</v>
+      </c>
+      <c r="I9">
+        <v>157</v>
+      </c>
+      <c r="J9">
+        <v>88</v>
+      </c>
+      <c r="K9">
+        <v>83</v>
+      </c>
+      <c r="L9">
+        <v>67</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>13</v>
-      </c>
-      <c r="D9">
-        <v>23</v>
-      </c>
-      <c r="E9">
-        <v>19</v>
-      </c>
-      <c r="F9">
-        <v>23</v>
-      </c>
-      <c r="G9">
-        <v>11</v>
-      </c>
-      <c r="H9">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <v>12</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>21</v>
-      </c>
-      <c r="L9">
-        <v>30</v>
-      </c>
-      <c r="M9">
-        <v>12</v>
+      <c r="B10">
+        <v>167</v>
+      </c>
+      <c r="C10">
+        <v>269</v>
+      </c>
+      <c r="D10">
+        <v>448</v>
+      </c>
+      <c r="E10">
+        <v>539</v>
+      </c>
+      <c r="F10">
+        <v>512</v>
+      </c>
+      <c r="G10">
+        <v>209</v>
+      </c>
+      <c r="H10">
+        <v>141</v>
+      </c>
+      <c r="I10">
+        <v>264</v>
+      </c>
+      <c r="J10">
+        <v>180</v>
+      </c>
+      <c r="K10">
+        <v>162</v>
+      </c>
+      <c r="L10">
+        <v>145</v>
+      </c>
+      <c r="M10">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -15893,7 +15976,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -16027,7 +16110,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -16706,7 +16789,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -16839,7 +16922,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -17003,7 +17086,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -17076,7 +17159,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -17723,40 +17806,25 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
         <v>3</v>
       </c>
     </row>
@@ -17764,56 +17832,53 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>1</v>
       </c>
     </row>
@@ -17822,40 +17887,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17863,40 +17928,40 @@
         <v>9</v>
       </c>
       <c r="B7">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
         <v>14</v>
       </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>26</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
       <c r="G7">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
         <v>9</v>
       </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
       <c r="L7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -17904,40 +17969,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>24</v>
+      </c>
+      <c r="D8">
         <v>27</v>
       </c>
-      <c r="C8">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
       <c r="E8">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G8">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I8">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J8">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K8">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -18304,6 +18369,9 @@
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="J3">
         <v>1</v>
       </c>
@@ -18436,7 +18504,7 @@
         <v>14</v>
       </c>
       <c r="I7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7">
         <v>23</v>
@@ -18899,7 +18967,7 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -18908,7 +18976,7 @@
         <v>15</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>20</v>
@@ -18940,7 +19008,7 @@
         <v>20</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>14</v>
@@ -18949,7 +19017,7 @@
         <v>16</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8">
         <v>25</v>
@@ -19604,7 +19672,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -19686,7 +19754,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>18</v>
@@ -20155,10 +20223,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -20170,10 +20238,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20196,172 +20263,119 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>6</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -21962,20 +21976,8 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -21983,17 +21985,14 @@
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
       <c r="K2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22001,34 +22000,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -22038,7 +22037,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -22046,10 +22045,7 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
@@ -22057,11 +22053,8 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
+      <c r="H6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22069,40 +22062,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7">
         <v>7</v>
       </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
       <c r="H7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -22110,40 +22103,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
         <v>9</v>
       </c>
-      <c r="I8">
-        <v>11</v>
-      </c>
-      <c r="J8">
-        <v>13</v>
-      </c>
       <c r="K8">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22151,40 +22144,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E9">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H9">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J9">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L9">
         <v>30</v>
       </c>
       <c r="M9">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -22279,7 +22272,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -22319,7 +22312,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -23343,6 +23336,9 @@
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="J3">
         <v>1</v>
       </c>
@@ -23370,7 +23366,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -23446,10 +23442,10 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -23882,7 +23878,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23951,23 +23947,35 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23977,179 +23985,177 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>2</v>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>4</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>17</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
         <v>14</v>
-      </c>
-      <c r="D8">
-        <v>26</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>35</v>
-      </c>
-      <c r="G8">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8">
-        <v>17</v>
-      </c>
-      <c r="J8">
-        <v>16</v>
-      </c>
-      <c r="K8">
-        <v>11</v>
-      </c>
-      <c r="L8">
-        <v>9</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>18</v>
-      </c>
-      <c r="C9">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>23</v>
-      </c>
-      <c r="F9">
-        <v>42</v>
-      </c>
-      <c r="G9">
-        <v>24</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>26</v>
-      </c>
-      <c r="J9">
-        <v>19</v>
-      </c>
-      <c r="K9">
-        <v>22</v>
-      </c>
-      <c r="L9">
-        <v>18</v>
-      </c>
-      <c r="M9">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,28 +9,28 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="River North" sheetId="3" r:id="rId3"/>
-    <sheet name="North Lawndale" sheetId="4" r:id="rId4"/>
-    <sheet name="Englewood" sheetId="5" r:id="rId5"/>
-    <sheet name="Uptown" sheetId="6" r:id="rId6"/>
-    <sheet name="Loop" sheetId="7" r:id="rId7"/>
-    <sheet name="Logan Square" sheetId="8" r:id="rId8"/>
-    <sheet name="Riverdale" sheetId="9" r:id="rId9"/>
-    <sheet name="Fuller Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Little Village" sheetId="11" r:id="rId11"/>
-    <sheet name="Chatham" sheetId="12" r:id="rId12"/>
-    <sheet name="West Loop" sheetId="13" r:id="rId13"/>
-    <sheet name="Auburn Gresham" sheetId="14" r:id="rId14"/>
-    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
-    <sheet name="Humboldt Park" sheetId="16" r:id="rId16"/>
-    <sheet name="Austin" sheetId="17" r:id="rId17"/>
-    <sheet name="Roseland" sheetId="18" r:id="rId18"/>
-    <sheet name="Albany Park" sheetId="19" r:id="rId19"/>
-    <sheet name="Woodlawn" sheetId="20" r:id="rId20"/>
-    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
-    <sheet name="Old Town" sheetId="22" r:id="rId22"/>
-    <sheet name="Lincoln Park" sheetId="23" r:id="rId23"/>
-    <sheet name="O'Hare" sheetId="24" r:id="rId24"/>
+    <sheet name="O'Hare" sheetId="3" r:id="rId3"/>
+    <sheet name="River North" sheetId="4" r:id="rId4"/>
+    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
+    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
+    <sheet name="Uptown" sheetId="7" r:id="rId7"/>
+    <sheet name="Loop" sheetId="8" r:id="rId8"/>
+    <sheet name="Logan Square" sheetId="9" r:id="rId9"/>
+    <sheet name="Riverdale" sheetId="10" r:id="rId10"/>
+    <sheet name="Fuller Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Little Village" sheetId="12" r:id="rId12"/>
+    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
+    <sheet name="West Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Auburn Gresham" sheetId="15" r:id="rId15"/>
+    <sheet name="Lake View" sheetId="16" r:id="rId16"/>
+    <sheet name="Humboldt Park" sheetId="17" r:id="rId17"/>
+    <sheet name="Austin" sheetId="18" r:id="rId18"/>
+    <sheet name="Roseland" sheetId="19" r:id="rId19"/>
+    <sheet name="Albany Park" sheetId="20" r:id="rId20"/>
+    <sheet name="Woodlawn" sheetId="21" r:id="rId21"/>
+    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
+    <sheet name="Old Town" sheetId="23" r:id="rId23"/>
+    <sheet name="Lincoln Park" sheetId="24" r:id="rId24"/>
     <sheet name="Near South Side" sheetId="25" r:id="rId25"/>
     <sheet name="Grand Crossing" sheetId="26" r:id="rId26"/>
     <sheet name="Avondale" sheetId="27" r:id="rId27"/>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="109">
   <si>
     <t>crime_category</t>
   </si>
@@ -872,25 +872,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2">
+        <v>68</v>
+      </c>
+      <c r="G2">
         <v>67</v>
       </c>
-      <c r="G2">
-        <v>66</v>
-      </c>
       <c r="H2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I2">
         <v>91</v>
@@ -902,7 +902,7 @@
         <v>111</v>
       </c>
       <c r="L2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M2">
         <v>89</v>
@@ -913,37 +913,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E3">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F3">
         <v>99</v>
       </c>
       <c r="G3">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I3">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J3">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K3">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L3">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M3">
         <v>155</v>
@@ -986,7 +986,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1030,13 +1030,13 @@
         <v>16</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1117,37 +1117,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C9">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D9">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E9">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F9">
         <v>404</v>
       </c>
       <c r="G9">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="H9">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="I9">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="J9">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K9">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="L9">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M9">
         <v>198</v>
@@ -1158,40 +1158,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>974</v>
+        <v>992</v>
       </c>
       <c r="C10">
-        <v>1189</v>
+        <v>1213</v>
       </c>
       <c r="D10">
-        <v>1348</v>
+        <v>1371</v>
       </c>
       <c r="E10">
-        <v>1663</v>
+        <v>1685</v>
       </c>
       <c r="F10">
-        <v>1692</v>
+        <v>1705</v>
       </c>
       <c r="G10">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="H10">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="I10">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="J10">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="K10">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="L10">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="M10">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1199,37 +1199,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1371</v>
+        <v>1393</v>
       </c>
       <c r="C11">
-        <v>1679</v>
+        <v>1709</v>
       </c>
       <c r="D11">
-        <v>1848</v>
+        <v>1880</v>
       </c>
       <c r="E11">
-        <v>2163</v>
+        <v>2193</v>
       </c>
       <c r="F11">
-        <v>2271</v>
+        <v>2285</v>
       </c>
       <c r="G11">
-        <v>1330</v>
+        <v>1344</v>
       </c>
       <c r="H11">
-        <v>989</v>
+        <v>1002</v>
       </c>
       <c r="I11">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="J11">
-        <v>1132</v>
+        <v>1147</v>
       </c>
       <c r="K11">
-        <v>1251</v>
+        <v>1268</v>
       </c>
       <c r="L11">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="M11">
         <v>850</v>
@@ -1241,6 +1241,171 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1418,7 +1583,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -1441,7 +1606,7 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8">
         <v>14</v>
@@ -1482,7 +1647,7 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>23</v>
@@ -1500,7 +1665,7 @@
         <v>20</v>
       </c>
       <c r="K9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9">
         <v>30</v>
@@ -1514,7 +1679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1654,7 +1819,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1692,7 +1857,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1730,7 +1895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1837,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1858,7 +2023,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -1946,7 +2111,7 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>26</v>
@@ -1987,10 +2152,10 @@
         <v>36</v>
       </c>
       <c r="C9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9">
         <v>39</v>
@@ -2011,7 +2176,7 @@
         <v>32</v>
       </c>
       <c r="K9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L9">
         <v>30</v>
@@ -2025,7 +2190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2094,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -2223,13 +2388,13 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8">
         <v>27</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>35</v>
@@ -2264,13 +2429,13 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>34</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9">
         <v>42</v>
@@ -2302,7 +2467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2437,7 +2602,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -2478,7 +2643,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -2493,7 +2658,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -2519,7 +2684,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -2534,7 +2699,7 @@
         <v>19</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -2560,7 +2725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2748,7 +2913,7 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>12</v>
@@ -2774,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>38</v>
@@ -2783,7 +2948,7 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>45</v>
@@ -2815,7 +2980,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8">
         <v>58</v>
@@ -2824,13 +2989,13 @@
         <v>42</v>
       </c>
       <c r="E8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8">
         <v>58</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H8">
         <v>32</v>
@@ -2856,7 +3021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3012,7 +3177,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -3038,7 +3203,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -3056,7 +3221,7 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -3079,7 +3244,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -3094,10 +3259,10 @@
         <v>23</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7">
         <v>11</v>
@@ -3120,7 +3285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3198,7 +3363,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -3325,19 +3490,19 @@
         <v>19</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <v>17</v>
       </c>
       <c r="K7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M7">
         <v>15</v>
@@ -3357,22 +3522,22 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>52</v>
       </c>
       <c r="H8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K8">
         <v>19</v>
@@ -3398,28 +3563,28 @@
         <v>45</v>
       </c>
       <c r="E9">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F9">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G9">
         <v>77</v>
       </c>
       <c r="H9">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I9">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M9">
         <v>53</v>
@@ -3430,7 +3595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3502,7 +3667,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -3537,7 +3702,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -3643,7 +3808,7 @@
         <v>12</v>
       </c>
       <c r="I8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J8">
         <v>15</v>
@@ -3666,7 +3831,7 @@
         <v>40</v>
       </c>
       <c r="C9">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9">
         <v>27</v>
@@ -3675,7 +3840,7 @@
         <v>34</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9">
         <v>24</v>
@@ -3684,19 +3849,19 @@
         <v>22</v>
       </c>
       <c r="I9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <v>30</v>
       </c>
       <c r="K9">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L9">
         <v>15</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3704,19 +3869,19 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>55</v>
       </c>
       <c r="F10">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10">
         <v>42</v>
@@ -3725,259 +3890,19 @@
         <v>43</v>
       </c>
       <c r="I10">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J10">
         <v>56</v>
       </c>
       <c r="K10">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L10">
         <v>37</v>
       </c>
       <c r="M10">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>14</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -4054,7 +3979,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>9</v>
@@ -4123,6 +4048,9 @@
       <c r="C4">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="F4">
         <v>1</v>
       </c>
@@ -4147,10 +4075,10 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -4171,13 +4099,13 @@
         <v>24</v>
       </c>
       <c r="J5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -4229,7 +4157,7 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -4244,7 +4172,7 @@
         <v>19</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -4279,28 +4207,28 @@
         <v>45</v>
       </c>
       <c r="E8">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F8">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G8">
         <v>77</v>
       </c>
       <c r="H8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I8">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M8">
         <v>53</v>
@@ -4358,7 +4286,7 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10">
         <v>15</v>
@@ -4367,16 +4295,16 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>12</v>
       </c>
       <c r="J10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L10">
         <v>17</v>
@@ -4420,7 +4348,7 @@
         <v>2</v>
       </c>
       <c r="M11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4501,7 +4429,7 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L14">
         <v>3</v>
@@ -4536,7 +4464,7 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>2</v>
@@ -4655,10 +4583,10 @@
         <v>36</v>
       </c>
       <c r="C19">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19">
         <v>39</v>
@@ -4679,7 +4607,7 @@
         <v>32</v>
       </c>
       <c r="K19">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L19">
         <v>30</v>
@@ -4699,7 +4627,7 @@
         <v>14</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -4708,13 +4636,13 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20">
         <v>7</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -4743,7 +4671,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <v>22</v>
@@ -4775,7 +4703,7 @@
         <v>32</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -4799,7 +4727,7 @@
         <v>5</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22">
         <v>4</v>
@@ -4834,7 +4762,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>12</v>
@@ -4941,7 +4869,7 @@
         <v>14</v>
       </c>
       <c r="C27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -4950,7 +4878,7 @@
         <v>22</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G27">
         <v>15</v>
@@ -4982,19 +4910,19 @@
         <v>78</v>
       </c>
       <c r="C28">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D28">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E28">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F28">
         <v>90</v>
       </c>
       <c r="G28">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H28">
         <v>62</v>
@@ -5006,10 +4934,10 @@
         <v>42</v>
       </c>
       <c r="K28">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L28">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M28">
         <v>36</v>
@@ -5029,7 +4957,7 @@
         <v>23</v>
       </c>
       <c r="E29">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F29">
         <v>23</v>
@@ -5047,7 +4975,7 @@
         <v>20</v>
       </c>
       <c r="K29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L29">
         <v>30</v>
@@ -5091,7 +5019,7 @@
         <v>15</v>
       </c>
       <c r="L30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M30">
         <v>7</v>
@@ -5128,37 +5056,37 @@
         <v>42</v>
       </c>
       <c r="B32">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D32">
         <v>78</v>
       </c>
       <c r="E32">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F32">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G32">
         <v>91</v>
       </c>
       <c r="H32">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I32">
         <v>78</v>
       </c>
       <c r="J32">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K32">
         <v>64</v>
       </c>
       <c r="L32">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M32">
         <v>46</v>
@@ -5181,7 +5109,7 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33">
         <v>1</v>
@@ -5227,10 +5155,10 @@
         <v>15</v>
       </c>
       <c r="C35">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35">
         <v>18</v>
@@ -5248,7 +5176,7 @@
         <v>9</v>
       </c>
       <c r="J35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K35">
         <v>12</v>
@@ -5274,7 +5202,7 @@
         <v>65</v>
       </c>
       <c r="E36">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F36">
         <v>68</v>
@@ -5286,16 +5214,16 @@
         <v>51</v>
       </c>
       <c r="I36">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J36">
         <v>43</v>
       </c>
       <c r="K36">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L36">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M36">
         <v>40</v>
@@ -5362,7 +5290,7 @@
         <v>5</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>9</v>
@@ -5434,7 +5362,7 @@
         <v>51</v>
       </c>
       <c r="B41">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41">
         <v>25</v>
@@ -5449,10 +5377,10 @@
         <v>23</v>
       </c>
       <c r="G41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I41">
         <v>11</v>
@@ -5516,7 +5444,7 @@
         <v>53</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C43">
         <v>11</v>
@@ -5534,7 +5462,7 @@
         <v>13</v>
       </c>
       <c r="H43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43">
         <v>11</v>
@@ -5589,7 +5517,7 @@
         <v>55</v>
       </c>
       <c r="B45">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C45">
         <v>15</v>
@@ -5598,7 +5526,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F45">
         <v>19</v>
@@ -5607,13 +5535,13 @@
         <v>25</v>
       </c>
       <c r="H45">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I45">
         <v>10</v>
       </c>
       <c r="J45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K45">
         <v>14</v>
@@ -5671,7 +5599,7 @@
         <v>57</v>
       </c>
       <c r="B47">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C47">
         <v>58</v>
@@ -5680,13 +5608,13 @@
         <v>42</v>
       </c>
       <c r="E47">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F47">
         <v>58</v>
       </c>
       <c r="G47">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H47">
         <v>32</v>
@@ -5718,7 +5646,7 @@
         <v>11</v>
       </c>
       <c r="D48">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48">
         <v>9</v>
@@ -5727,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="G48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -5756,16 +5684,16 @@
         <v>4</v>
       </c>
       <c r="C49">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D49">
         <v>7</v>
       </c>
       <c r="E49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G49">
         <v>7</v>
@@ -5783,7 +5711,7 @@
         <v>4</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M49">
         <v>3</v>
@@ -5815,7 +5743,7 @@
         <v>19</v>
       </c>
       <c r="I50">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J50">
         <v>24</v>
@@ -5838,7 +5766,7 @@
         <v>9</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51">
         <v>6</v>
@@ -5882,7 +5810,7 @@
         <v>25</v>
       </c>
       <c r="D52">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E52">
         <v>24</v>
@@ -5900,13 +5828,13 @@
         <v>19</v>
       </c>
       <c r="J52">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K52">
         <v>16</v>
       </c>
       <c r="L52">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M52">
         <v>9</v>
@@ -5917,40 +5845,40 @@
         <v>63</v>
       </c>
       <c r="B53">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C53">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D53">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="E53">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="F53">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G53">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H53">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I53">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J53">
         <v>180</v>
       </c>
       <c r="K53">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L53">
         <v>145</v>
       </c>
       <c r="M53">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6005,7 +5933,7 @@
         <v>5</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55">
         <v>6</v>
@@ -6058,7 +5986,7 @@
         <v>3</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56">
         <v>2</v>
@@ -6070,7 +5998,7 @@
         <v>10</v>
       </c>
       <c r="L56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M56">
         <v>2</v>
@@ -6145,7 +6073,7 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -6185,13 +6113,13 @@
         <v>33</v>
       </c>
       <c r="D61">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E61">
         <v>47</v>
       </c>
       <c r="F61">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G61">
         <v>19</v>
@@ -6206,13 +6134,13 @@
         <v>5</v>
       </c>
       <c r="K61">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L61">
         <v>10</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6223,10 +6151,10 @@
         <v>21</v>
       </c>
       <c r="C62">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E62">
         <v>22</v>
@@ -6288,7 +6216,7 @@
         <v>5</v>
       </c>
       <c r="K63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L63">
         <v>3</v>
@@ -6308,7 +6236,7 @@
         <v>5</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E64">
         <v>5</v>
@@ -6349,19 +6277,19 @@
         <v>43</v>
       </c>
       <c r="E65">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F65">
         <v>54</v>
       </c>
       <c r="G65">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H65">
         <v>17</v>
       </c>
       <c r="I65">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J65">
         <v>12</v>
@@ -6370,7 +6298,7 @@
         <v>23</v>
       </c>
       <c r="L65">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M65">
         <v>15</v>
@@ -6466,7 +6394,7 @@
         <v>8</v>
       </c>
       <c r="C68">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D68">
         <v>21</v>
@@ -6484,10 +6412,10 @@
         <v>5</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J68">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K68">
         <v>16</v>
@@ -6496,7 +6424,7 @@
         <v>16</v>
       </c>
       <c r="M68">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -6557,7 +6485,7 @@
         <v>27</v>
       </c>
       <c r="J70">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K70">
         <v>26</v>
@@ -6618,7 +6546,7 @@
         <v>8</v>
       </c>
       <c r="D72">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72">
         <v>11</v>
@@ -6630,7 +6558,7 @@
         <v>7</v>
       </c>
       <c r="H72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I72">
         <v>13</v>
@@ -6653,7 +6581,7 @@
         <v>83</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D73">
         <v>3</v>
@@ -6679,13 +6607,13 @@
         <v>41</v>
       </c>
       <c r="C74">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D74">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E74">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F74">
         <v>78</v>
@@ -6697,16 +6625,16 @@
         <v>18</v>
       </c>
       <c r="I74">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J74">
         <v>30</v>
       </c>
       <c r="K74">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L74">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M74">
         <v>20</v>
@@ -6723,7 +6651,7 @@
         <v>1</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -6755,19 +6683,19 @@
         <v>86</v>
       </c>
       <c r="B76">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C76">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D76">
         <v>44</v>
       </c>
       <c r="E76">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F76">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G76">
         <v>37</v>
@@ -6785,7 +6713,7 @@
         <v>39</v>
       </c>
       <c r="L76">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M76">
         <v>24</v>
@@ -6796,19 +6724,19 @@
         <v>87</v>
       </c>
       <c r="B77">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C77">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D77">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E77">
         <v>55</v>
       </c>
       <c r="F77">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G77">
         <v>42</v>
@@ -6817,19 +6745,19 @@
         <v>43</v>
       </c>
       <c r="I77">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J77">
         <v>56</v>
       </c>
       <c r="K77">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L77">
         <v>37</v>
       </c>
       <c r="M77">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6837,16 +6765,16 @@
         <v>88</v>
       </c>
       <c r="B78">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C78">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D78">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E78">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F78">
         <v>41</v>
@@ -6889,7 +6817,7 @@
         <v>90</v>
       </c>
       <c r="B80">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C80">
         <v>20</v>
@@ -6910,7 +6838,7 @@
         <v>12</v>
       </c>
       <c r="I80">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J80">
         <v>9</v>
@@ -6939,13 +6867,13 @@
         <v>7</v>
       </c>
       <c r="E81">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F81">
         <v>10</v>
       </c>
       <c r="G81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H81">
         <v>10</v>
@@ -7015,7 +6943,7 @@
         <v>28</v>
       </c>
       <c r="D83">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E83">
         <v>16</v>
@@ -7033,7 +6961,7 @@
         <v>13</v>
       </c>
       <c r="J83">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K83">
         <v>10</v>
@@ -7109,7 +7037,7 @@
         <v>3</v>
       </c>
       <c r="L85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M85">
         <v>4</v>
@@ -7126,7 +7054,7 @@
         <v>18</v>
       </c>
       <c r="D86">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E86">
         <v>13</v>
@@ -7141,7 +7069,7 @@
         <v>5</v>
       </c>
       <c r="I86">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J86">
         <v>15</v>
@@ -7176,7 +7104,7 @@
         <v>23</v>
       </c>
       <c r="G87">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H87">
         <v>23</v>
@@ -7185,13 +7113,13 @@
         <v>18</v>
       </c>
       <c r="J87">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K87">
         <v>24</v>
       </c>
       <c r="L87">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M87">
         <v>17</v>
@@ -7249,13 +7177,13 @@
         <v>23</v>
       </c>
       <c r="D89">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E89">
         <v>15</v>
       </c>
       <c r="F89">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G89">
         <v>11</v>
@@ -7357,13 +7285,13 @@
         <v>18</v>
       </c>
       <c r="C92">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D92">
         <v>34</v>
       </c>
       <c r="E92">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F92">
         <v>42</v>
@@ -7474,10 +7402,10 @@
         <v>105</v>
       </c>
       <c r="B95">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D95">
         <v>41</v>
@@ -7486,7 +7414,7 @@
         <v>71</v>
       </c>
       <c r="F95">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G95">
         <v>13</v>
@@ -7495,7 +7423,7 @@
         <v>13</v>
       </c>
       <c r="I95">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J95">
         <v>11</v>
@@ -7504,7 +7432,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M95">
         <v>16</v>
@@ -7521,7 +7449,7 @@
         <v>13</v>
       </c>
       <c r="D96">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E96">
         <v>28</v>
@@ -7556,7 +7484,7 @@
         <v>107</v>
       </c>
       <c r="B97">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C97">
         <v>17</v>
@@ -7565,7 +7493,7 @@
         <v>20</v>
       </c>
       <c r="E97">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F97">
         <v>18</v>
@@ -7580,7 +7508,7 @@
         <v>16</v>
       </c>
       <c r="J97">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K97">
         <v>10</v>
@@ -7638,37 +7566,37 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1371</v>
+        <v>1393</v>
       </c>
       <c r="C99">
-        <v>1679</v>
+        <v>1709</v>
       </c>
       <c r="D99">
-        <v>1848</v>
+        <v>1880</v>
       </c>
       <c r="E99">
-        <v>2163</v>
+        <v>2193</v>
       </c>
       <c r="F99">
-        <v>2271</v>
+        <v>2285</v>
       </c>
       <c r="G99">
-        <v>1330</v>
+        <v>1344</v>
       </c>
       <c r="H99">
-        <v>989</v>
+        <v>1002</v>
       </c>
       <c r="I99">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="J99">
-        <v>1132</v>
+        <v>1147</v>
       </c>
       <c r="K99">
-        <v>1251</v>
+        <v>1268</v>
       </c>
       <c r="L99">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="M99">
         <v>850</v>
@@ -7844,20 +7772,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7865,44 +7799,35 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -7911,37 +7836,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -7952,40 +7868,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>6</v>
       </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
       <c r="E6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -7993,40 +7909,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>10</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
         <v>7</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8035,6 +7951,261 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8135,7 +8306,7 @@
         <v>3</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -8191,7 +8362,7 @@
         <v>7</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>3</v>
@@ -8255,7 +8426,7 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>16</v>
@@ -8273,7 +8444,7 @@
         <v>13</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -8290,7 +8461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8403,7 +8574,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -8531,7 +8702,7 @@
         <v>27</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7">
         <v>26</v>
@@ -8548,7 +8719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8676,6 +8847,9 @@
       <c r="F5">
         <v>2</v>
       </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
       <c r="H5">
         <v>2</v>
       </c>
@@ -8700,7 +8874,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -8741,7 +8915,7 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -8750,7 +8924,7 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -8769,233 +8943,6 @@
       </c>
       <c r="M7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>33</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>11</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>35</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>16</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -9137,7 +9084,7 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -9175,7 +9122,7 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -9216,10 +9163,10 @@
         <v>21</v>
       </c>
       <c r="C8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>22</v>
@@ -9391,7 +9338,7 @@
         <v>12</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -9459,7 +9406,7 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>16</v>
@@ -9471,7 +9418,7 @@
         <v>20</v>
       </c>
       <c r="I7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7">
         <v>18</v>
@@ -9518,7 +9465,7 @@
         <v>11</v>
       </c>
       <c r="K8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L8">
         <v>25</v>
@@ -9541,7 +9488,7 @@
         <v>65</v>
       </c>
       <c r="E9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9">
         <v>68</v>
@@ -9553,16 +9500,16 @@
         <v>51</v>
       </c>
       <c r="I9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J9">
         <v>43</v>
       </c>
       <c r="K9">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L9">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M9">
         <v>40</v>
@@ -9717,13 +9664,16 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -9743,7 +9693,7 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>12</v>
@@ -9761,7 +9711,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -9784,7 +9734,7 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>15</v>
@@ -9793,16 +9743,16 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>12</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L7">
         <v>17</v>
@@ -9983,16 +9933,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>33</v>
@@ -10024,16 +9974,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>41</v>
@@ -10196,7 +10146,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10259,32 +10209,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
       <c r="I2">
         <v>3</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10292,165 +10236,137 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
         <v>6</v>
       </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
-      </c>
       <c r="L5">
         <v>2</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>38</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>56</v>
-      </c>
-      <c r="E6">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>68</v>
-      </c>
-      <c r="G6">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>18</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>41</v>
-      </c>
-      <c r="C7">
-        <v>30</v>
-      </c>
-      <c r="D7">
-        <v>66</v>
-      </c>
-      <c r="E7">
-        <v>67</v>
-      </c>
-      <c r="F7">
-        <v>78</v>
-      </c>
-      <c r="G7">
-        <v>30</v>
-      </c>
-      <c r="H7">
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>16</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
         <v>18</v>
-      </c>
-      <c r="I7">
-        <v>33</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>13</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -10625,6 +10541,9 @@
       <c r="J5">
         <v>1</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
       <c r="L5">
         <v>1</v>
       </c>
@@ -10664,7 +10583,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -10823,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -10861,7 +10780,7 @@
         <v>2</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -11016,7 +10935,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -11028,7 +10947,7 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -11057,7 +10976,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>11</v>
@@ -11069,7 +10988,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>13</v>
@@ -11550,7 +11469,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -11591,7 +11510,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>13</v>
@@ -11609,7 +11528,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -11629,10 +11548,10 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>18</v>
@@ -11650,7 +11569,7 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <v>12</v>
@@ -11840,10 +11759,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -11852,7 +11771,7 @@
         <v>66</v>
       </c>
       <c r="F6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -11861,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -11870,7 +11789,7 @@
         <v>13</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -11881,10 +11800,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -11893,7 +11812,7 @@
         <v>71</v>
       </c>
       <c r="F7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -11902,7 +11821,7 @@
         <v>13</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>11</v>
@@ -11911,7 +11830,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7">
         <v>16</v>
@@ -11993,6 +11912,9 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="I2">
         <v>1</v>
       </c>
@@ -12141,7 +12063,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>12</v>
@@ -12570,13 +12492,13 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -12611,13 +12533,13 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>15</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -12648,7 +12570,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12711,9 +12633,6 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
@@ -12726,61 +12645,52 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -12788,144 +12698,136 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>57</v>
+      </c>
+      <c r="E6">
+        <v>63</v>
+      </c>
+      <c r="F6">
+        <v>68</v>
+      </c>
+      <c r="G6">
+        <v>17</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
+      <c r="K6">
         <v>14</v>
       </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
       <c r="M6">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>42</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>33</v>
-      </c>
-      <c r="F8">
-        <v>54</v>
-      </c>
-      <c r="G8">
-        <v>39</v>
-      </c>
-      <c r="H8">
-        <v>17</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>23</v>
-      </c>
-      <c r="L8">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -13073,7 +12975,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -13114,7 +13016,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -13209,7 +13111,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -13345,19 +13247,19 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>34</v>
       </c>
       <c r="E7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7">
         <v>24</v>
@@ -13375,7 +13277,7 @@
         <v>20</v>
       </c>
       <c r="L7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7">
         <v>15</v>
@@ -13386,19 +13288,19 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8">
         <v>44</v>
       </c>
       <c r="E8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F8">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>37</v>
@@ -13416,7 +13318,7 @@
         <v>39</v>
       </c>
       <c r="L8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8">
         <v>24</v>
@@ -13611,13 +13513,13 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>44</v>
@@ -13626,7 +13528,7 @@
         <v>35</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7">
         <v>24</v>
@@ -13649,19 +13551,19 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8">
         <v>36</v>
       </c>
       <c r="E8">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G8">
         <v>48</v>
@@ -13673,13 +13575,13 @@
         <v>41</v>
       </c>
       <c r="J8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8">
         <v>25</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8">
         <v>19</v>
@@ -13690,37 +13592,37 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D9">
         <v>78</v>
       </c>
       <c r="E9">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F9">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G9">
         <v>91</v>
       </c>
       <c r="H9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I9">
         <v>78</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K9">
         <v>64</v>
       </c>
       <c r="L9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M9">
         <v>46</v>
@@ -13874,7 +13776,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -13924,7 +13826,7 @@
         <v>16</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -13956,7 +13858,7 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>21</v>
@@ -13965,7 +13867,7 @@
         <v>22</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8">
         <v>15</v>
@@ -14165,7 +14067,7 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -14247,7 +14149,7 @@
         <v>19</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <v>24</v>
@@ -14371,7 +14273,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -14507,7 +14409,7 @@
         <v>15</v>
       </c>
       <c r="L8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M8">
         <v>7</v>
@@ -14658,7 +14560,7 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>24</v>
@@ -14699,7 +14601,7 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>28</v>
@@ -15334,7 +15236,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15397,35 +15299,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15433,205 +15341,179 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <v>6</v>
       </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>15</v>
-      </c>
-      <c r="L3">
-        <v>15</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
         <v>26</v>
       </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
       <c r="E7">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="K7">
-        <v>28</v>
-      </c>
       <c r="L7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C8">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>17</v>
+      </c>
+      <c r="I8">
         <v>30</v>
       </c>
-      <c r="H8">
-        <v>24</v>
-      </c>
-      <c r="I8">
-        <v>33</v>
-      </c>
       <c r="J8">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>78</v>
-      </c>
-      <c r="C9">
-        <v>110</v>
-      </c>
-      <c r="D9">
-        <v>81</v>
-      </c>
-      <c r="E9">
-        <v>72</v>
-      </c>
-      <c r="F9">
-        <v>90</v>
-      </c>
-      <c r="G9">
-        <v>65</v>
-      </c>
-      <c r="H9">
-        <v>62</v>
-      </c>
-      <c r="I9">
-        <v>71</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>68</v>
-      </c>
-      <c r="L9">
-        <v>77</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -15711,6 +15593,9 @@
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>3</v>
       </c>
@@ -15773,7 +15658,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -15909,7 +15794,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -15981,7 +15866,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -16022,7 +15907,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -16043,7 +15928,7 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -16065,10 +15950,10 @@
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -16163,19 +16048,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -16183,83 +16056,103 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
         <v>3</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
       </c>
       <c r="E6">
         <v>7</v>
       </c>
       <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
         <v>10</v>
       </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
         <v>2</v>
       </c>
     </row>
@@ -16366,13 +16259,16 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4">
         <v>1</v>
       </c>
@@ -16409,10 +16305,10 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -16430,7 +16326,7 @@
         <v>3</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -16444,16 +16340,16 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -16471,7 +16367,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -16962,7 +16858,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -17000,7 +16896,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -17031,7 +16927,7 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -17107,7 +17003,7 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -17116,13 +17012,13 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>7</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -17144,7 +17040,7 @@
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -17204,62 +17100,70 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>2</v>
       </c>
     </row>
@@ -17748,73 +17652,73 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
       <c r="G2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -17822,17 +17726,32 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -17840,7 +17759,10 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -17849,40 +17771,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -17890,40 +17812,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C8">
+        <v>72</v>
+      </c>
+      <c r="D8">
+        <v>48</v>
+      </c>
+      <c r="E8">
+        <v>47</v>
+      </c>
+      <c r="F8">
+        <v>49</v>
+      </c>
+      <c r="G8">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>33</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
         <v>22</v>
       </c>
-      <c r="D8">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>13</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
+      <c r="L8">
+        <v>24</v>
+      </c>
+      <c r="M8">
         <v>9</v>
-      </c>
-      <c r="L8">
-        <v>13</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17931,40 +17853,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="G9">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="I9">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="J9">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L9">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="M9">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -18075,6 +17997,9 @@
       <c r="F3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>1</v>
       </c>
@@ -18146,7 +18071,7 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -18187,13 +18112,13 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>10</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -18387,10 +18312,10 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>14</v>
@@ -18404,10 +18329,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -18434,7 +18359,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -18445,10 +18370,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -18469,13 +18394,13 @@
         <v>24</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -18581,7 +18506,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -18725,7 +18650,7 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>22</v>
@@ -18909,7 +18834,7 @@
         <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -18926,7 +18851,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -18935,7 +18860,7 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>16</v>
@@ -18944,7 +18869,7 @@
         <v>20</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -18967,7 +18892,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8">
         <v>15</v>
@@ -18976,7 +18901,7 @@
         <v>14</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>19</v>
@@ -18985,13 +18910,13 @@
         <v>25</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>14</v>
@@ -19334,6 +19259,9 @@
       <c r="G3">
         <v>2</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
       <c r="I3">
         <v>2</v>
       </c>
@@ -19359,6 +19287,9 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
       <c r="C5">
         <v>2</v>
       </c>
@@ -19398,7 +19329,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -19439,7 +19370,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>11</v>
@@ -19457,7 +19388,7 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>11</v>
@@ -19612,6 +19543,9 @@
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="F4">
         <v>1</v>
       </c>
@@ -19699,7 +19633,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -19725,7 +19659,7 @@
         <v>18</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -19740,7 +19674,7 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>15</v>
@@ -20042,7 +19976,7 @@
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -20054,9 +19988,10 @@
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20067,47 +20002,50 @@
         <v>2016</v>
       </c>
       <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
         <v>2019</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2023</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2024</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2025</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -20115,7 +20053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -20125,14 +20063,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -20142,17 +20080,20 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>2</v>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -20169,15 +20110,18 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>2</v>
       </c>
     </row>
@@ -20188,7 +20132,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -20252,97 +20196,82 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
       <c r="C3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -20350,180 +20279,139 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+        <v>7</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
       <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>13</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>27</v>
-      </c>
-      <c r="D8">
-        <v>35</v>
-      </c>
-      <c r="E8">
-        <v>51</v>
-      </c>
-      <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>47</v>
-      </c>
-      <c r="H8">
-        <v>49</v>
-      </c>
-      <c r="I8">
-        <v>68</v>
-      </c>
-      <c r="J8">
-        <v>47</v>
-      </c>
-      <c r="K8">
-        <v>40</v>
-      </c>
-      <c r="L8">
-        <v>36</v>
-      </c>
-      <c r="M8">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="C9">
-        <v>227</v>
+        <v>33</v>
       </c>
       <c r="D9">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>479</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>456</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="I9">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="J9">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="K9">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="L9">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="M9">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>169</v>
-      </c>
-      <c r="C10">
-        <v>269</v>
-      </c>
-      <c r="D10">
-        <v>449</v>
-      </c>
-      <c r="E10">
-        <v>541</v>
-      </c>
-      <c r="F10">
-        <v>515</v>
-      </c>
-      <c r="G10">
-        <v>210</v>
-      </c>
-      <c r="H10">
-        <v>142</v>
-      </c>
-      <c r="I10">
-        <v>265</v>
-      </c>
-      <c r="J10">
-        <v>180</v>
-      </c>
-      <c r="K10">
-        <v>162</v>
-      </c>
-      <c r="L10">
-        <v>145</v>
-      </c>
-      <c r="M10">
-        <v>94</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -20848,7 +20736,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -20868,7 +20756,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -21969,7 +21857,7 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22045,7 +21933,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -22061,7 +21949,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -22124,118 +22012,145 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
       <c r="I2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="L4">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -22243,84 +22158,133 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <v>51</v>
+      </c>
+      <c r="F8">
+        <v>44</v>
+      </c>
+      <c r="G8">
+        <v>48</v>
+      </c>
+      <c r="H8">
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>68</v>
+      </c>
+      <c r="J8">
+        <v>47</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>36</v>
+      </c>
+      <c r="M8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>139</v>
+      </c>
+      <c r="C9">
+        <v>232</v>
+      </c>
+      <c r="D9">
+        <v>398</v>
+      </c>
+      <c r="E9">
+        <v>485</v>
+      </c>
+      <c r="F9">
+        <v>460</v>
+      </c>
+      <c r="G9">
+        <v>144</v>
+      </c>
+      <c r="H9">
+        <v>74</v>
+      </c>
+      <c r="I9">
+        <v>160</v>
+      </c>
+      <c r="J9">
+        <v>88</v>
+      </c>
+      <c r="K9">
+        <v>84</v>
+      </c>
+      <c r="L9">
+        <v>67</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>28</v>
-      </c>
-      <c r="E8">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>18</v>
-      </c>
-      <c r="G8">
-        <v>19</v>
-      </c>
-      <c r="H8">
-        <v>14</v>
-      </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>23</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>20</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
+      <c r="B10">
+        <v>175</v>
+      </c>
+      <c r="C10">
+        <v>274</v>
+      </c>
+      <c r="D10">
+        <v>459</v>
+      </c>
+      <c r="E10">
+        <v>547</v>
+      </c>
+      <c r="F10">
+        <v>519</v>
+      </c>
+      <c r="G10">
+        <v>212</v>
+      </c>
+      <c r="H10">
+        <v>144</v>
+      </c>
+      <c r="I10">
+        <v>267</v>
+      </c>
+      <c r="J10">
+        <v>180</v>
+      </c>
+      <c r="K10">
+        <v>164</v>
+      </c>
+      <c r="L10">
+        <v>145</v>
+      </c>
+      <c r="M10">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -22406,6 +22370,9 @@
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
@@ -22464,7 +22431,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -22489,7 +22456,7 @@
 
 <file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -22546,102 +22513,110 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
         <v>4</v>
       </c>
     </row>
@@ -22884,7 +22859,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -22928,7 +22903,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -22969,7 +22944,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -22993,7 +22968,7 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>4</v>
@@ -23160,6 +23135,9 @@
       <c r="H6">
         <v>1</v>
       </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
       <c r="K6">
         <v>1</v>
       </c>
@@ -23193,7 +23171,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -23694,7 +23672,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -23735,7 +23713,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -24024,10 +24002,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -24039,9 +24017,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24064,119 +24043,225 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
+      <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>24</v>
+      </c>
+      <c r="K8">
+        <v>16</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -9,46 +9,46 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="O'Hare" sheetId="3" r:id="rId3"/>
-    <sheet name="River North" sheetId="4" r:id="rId4"/>
-    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
-    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
-    <sheet name="Uptown" sheetId="7" r:id="rId7"/>
-    <sheet name="Loop" sheetId="8" r:id="rId8"/>
-    <sheet name="Logan Square" sheetId="9" r:id="rId9"/>
-    <sheet name="Riverdale" sheetId="10" r:id="rId10"/>
-    <sheet name="Fuller Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Little Village" sheetId="12" r:id="rId12"/>
-    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
-    <sheet name="West Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Auburn Gresham" sheetId="15" r:id="rId15"/>
-    <sheet name="Lake View" sheetId="16" r:id="rId16"/>
-    <sheet name="Humboldt Park" sheetId="17" r:id="rId17"/>
-    <sheet name="Austin" sheetId="18" r:id="rId18"/>
-    <sheet name="Roseland" sheetId="19" r:id="rId19"/>
-    <sheet name="Albany Park" sheetId="20" r:id="rId20"/>
-    <sheet name="Woodlawn" sheetId="21" r:id="rId21"/>
-    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
-    <sheet name="Old Town" sheetId="23" r:id="rId23"/>
-    <sheet name="Lincoln Park" sheetId="24" r:id="rId24"/>
-    <sheet name="Near South Side" sheetId="25" r:id="rId25"/>
-    <sheet name="Grand Crossing" sheetId="26" r:id="rId26"/>
-    <sheet name="Avondale" sheetId="27" r:id="rId27"/>
-    <sheet name="Rush &amp; Division" sheetId="28" r:id="rId28"/>
-    <sheet name="Oakland" sheetId="29" r:id="rId29"/>
-    <sheet name="New City" sheetId="30" r:id="rId30"/>
-    <sheet name="Belmont Cragin" sheetId="31" r:id="rId31"/>
-    <sheet name="Printers Row" sheetId="32" r:id="rId32"/>
-    <sheet name="Hegewisch" sheetId="33" r:id="rId33"/>
-    <sheet name="Hyde Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Grand Boulevard" sheetId="35" r:id="rId35"/>
-    <sheet name="West Town" sheetId="36" r:id="rId36"/>
-    <sheet name="Douglas" sheetId="37" r:id="rId37"/>
-    <sheet name="Norwood Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Washington Park" sheetId="39" r:id="rId39"/>
-    <sheet name="Greektown" sheetId="40" r:id="rId40"/>
-    <sheet name="Rogers Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Garfield Park" sheetId="42" r:id="rId42"/>
+    <sheet name="Garfield Park" sheetId="3" r:id="rId3"/>
+    <sheet name="O'Hare" sheetId="4" r:id="rId4"/>
+    <sheet name="River North" sheetId="5" r:id="rId5"/>
+    <sheet name="North Lawndale" sheetId="6" r:id="rId6"/>
+    <sheet name="Englewood" sheetId="7" r:id="rId7"/>
+    <sheet name="Uptown" sheetId="8" r:id="rId8"/>
+    <sheet name="Loop" sheetId="9" r:id="rId9"/>
+    <sheet name="Logan Square" sheetId="10" r:id="rId10"/>
+    <sheet name="Riverdale" sheetId="11" r:id="rId11"/>
+    <sheet name="Fuller Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Little Village" sheetId="13" r:id="rId13"/>
+    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
+    <sheet name="West Loop" sheetId="15" r:id="rId15"/>
+    <sheet name="Auburn Gresham" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="Humboldt Park" sheetId="18" r:id="rId18"/>
+    <sheet name="Austin" sheetId="19" r:id="rId19"/>
+    <sheet name="Roseland" sheetId="20" r:id="rId20"/>
+    <sheet name="Albany Park" sheetId="21" r:id="rId21"/>
+    <sheet name="Woodlawn" sheetId="22" r:id="rId22"/>
+    <sheet name="South Shore" sheetId="23" r:id="rId23"/>
+    <sheet name="Old Town" sheetId="24" r:id="rId24"/>
+    <sheet name="Lincoln Park" sheetId="25" r:id="rId25"/>
+    <sheet name="Near South Side" sheetId="26" r:id="rId26"/>
+    <sheet name="Grand Crossing" sheetId="27" r:id="rId27"/>
+    <sheet name="Avondale" sheetId="28" r:id="rId28"/>
+    <sheet name="Rush &amp; Division" sheetId="29" r:id="rId29"/>
+    <sheet name="Oakland" sheetId="30" r:id="rId30"/>
+    <sheet name="New City" sheetId="31" r:id="rId31"/>
+    <sheet name="Belmont Cragin" sheetId="32" r:id="rId32"/>
+    <sheet name="Printers Row" sheetId="33" r:id="rId33"/>
+    <sheet name="Hegewisch" sheetId="34" r:id="rId34"/>
+    <sheet name="Hyde Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Grand Boulevard" sheetId="36" r:id="rId36"/>
+    <sheet name="West Town" sheetId="37" r:id="rId37"/>
+    <sheet name="Douglas" sheetId="38" r:id="rId38"/>
+    <sheet name="Norwood Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Washington Park" sheetId="40" r:id="rId40"/>
+    <sheet name="Greektown" sheetId="41" r:id="rId41"/>
+    <sheet name="Rogers Park" sheetId="42" r:id="rId42"/>
     <sheet name="Edgewater" sheetId="43" r:id="rId43"/>
     <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
     <sheet name="Gage Park" sheetId="45" r:id="rId45"/>
@@ -946,7 +946,7 @@
         <v>194</v>
       </c>
       <c r="M3">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1191,7 +1191,7 @@
         <v>523</v>
       </c>
       <c r="M10">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1232,7 +1232,7 @@
         <v>1204</v>
       </c>
       <c r="M11">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -1241,6 +1241,275 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>24</v>
+      </c>
+      <c r="K8">
+        <v>16</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1405,7 +1674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1679,7 +1948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1895,7 +2164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2190,7 +2459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2467,7 +2736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2725,7 +2994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3021,7 +3290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3285,7 +3554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3588,321 +3857,6 @@
       </c>
       <c r="M9">
         <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8">
-        <v>25</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>16</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>40</v>
-      </c>
-      <c r="C9">
-        <v>37</v>
-      </c>
-      <c r="D9">
-        <v>27</v>
-      </c>
-      <c r="E9">
-        <v>34</v>
-      </c>
-      <c r="F9">
-        <v>37</v>
-      </c>
-      <c r="G9">
-        <v>24</v>
-      </c>
-      <c r="H9">
-        <v>22</v>
-      </c>
-      <c r="I9">
-        <v>30</v>
-      </c>
-      <c r="J9">
-        <v>30</v>
-      </c>
-      <c r="K9">
-        <v>31</v>
-      </c>
-      <c r="L9">
-        <v>15</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>61</v>
-      </c>
-      <c r="C10">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>40</v>
-      </c>
-      <c r="E10">
-        <v>55</v>
-      </c>
-      <c r="F10">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>42</v>
-      </c>
-      <c r="H10">
-        <v>43</v>
-      </c>
-      <c r="I10">
-        <v>69</v>
-      </c>
-      <c r="J10">
-        <v>56</v>
-      </c>
-      <c r="K10">
-        <v>52</v>
-      </c>
-      <c r="L10">
-        <v>37</v>
-      </c>
-      <c r="M10">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -5089,7 +5043,7 @@
         <v>52</v>
       </c>
       <c r="M32">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -7599,7 +7553,7 @@
         <v>1204</v>
       </c>
       <c r="M99">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -7709,7 +7663,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7772,26 +7726,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7799,54 +7768,57 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
       <c r="G5">
         <v>1</v>
       </c>
@@ -7854,95 +7826,149 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>27</v>
+      </c>
+      <c r="E9">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>37</v>
+      </c>
+      <c r="G9">
+        <v>24</v>
+      </c>
+      <c r="H9">
+        <v>22</v>
+      </c>
+      <c r="I9">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>31</v>
+      </c>
+      <c r="L9">
+        <v>15</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>12</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>14</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
+      <c r="B10">
+        <v>61</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>55</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>42</v>
+      </c>
+      <c r="H10">
+        <v>43</v>
+      </c>
+      <c r="I10">
+        <v>69</v>
+      </c>
+      <c r="J10">
+        <v>56</v>
+      </c>
+      <c r="K10">
+        <v>52</v>
+      </c>
+      <c r="L10">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -8015,20 +8041,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8036,44 +8068,35 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -8082,37 +8105,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -8123,40 +8137,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>6</v>
       </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
       <c r="E6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8164,40 +8178,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>10</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
         <v>7</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>16</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8206,6 +8220,261 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8461,7 +8730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8719,7 +8988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8950,7 +9219,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9201,7 +9470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9513,252 +9782,6 @@
       </c>
       <c r="M9">
         <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>25</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>26</v>
-      </c>
-      <c r="E7">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>16</v>
-      </c>
-      <c r="K7">
-        <v>13</v>
-      </c>
-      <c r="L7">
-        <v>17</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -9831,59 +9854,59 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -9892,40 +9915,37 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9933,40 +9953,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9974,40 +9994,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="I7">
-        <v>20</v>
-      </c>
       <c r="J7">
+        <v>16</v>
+      </c>
+      <c r="K7">
         <v>13</v>
       </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
       <c r="L7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -10017,136 +10037,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10210,78 +10101,138 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>46</v>
+      </c>
+      <c r="E6">
+        <v>35</v>
+      </c>
+      <c r="F6">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
+      <c r="L6">
+        <v>9</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -10289,84 +10240,347 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>40</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
         <v>9</v>
       </c>
+      <c r="K3">
+        <v>14</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>38</v>
+      </c>
+      <c r="C8">
+        <v>45</v>
+      </c>
+      <c r="D8">
+        <v>36</v>
+      </c>
+      <c r="E8">
+        <v>64</v>
+      </c>
+      <c r="F8">
+        <v>104</v>
+      </c>
+      <c r="G8">
+        <v>48</v>
+      </c>
+      <c r="H8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>41</v>
+      </c>
+      <c r="J8">
+        <v>24</v>
+      </c>
+      <c r="K8">
+        <v>25</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>12</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>35</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>16</v>
-      </c>
-      <c r="M8">
-        <v>18</v>
+      <c r="B9">
+        <v>49</v>
+      </c>
+      <c r="C9">
+        <v>74</v>
+      </c>
+      <c r="D9">
+        <v>78</v>
+      </c>
+      <c r="E9">
+        <v>106</v>
+      </c>
+      <c r="F9">
+        <v>157</v>
+      </c>
+      <c r="G9">
+        <v>91</v>
+      </c>
+      <c r="H9">
+        <v>64</v>
+      </c>
+      <c r="I9">
+        <v>78</v>
+      </c>
+      <c r="J9">
+        <v>56</v>
+      </c>
+      <c r="K9">
+        <v>64</v>
+      </c>
+      <c r="L9">
+        <v>52</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -10375,6 +10589,135 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10597,7 +10940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10788,7 +11131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11011,7 +11354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11117,7 +11460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11337,7 +11680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11586,7 +11929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11834,251 +12177,6 @@
       </c>
       <c r="M7">
         <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>16</v>
-      </c>
-      <c r="C8">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>13</v>
-      </c>
-      <c r="E8">
-        <v>14</v>
-      </c>
-      <c r="F8">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12151,13 +12249,22 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K2">
-        <v>1</v>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -12165,30 +12272,30 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -12196,7 +12303,7 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -12204,26 +12311,35 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
         <v>4</v>
       </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="I6">
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12237,34 +12353,34 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
         <v>7</v>
       </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -12272,40 +12388,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8">
         <v>15</v>
       </c>
-      <c r="F8">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8">
-        <v>6</v>
-      </c>
       <c r="L8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12315,7 +12431,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12378,17 +12494,8 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -12401,166 +12508,147 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>18</v>
-      </c>
       <c r="C7">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
         <v>15</v>
       </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8">
         <v>8</v>
       </c>
-      <c r="L7">
+      <c r="H8">
         <v>7</v>
       </c>
-      <c r="M7">
-        <v>14</v>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -12570,7 +12658,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12633,32 +12721,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
       <c r="I2">
         <v>3</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12666,168 +12748,137 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
         <v>6</v>
       </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
       <c r="L5">
         <v>2</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>38</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>57</v>
-      </c>
-      <c r="E6">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>68</v>
-      </c>
-      <c r="G6">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>41</v>
-      </c>
-      <c r="C7">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>67</v>
-      </c>
-      <c r="E7">
-        <v>69</v>
-      </c>
-      <c r="F7">
-        <v>78</v>
-      </c>
-      <c r="G7">
-        <v>30</v>
-      </c>
-      <c r="H7">
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>16</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
         <v>18</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>28</v>
-      </c>
-      <c r="L7">
-        <v>15</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -12900,10 +12951,22 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -12911,15 +12974,42 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -12927,29 +13017,41 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
       <c r="D5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12957,40 +13059,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12998,40 +13100,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
         <v>14</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>5</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13040,6 +13142,210 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13322,310 +13628,6 @@
       </c>
       <c r="M8">
         <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>9</v>
-      </c>
-      <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
-      <c r="E7">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>44</v>
-      </c>
-      <c r="G7">
-        <v>35</v>
-      </c>
-      <c r="H7">
-        <v>32</v>
-      </c>
-      <c r="I7">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>22</v>
-      </c>
-      <c r="K7">
-        <v>21</v>
-      </c>
-      <c r="L7">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>38</v>
-      </c>
-      <c r="C8">
-        <v>45</v>
-      </c>
-      <c r="D8">
-        <v>36</v>
-      </c>
-      <c r="E8">
-        <v>64</v>
-      </c>
-      <c r="F8">
-        <v>104</v>
-      </c>
-      <c r="G8">
-        <v>48</v>
-      </c>
-      <c r="H8">
-        <v>23</v>
-      </c>
-      <c r="I8">
-        <v>41</v>
-      </c>
-      <c r="J8">
-        <v>24</v>
-      </c>
-      <c r="K8">
-        <v>25</v>
-      </c>
-      <c r="L8">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>49</v>
-      </c>
-      <c r="C9">
-        <v>74</v>
-      </c>
-      <c r="D9">
-        <v>78</v>
-      </c>
-      <c r="E9">
-        <v>106</v>
-      </c>
-      <c r="F9">
-        <v>157</v>
-      </c>
-      <c r="G9">
-        <v>91</v>
-      </c>
-      <c r="H9">
-        <v>64</v>
-      </c>
-      <c r="I9">
-        <v>78</v>
-      </c>
-      <c r="J9">
-        <v>56</v>
-      </c>
-      <c r="K9">
-        <v>64</v>
-      </c>
-      <c r="L9">
-        <v>52</v>
-      </c>
-      <c r="M9">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -15236,7 +15238,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15299,9 +15301,6 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
@@ -15314,55 +15313,46 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -15376,144 +15366,136 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>57</v>
+      </c>
+      <c r="E6">
+        <v>63</v>
+      </c>
+      <c r="F6">
+        <v>68</v>
+      </c>
+      <c r="G6">
+        <v>17</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
+      <c r="K6">
         <v>14</v>
       </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
       <c r="M6">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>42</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>34</v>
-      </c>
-      <c r="F8">
-        <v>54</v>
-      </c>
-      <c r="G8">
-        <v>40</v>
-      </c>
-      <c r="H8">
-        <v>17</v>
-      </c>
-      <c r="I8">
-        <v>30</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>23</v>
-      </c>
-      <c r="L8">
-        <v>18</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -17589,7 +17571,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17652,35 +17634,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17688,205 +17676,179 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <v>6</v>
       </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>15</v>
-      </c>
-      <c r="L3">
-        <v>16</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
         <v>26</v>
       </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
       <c r="E7">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="K7">
-        <v>29</v>
-      </c>
       <c r="L7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C8">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D8">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>17</v>
+      </c>
+      <c r="I8">
         <v>30</v>
       </c>
-      <c r="H8">
-        <v>24</v>
-      </c>
-      <c r="I8">
-        <v>33</v>
-      </c>
       <c r="J8">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>78</v>
-      </c>
-      <c r="C9">
-        <v>111</v>
-      </c>
-      <c r="D9">
-        <v>85</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>90</v>
-      </c>
-      <c r="G9">
-        <v>67</v>
-      </c>
-      <c r="H9">
-        <v>62</v>
-      </c>
-      <c r="I9">
-        <v>71</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>69</v>
-      </c>
-      <c r="L9">
-        <v>78</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -20195,73 +20157,73 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
       <c r="G2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -20269,17 +20231,32 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -20287,7 +20264,10 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -20296,40 +20276,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -20337,40 +20317,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C8">
+        <v>72</v>
+      </c>
+      <c r="D8">
+        <v>48</v>
+      </c>
+      <c r="E8">
+        <v>47</v>
+      </c>
+      <c r="F8">
+        <v>49</v>
+      </c>
+      <c r="G8">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>33</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
         <v>22</v>
       </c>
-      <c r="D8">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
-      <c r="K8">
+      <c r="L8">
+        <v>24</v>
+      </c>
+      <c r="M8">
         <v>9</v>
-      </c>
-      <c r="L8">
-        <v>13</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20378,40 +20358,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="G9">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="I9">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="J9">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L9">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="M9">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -21949,7 +21929,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -22013,97 +21993,82 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
       <c r="C3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -22111,180 +22076,139 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+        <v>7</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
       <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>13</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>27</v>
-      </c>
-      <c r="D8">
-        <v>35</v>
-      </c>
-      <c r="E8">
-        <v>51</v>
-      </c>
-      <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>48</v>
-      </c>
-      <c r="H8">
-        <v>49</v>
-      </c>
-      <c r="I8">
-        <v>68</v>
-      </c>
-      <c r="J8">
-        <v>47</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>36</v>
-      </c>
-      <c r="M8">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="C9">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c r="D9">
-        <v>398</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>485</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>460</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="I9">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="J9">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="K9">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L9">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="M9">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>175</v>
-      </c>
-      <c r="C10">
-        <v>274</v>
-      </c>
-      <c r="D10">
-        <v>459</v>
-      </c>
-      <c r="E10">
-        <v>547</v>
-      </c>
-      <c r="F10">
-        <v>519</v>
-      </c>
-      <c r="G10">
-        <v>212</v>
-      </c>
-      <c r="H10">
-        <v>144</v>
-      </c>
-      <c r="I10">
-        <v>267</v>
-      </c>
-      <c r="J10">
-        <v>180</v>
-      </c>
-      <c r="K10">
-        <v>164</v>
-      </c>
-      <c r="L10">
-        <v>145</v>
-      </c>
-      <c r="M10">
-        <v>93</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -24002,7 +23926,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -24065,118 +23989,145 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
       <c r="I2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="L4">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -24184,84 +24135,133 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <v>51</v>
+      </c>
+      <c r="F8">
+        <v>44</v>
+      </c>
+      <c r="G8">
+        <v>48</v>
+      </c>
+      <c r="H8">
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>68</v>
+      </c>
+      <c r="J8">
+        <v>47</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>36</v>
+      </c>
+      <c r="M8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>139</v>
+      </c>
+      <c r="C9">
+        <v>232</v>
+      </c>
+      <c r="D9">
+        <v>398</v>
+      </c>
+      <c r="E9">
+        <v>485</v>
+      </c>
+      <c r="F9">
+        <v>460</v>
+      </c>
+      <c r="G9">
+        <v>144</v>
+      </c>
+      <c r="H9">
+        <v>74</v>
+      </c>
+      <c r="I9">
+        <v>160</v>
+      </c>
+      <c r="J9">
+        <v>88</v>
+      </c>
+      <c r="K9">
+        <v>84</v>
+      </c>
+      <c r="L9">
+        <v>67</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>29</v>
-      </c>
-      <c r="E8">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>18</v>
-      </c>
-      <c r="G8">
-        <v>19</v>
-      </c>
-      <c r="H8">
-        <v>14</v>
-      </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>24</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
+      <c r="B10">
+        <v>175</v>
+      </c>
+      <c r="C10">
+        <v>274</v>
+      </c>
+      <c r="D10">
+        <v>459</v>
+      </c>
+      <c r="E10">
+        <v>547</v>
+      </c>
+      <c r="F10">
+        <v>519</v>
+      </c>
+      <c r="G10">
+        <v>212</v>
+      </c>
+      <c r="H10">
+        <v>144</v>
+      </c>
+      <c r="I10">
+        <v>267</v>
+      </c>
+      <c r="J10">
+        <v>180</v>
+      </c>
+      <c r="K10">
+        <v>164</v>
+      </c>
+      <c r="L10">
+        <v>145</v>
+      </c>
+      <c r="M10">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -45,16 +45,16 @@
     <sheet name="Greektown" sheetId="36" r:id="rId36"/>
     <sheet name="Norwood Park" sheetId="37" r:id="rId37"/>
     <sheet name="River North" sheetId="38" r:id="rId38"/>
-    <sheet name="Roseland" sheetId="39" r:id="rId39"/>
-    <sheet name="Chinatown" sheetId="40" r:id="rId40"/>
-    <sheet name="Austin" sheetId="41" r:id="rId41"/>
-    <sheet name="Rogers Park" sheetId="42" r:id="rId42"/>
-    <sheet name="Mckinley Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Armour Square" sheetId="44" r:id="rId44"/>
-    <sheet name="West Elsdon" sheetId="45" r:id="rId45"/>
-    <sheet name="Logan Square" sheetId="46" r:id="rId46"/>
-    <sheet name="Woodlawn" sheetId="47" r:id="rId47"/>
-    <sheet name="Edgewater" sheetId="48" r:id="rId48"/>
+    <sheet name="Edgewater" sheetId="39" r:id="rId39"/>
+    <sheet name="Roseland" sheetId="40" r:id="rId40"/>
+    <sheet name="Chinatown" sheetId="41" r:id="rId41"/>
+    <sheet name="Austin" sheetId="42" r:id="rId42"/>
+    <sheet name="Rogers Park" sheetId="43" r:id="rId43"/>
+    <sheet name="Mckinley Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Armour Square" sheetId="45" r:id="rId45"/>
+    <sheet name="West Elsdon" sheetId="46" r:id="rId46"/>
+    <sheet name="Logan Square" sheetId="47" r:id="rId47"/>
+    <sheet name="Woodlawn" sheetId="48" r:id="rId48"/>
     <sheet name="Lincoln Park" sheetId="49" r:id="rId49"/>
     <sheet name="Near South Side" sheetId="50" r:id="rId50"/>
     <sheet name="Ukrainian Village" sheetId="51" r:id="rId51"/>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="109">
   <si>
     <t>crime_category</t>
   </si>
@@ -875,7 +875,7 @@
         <v>33</v>
       </c>
       <c r="C2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2">
         <v>75</v>
@@ -890,22 +890,22 @@
         <v>69</v>
       </c>
       <c r="H2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -922,28 +922,28 @@
         <v>107</v>
       </c>
       <c r="E3">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H3">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J3">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K3">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="L3">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M3">
         <v>159</v>
@@ -977,6 +977,9 @@
       <c r="K4">
         <v>1</v>
       </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
       <c r="M4">
         <v>4</v>
       </c>
@@ -1024,7 +1027,7 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>16</v>
@@ -1117,40 +1120,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C9">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D9">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E9">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F9">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G9">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H9">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="I9">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="J9">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K9">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L9">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="M9">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1158,40 +1161,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="C10">
-        <v>1252</v>
+        <v>1263</v>
       </c>
       <c r="D10">
-        <v>1414</v>
+        <v>1431</v>
       </c>
       <c r="E10">
-        <v>1733</v>
+        <v>1741</v>
       </c>
       <c r="F10">
-        <v>1748</v>
+        <v>1762</v>
       </c>
       <c r="G10">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="H10">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="I10">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="J10">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="K10">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="L10">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M10">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1199,40 +1202,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1456</v>
+        <v>1469</v>
       </c>
       <c r="C11">
-        <v>1764</v>
+        <v>1779</v>
       </c>
       <c r="D11">
-        <v>1935</v>
+        <v>1956</v>
       </c>
       <c r="E11">
-        <v>2260</v>
+        <v>2274</v>
       </c>
       <c r="F11">
-        <v>2339</v>
+        <v>2357</v>
       </c>
       <c r="G11">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="H11">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="I11">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="J11">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="K11">
-        <v>1297</v>
+        <v>1314</v>
       </c>
       <c r="L11">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="M11">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -1630,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -1709,7 +1712,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -1804,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1982,7 +1985,7 @@
         <v>22</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>26</v>
@@ -2083,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -2285,7 +2288,7 @@
         <v>34</v>
       </c>
       <c r="H10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10">
         <v>28</v>
@@ -2475,7 +2478,7 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -2516,7 +2519,7 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -2691,7 +2694,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>24</v>
@@ -2732,7 +2735,7 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>28</v>
@@ -2831,6 +2834,9 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="L2">
         <v>1</v>
       </c>
@@ -2947,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -3070,6 +3076,9 @@
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>1</v>
       </c>
@@ -3108,7 +3117,7 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -3146,7 +3155,7 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>68</v>
@@ -3187,10 +3196,10 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>54</v>
@@ -3407,7 +3416,7 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -3448,7 +3457,7 @@
         <v>15</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -3599,13 +3608,13 @@
         <v>4</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -3653,7 +3662,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -3668,7 +3677,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -3735,7 +3744,7 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8">
         <v>43</v>
@@ -3750,13 +3759,13 @@
         <v>48</v>
       </c>
       <c r="H8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I8">
         <v>41</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K8">
         <v>31</v>
@@ -3845,7 +3854,7 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -3941,7 +3950,7 @@
         <v>24</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -4020,7 +4029,7 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -4038,7 +4047,7 @@
         <v>27</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>17</v>
@@ -4067,13 +4076,13 @@
         <v>79</v>
       </c>
       <c r="D8">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F8">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G8">
         <v>78</v>
@@ -4082,7 +4091,7 @@
         <v>85</v>
       </c>
       <c r="I8">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J8">
         <v>54</v>
@@ -4158,10 +4167,10 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10">
         <v>16</v>
@@ -4202,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>2</v>
@@ -4405,7 +4414,7 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -4461,7 +4470,7 @@
         <v>34</v>
       </c>
       <c r="H19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I19">
         <v>28</v>
@@ -4552,7 +4561,7 @@
         <v>13</v>
       </c>
       <c r="K21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L21">
         <v>25</v>
@@ -4607,10 +4616,10 @@
         <v>33</v>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D23">
         <v>14</v>
@@ -4753,19 +4762,19 @@
         <v>16</v>
       </c>
       <c r="I27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27">
         <v>16</v>
       </c>
       <c r="K27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L27">
         <v>18</v>
       </c>
       <c r="M27">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -4791,7 +4800,7 @@
         <v>71</v>
       </c>
       <c r="H28">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I28">
         <v>76</v>
@@ -4803,7 +4812,7 @@
         <v>69</v>
       </c>
       <c r="L28">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M28">
         <v>38</v>
@@ -4820,7 +4829,7 @@
         <v>13</v>
       </c>
       <c r="D29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29">
         <v>21</v>
@@ -4922,19 +4931,19 @@
         <v>42</v>
       </c>
       <c r="B32">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E32">
         <v>110</v>
       </c>
       <c r="F32">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G32">
         <v>91</v>
@@ -4946,13 +4955,13 @@
         <v>79</v>
       </c>
       <c r="J32">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K32">
         <v>65</v>
       </c>
       <c r="L32">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M32">
         <v>49</v>
@@ -5018,13 +5027,13 @@
         <v>45</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35">
         <v>18</v>
       </c>
       <c r="D35">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E35">
         <v>19</v>
@@ -5059,7 +5068,7 @@
         <v>46</v>
       </c>
       <c r="B36">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C36">
         <v>80</v>
@@ -5071,10 +5080,10 @@
         <v>72</v>
       </c>
       <c r="F36">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G36">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H36">
         <v>52</v>
@@ -5086,10 +5095,10 @@
         <v>45</v>
       </c>
       <c r="K36">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L36">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M36">
         <v>41</v>
@@ -5252,13 +5261,13 @@
         <v>11</v>
       </c>
       <c r="J41">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L41">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M41">
         <v>15</v>
@@ -5275,13 +5284,13 @@
         <v>4</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>10</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5319,7 +5328,7 @@
         <v>19</v>
       </c>
       <c r="E43">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F43">
         <v>12</v>
@@ -5439,7 +5448,7 @@
         <v>3</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46">
         <v>2</v>
@@ -5468,7 +5477,7 @@
         <v>44</v>
       </c>
       <c r="C47">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D47">
         <v>43</v>
@@ -5483,13 +5492,13 @@
         <v>48</v>
       </c>
       <c r="H47">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I47">
         <v>41</v>
       </c>
       <c r="J47">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K47">
         <v>31</v>
@@ -5506,10 +5515,10 @@
         <v>58</v>
       </c>
       <c r="B48">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D48">
         <v>14</v>
@@ -5527,7 +5536,7 @@
         <v>5</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J48">
         <v>10</v>
@@ -5609,7 +5618,7 @@
         <v>22</v>
       </c>
       <c r="I50">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J50">
         <v>26</v>
@@ -5656,7 +5665,7 @@
         <v>3</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L51">
         <v>8</v>
@@ -5697,7 +5706,7 @@
         <v>24</v>
       </c>
       <c r="K52">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L52">
         <v>22</v>
@@ -5711,37 +5720,37 @@
         <v>63</v>
       </c>
       <c r="B53">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C53">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D53">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="E53">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F53">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G53">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H53">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I53">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J53">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K53">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L53">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M53">
         <v>94</v>
@@ -5773,7 +5782,7 @@
         <v>6</v>
       </c>
       <c r="I54">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J54">
         <v>9</v>
@@ -5936,7 +5945,7 @@
         <v>2</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -5985,7 +5994,7 @@
         <v>47</v>
       </c>
       <c r="F61">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G61">
         <v>19</v>
@@ -6006,7 +6015,7 @@
         <v>14</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6023,7 +6032,7 @@
         <v>21</v>
       </c>
       <c r="E62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F62">
         <v>20</v>
@@ -6041,7 +6050,7 @@
         <v>11</v>
       </c>
       <c r="K62">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L62">
         <v>10</v>
@@ -6137,16 +6146,16 @@
         <v>27</v>
       </c>
       <c r="C65">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D65">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E65">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F65">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G65">
         <v>41</v>
@@ -6158,10 +6167,10 @@
         <v>30</v>
       </c>
       <c r="J65">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L65">
         <v>19</v>
@@ -6228,7 +6237,7 @@
         <v>15</v>
       </c>
       <c r="F67">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G67">
         <v>8</v>
@@ -6312,6 +6321,9 @@
       <c r="H69">
         <v>1</v>
       </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
       <c r="K69">
         <v>1</v>
       </c>
@@ -6327,7 +6339,7 @@
         <v>80</v>
       </c>
       <c r="B70">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C70">
         <v>27</v>
@@ -6348,13 +6360,13 @@
         <v>18</v>
       </c>
       <c r="I70">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J70">
         <v>18</v>
       </c>
       <c r="K70">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L70">
         <v>12</v>
@@ -6395,7 +6407,7 @@
         <v>4</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71">
         <v>3</v>
@@ -6418,7 +6430,7 @@
         <v>11</v>
       </c>
       <c r="E72">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F72">
         <v>30</v>
@@ -6494,13 +6506,13 @@
         <v>18</v>
       </c>
       <c r="I74">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J74">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K74">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L74">
         <v>16</v>
@@ -6561,10 +6573,10 @@
         <v>44</v>
       </c>
       <c r="E76">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F76">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G76">
         <v>37</v>
@@ -6582,7 +6594,7 @@
         <v>40</v>
       </c>
       <c r="L76">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M76">
         <v>24</v>
@@ -6593,37 +6605,37 @@
         <v>87</v>
       </c>
       <c r="B77">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C77">
         <v>57</v>
       </c>
       <c r="D77">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E77">
         <v>58</v>
       </c>
       <c r="F77">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G77">
         <v>43</v>
       </c>
       <c r="H77">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I77">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J77">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K77">
         <v>54</v>
       </c>
       <c r="L77">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M77">
         <v>28</v>
@@ -6661,7 +6673,7 @@
         <v>15</v>
       </c>
       <c r="K78">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L78">
         <v>12</v>
@@ -6692,7 +6704,7 @@
         <v>20</v>
       </c>
       <c r="D80">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E80">
         <v>28</v>
@@ -6727,7 +6739,7 @@
         <v>91</v>
       </c>
       <c r="B81">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C81">
         <v>13</v>
@@ -6754,13 +6766,13 @@
         <v>9</v>
       </c>
       <c r="K81">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L81">
         <v>15</v>
       </c>
       <c r="M81">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -6771,7 +6783,7 @@
         <v>4</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -6812,10 +6824,10 @@
         <v>28</v>
       </c>
       <c r="D83">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E83">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F83">
         <v>23</v>
@@ -6897,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85">
         <v>3</v>
@@ -6961,7 +6973,7 @@
         <v>31</v>
       </c>
       <c r="C87">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D87">
         <v>18</v>
@@ -6973,7 +6985,7 @@
         <v>23</v>
       </c>
       <c r="G87">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H87">
         <v>24</v>
@@ -7052,7 +7064,7 @@
         <v>15</v>
       </c>
       <c r="F89">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G89">
         <v>11</v>
@@ -7175,7 +7187,7 @@
         <v>17</v>
       </c>
       <c r="I92">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J92">
         <v>21</v>
@@ -7248,7 +7260,7 @@
         <v>2</v>
       </c>
       <c r="F94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H94">
         <v>2</v>
@@ -7280,10 +7292,10 @@
         <v>25</v>
       </c>
       <c r="D95">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E95">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F95">
         <v>54</v>
@@ -7321,7 +7333,7 @@
         <v>14</v>
       </c>
       <c r="D96">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E96">
         <v>28</v>
@@ -7415,13 +7427,13 @@
         <v>7</v>
       </c>
       <c r="H98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I98">
         <v>4</v>
       </c>
       <c r="J98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K98">
         <v>7</v>
@@ -7438,40 +7450,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1456</v>
+        <v>1469</v>
       </c>
       <c r="C99">
-        <v>1764</v>
+        <v>1779</v>
       </c>
       <c r="D99">
-        <v>1935</v>
+        <v>1956</v>
       </c>
       <c r="E99">
-        <v>2260</v>
+        <v>2274</v>
       </c>
       <c r="F99">
-        <v>2339</v>
+        <v>2357</v>
       </c>
       <c r="G99">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="H99">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="I99">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="J99">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="K99">
-        <v>1297</v>
+        <v>1314</v>
       </c>
       <c r="L99">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="M99">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -7683,7 +7695,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -7718,7 +7730,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -7800,10 +7812,10 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -7979,7 +7991,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -8020,7 +8032,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>8</v>
@@ -8058,10 +8070,10 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7">
         <v>16</v>
@@ -8350,7 +8362,7 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J8">
         <v>18</v>
@@ -8391,7 +8403,7 @@
         <v>17</v>
       </c>
       <c r="I9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <v>21</v>
@@ -8539,10 +8551,10 @@
         <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -8584,7 +8596,7 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -8602,7 +8614,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -8619,16 +8631,16 @@
         <v>14</v>
       </c>
       <c r="C7">
+        <v>31</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
         <v>30</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>26</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
       </c>
       <c r="G7">
         <v>24</v>
@@ -8660,16 +8672,16 @@
         <v>27</v>
       </c>
       <c r="C8">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>41</v>
@@ -8681,10 +8693,10 @@
         <v>30</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8">
         <v>19</v>
@@ -8782,7 +8794,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -8858,7 +8870,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -8866,7 +8878,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -8907,7 +8919,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>13</v>
@@ -8934,13 +8946,13 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6">
         <v>15</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8950,7 +8962,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -9078,132 +9090,140 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
       <c r="K6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>21</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>14</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>25</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>18</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>19</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>24</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>24</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>11</v>
       </c>
-      <c r="J7">
-        <v>26</v>
-      </c>
-      <c r="K7">
-        <v>13</v>
-      </c>
-      <c r="L7">
-        <v>15</v>
-      </c>
-      <c r="M7">
+      <c r="J8">
+        <v>27</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
         <v>15</v>
       </c>
     </row>
@@ -9337,7 +9357,7 @@
         <v>7</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3">
         <v>14</v>
@@ -9393,7 +9413,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>27</v>
@@ -9423,7 +9443,7 @@
         <v>22</v>
       </c>
       <c r="L7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>13</v>
@@ -9437,16 +9457,16 @@
         <v>39</v>
       </c>
       <c r="C8">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8">
         <v>64</v>
       </c>
       <c r="F8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G8">
         <v>48</v>
@@ -9458,7 +9478,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K8">
         <v>25</v>
@@ -9475,19 +9495,19 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E9">
         <v>110</v>
       </c>
       <c r="F9">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G9">
         <v>91</v>
@@ -9499,13 +9519,13 @@
         <v>79</v>
       </c>
       <c r="J9">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K9">
         <v>65</v>
       </c>
       <c r="L9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M9">
         <v>49</v>
@@ -9710,7 +9730,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -9751,7 +9771,7 @@
         <v>15</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7">
         <v>12</v>
@@ -11460,7 +11480,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>25</v>
@@ -11501,7 +11521,7 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>28</v>
@@ -11903,7 +11923,7 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -11944,7 +11964,7 @@
         <v>15</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -12138,7 +12158,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -12182,10 +12202,10 @@
         <v>20</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -12220,13 +12240,13 @@
         <v>18</v>
       </c>
       <c r="I7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>16</v>
@@ -12242,7 +12262,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12305,79 +12325,55 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -12387,7 +12383,7 @@
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -12395,159 +12391,131 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
       <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
         <v>6</v>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
         <v>7</v>
       </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
       <c r="J7">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L8">
+        <v>18</v>
+      </c>
+      <c r="M8">
         <v>16</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>43</v>
-      </c>
-      <c r="C9">
-        <v>37</v>
-      </c>
-      <c r="D9">
-        <v>28</v>
-      </c>
-      <c r="E9">
-        <v>37</v>
-      </c>
-      <c r="F9">
-        <v>37</v>
-      </c>
-      <c r="G9">
-        <v>25</v>
-      </c>
-      <c r="H9">
-        <v>22</v>
-      </c>
-      <c r="I9">
-        <v>30</v>
-      </c>
-      <c r="J9">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>32</v>
-      </c>
-      <c r="L9">
-        <v>15</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>64</v>
-      </c>
-      <c r="C10">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>41</v>
-      </c>
-      <c r="E10">
-        <v>58</v>
-      </c>
-      <c r="F10">
-        <v>51</v>
-      </c>
-      <c r="G10">
-        <v>43</v>
-      </c>
-      <c r="H10">
-        <v>45</v>
-      </c>
-      <c r="I10">
-        <v>70</v>
-      </c>
-      <c r="J10">
-        <v>57</v>
-      </c>
-      <c r="K10">
-        <v>54</v>
-      </c>
-      <c r="L10">
-        <v>38</v>
-      </c>
-      <c r="M10">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -12783,7 +12751,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12846,26 +12814,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12873,38 +12856,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
@@ -12912,7 +12904,19 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
       <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -12920,131 +12924,139 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F6">
+      <c r="D6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>13</v>
+      </c>
+      <c r="D8">
         <v>8</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
       <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
         <v>12</v>
       </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
       <c r="H8">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
         <v>6</v>
-      </c>
-      <c r="K8">
-        <v>6</v>
-      </c>
-      <c r="L8">
-        <v>4</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>28</v>
+      </c>
+      <c r="E9">
+        <v>37</v>
+      </c>
+      <c r="F9">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>23</v>
+      </c>
+      <c r="I9">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>32</v>
+      </c>
+      <c r="K9">
+        <v>32</v>
+      </c>
+      <c r="L9">
+        <v>15</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>7</v>
-      </c>
-      <c r="D9">
-        <v>11</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>16</v>
-      </c>
-      <c r="I9">
-        <v>24</v>
-      </c>
-      <c r="J9">
-        <v>13</v>
-      </c>
-      <c r="K9">
-        <v>26</v>
-      </c>
-      <c r="L9">
-        <v>25</v>
-      </c>
-      <c r="M9">
-        <v>7</v>
+      <c r="B10">
+        <v>65</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>42</v>
+      </c>
+      <c r="E10">
+        <v>58</v>
+      </c>
+      <c r="F10">
+        <v>52</v>
+      </c>
+      <c r="G10">
+        <v>43</v>
+      </c>
+      <c r="H10">
+        <v>46</v>
+      </c>
+      <c r="I10">
+        <v>72</v>
+      </c>
+      <c r="J10">
+        <v>58</v>
+      </c>
+      <c r="K10">
+        <v>54</v>
+      </c>
+      <c r="L10">
+        <v>39</v>
+      </c>
+      <c r="M10">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -13117,41 +13129,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>2</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13159,47 +13156,38 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -13207,30 +13195,15 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+      <c r="I5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
     </row>
@@ -13239,40 +13212,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -13280,40 +13253,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13321,40 +13294,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E9">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="H9">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="I9">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="K9">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="L9">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="M9">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13363,6 +13336,316 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>11</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>44</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>45</v>
+      </c>
+      <c r="D8">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>74</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>32</v>
+      </c>
+      <c r="I8">
+        <v>33</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>79</v>
+      </c>
+      <c r="D9">
+        <v>49</v>
+      </c>
+      <c r="E9">
+        <v>90</v>
+      </c>
+      <c r="F9">
+        <v>110</v>
+      </c>
+      <c r="G9">
+        <v>78</v>
+      </c>
+      <c r="H9">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>63</v>
+      </c>
+      <c r="J9">
+        <v>54</v>
+      </c>
+      <c r="K9">
+        <v>57</v>
+      </c>
+      <c r="L9">
+        <v>45</v>
+      </c>
+      <c r="M9">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13579,10 +13862,10 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7">
         <v>24</v>
@@ -13600,7 +13883,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M7">
         <v>15</v>
@@ -13620,10 +13903,10 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>37</v>
@@ -13641,226 +13924,10 @@
         <v>40</v>
       </c>
       <c r="L8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M8">
         <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -13936,26 +14003,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -13965,45 +14020,24 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
       <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -14012,40 +14046,22 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
       <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>15</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14053,40 +14069,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>7</v>
       </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
       <c r="F6">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14094,40 +14110,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -14136,6 +14152,273 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>15</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>30</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14331,7 +14614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14504,7 +14787,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -14586,7 +14869,7 @@
         <v>24</v>
       </c>
       <c r="K8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8">
         <v>22</v>
@@ -14600,7 +14883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14848,269 +15131,6 @@
       </c>
       <c r="M7">
         <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>21</v>
-      </c>
-      <c r="D8">
-        <v>23</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>16</v>
-      </c>
-      <c r="I8">
-        <v>17</v>
-      </c>
-      <c r="J8">
-        <v>16</v>
-      </c>
-      <c r="K8">
-        <v>19</v>
-      </c>
-      <c r="L8">
-        <v>18</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -15256,7 +15276,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -15270,10 +15290,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -15311,10 +15331,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -15332,7 +15352,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -15486,10 +15506,10 @@
         <v>9</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -15560,10 +15580,10 @@
         <v>19</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7">
         <v>20</v>
@@ -15578,7 +15598,7 @@
         <v>33</v>
       </c>
       <c r="L7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7">
         <v>13</v>
@@ -15589,7 +15609,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>49</v>
@@ -15630,7 +15650,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>80</v>
@@ -15642,10 +15662,10 @@
         <v>72</v>
       </c>
       <c r="F9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9">
         <v>52</v>
@@ -15657,10 +15677,10 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L9">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M9">
         <v>41</v>
@@ -15760,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -15867,7 +15887,7 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -15890,7 +15910,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>20</v>
@@ -15908,7 +15928,7 @@
         <v>11</v>
       </c>
       <c r="K8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -15983,6 +16003,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="K2">
         <v>1</v>
       </c>
@@ -16073,7 +16096,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>3</v>
@@ -16158,6 +16181,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>1</v>
       </c>
@@ -16251,7 +16277,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -17082,7 +17108,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -17123,7 +17149,7 @@
         <v>13</v>
       </c>
       <c r="D9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9">
         <v>21</v>
@@ -17324,6 +17350,9 @@
       <c r="J6">
         <v>3</v>
       </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
       <c r="L6">
         <v>6</v>
       </c>
@@ -17363,7 +17392,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -17872,7 +17901,7 @@
         <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -18028,7 +18057,7 @@
         <v>31</v>
       </c>
       <c r="H8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I8">
         <v>38</v>
@@ -18069,7 +18098,7 @@
         <v>71</v>
       </c>
       <c r="H9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I9">
         <v>76</v>
@@ -18081,7 +18110,7 @@
         <v>69</v>
       </c>
       <c r="L9">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M9">
         <v>38</v>
@@ -18242,7 +18271,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>23</v>
@@ -18283,7 +18312,7 @@
         <v>11</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>30</v>
@@ -18421,6 +18450,9 @@
       <c r="B5">
         <v>3</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="D5">
         <v>1</v>
       </c>
@@ -18480,7 +18512,7 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -18684,7 +18716,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -18737,7 +18769,7 @@
         <v>15</v>
       </c>
       <c r="G8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8">
         <v>11</v>
@@ -18766,7 +18798,7 @@
         <v>31</v>
       </c>
       <c r="C9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>18</v>
@@ -18778,7 +18810,7 @@
         <v>23</v>
       </c>
       <c r="G9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9">
         <v>24</v>
@@ -19214,7 +19246,7 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -19255,7 +19287,7 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -19364,6 +19396,9 @@
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="J2">
         <v>1</v>
       </c>
@@ -19428,7 +19463,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -19504,13 +19539,13 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -19733,7 +19768,7 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -19765,7 +19800,7 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -20044,7 +20079,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -20103,7 +20138,7 @@
         <v>19</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -20126,7 +20161,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -20144,7 +20179,7 @@
         <v>27</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>17</v>
@@ -20260,7 +20295,7 @@
         <v>15</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2">
         <v>14</v>
@@ -20286,25 +20321,25 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>15</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3">
         <v>27</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3">
         <v>23</v>
       </c>
       <c r="L3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3">
         <v>16</v>
@@ -20404,13 +20439,13 @@
         <v>54</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8">
         <v>48</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I8">
         <v>69</v>
@@ -20422,7 +20457,7 @@
         <v>41</v>
       </c>
       <c r="L8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M8">
         <v>21</v>
@@ -20433,37 +20468,37 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C9">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D9">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E9">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F9">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G9">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H9">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I9">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K9">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M9">
         <v>50</v>
@@ -20474,37 +20509,37 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C10">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D10">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="E10">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F10">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G10">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H10">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I10">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J10">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K10">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L10">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M10">
         <v>94</v>
@@ -20659,13 +20694,13 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>7</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -20700,13 +20735,13 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -21118,10 +21153,10 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -21159,10 +21194,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>14</v>
@@ -21396,7 +21431,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -21476,7 +21511,7 @@
         <v>3</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -22128,6 +22163,9 @@
       <c r="D4">
         <v>3</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="I4">
         <v>1</v>
       </c>
@@ -22172,7 +22210,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -22495,7 +22533,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -22527,7 +22565,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -22568,13 +22606,13 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>18</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>19</v>
@@ -23204,6 +23242,9 @@
       <c r="J3">
         <v>1</v>
       </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
       <c r="L3">
         <v>1</v>
       </c>
@@ -23289,7 +23330,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -23660,7 +23701,7 @@
 
 <file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -23672,9 +23713,10 @@
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -23694,16 +23736,19 @@
         <v>2021</v>
       </c>
       <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
         <v>2024</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2025</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -23711,7 +23756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -23722,7 +23767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -23732,11 +23777,11 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -23755,8 +23800,11 @@
       <c r="H5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -23782,6 +23830,9 @@
         <v>1</v>
       </c>
       <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
     </row>
@@ -24240,7 +24291,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -24261,13 +24312,13 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>9</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -24281,7 +24332,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>27</v>
@@ -24302,13 +24353,13 @@
         <v>18</v>
       </c>
       <c r="I7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7">
         <v>18</v>
       </c>
       <c r="K7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>12</v>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="109">
   <si>
     <t>crime_category</t>
   </si>
@@ -878,7 +878,7 @@
         <v>57</v>
       </c>
       <c r="D2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2">
         <v>60</v>
@@ -893,10 +893,10 @@
         <v>92</v>
       </c>
       <c r="I2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K2">
         <v>121</v>
@@ -922,28 +922,28 @@
         <v>109</v>
       </c>
       <c r="E3">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F3">
         <v>102</v>
       </c>
       <c r="G3">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H3">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I3">
         <v>170</v>
       </c>
       <c r="J3">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K3">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L3">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M3">
         <v>162</v>
@@ -1030,7 +1030,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>21</v>
@@ -1039,7 +1039,7 @@
         <v>20</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1123,37 +1123,37 @@
         <v>314</v>
       </c>
       <c r="C9">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D9">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E9">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F9">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G9">
         <v>390</v>
       </c>
       <c r="H9">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I9">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J9">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K9">
         <v>422</v>
       </c>
       <c r="L9">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M9">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1161,34 +1161,34 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C10">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="D10">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="E10">
-        <v>1762</v>
+        <v>1766</v>
       </c>
       <c r="F10">
-        <v>1801</v>
+        <v>1804</v>
       </c>
       <c r="G10">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H10">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I10">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="J10">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K10">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="L10">
         <v>547</v>
@@ -1202,40 +1202,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="C11">
-        <v>1817</v>
+        <v>1826</v>
       </c>
       <c r="D11">
-        <v>1990</v>
+        <v>1997</v>
       </c>
       <c r="E11">
-        <v>2303</v>
+        <v>2309</v>
       </c>
       <c r="F11">
-        <v>2410</v>
+        <v>2414</v>
       </c>
       <c r="G11">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="H11">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="I11">
-        <v>1439</v>
+        <v>1444</v>
       </c>
       <c r="J11">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="K11">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="L11">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="M11">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -1565,6 +1565,9 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="F2">
         <v>2</v>
       </c>
@@ -1697,7 +1700,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -2235,7 +2238,7 @@
         <v>37</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9">
         <v>27</v>
@@ -2276,7 +2279,7 @@
         <v>46</v>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10">
         <v>40</v>
@@ -2879,6 +2882,9 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
       <c r="I5">
         <v>3</v>
       </c>
@@ -2950,7 +2956,7 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -3086,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -3155,7 +3161,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>35</v>
@@ -3196,7 +3202,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>46</v>
@@ -3220,7 +3226,7 @@
         <v>11</v>
       </c>
       <c r="K7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7">
         <v>24</v>
@@ -3706,7 +3712,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7">
         <v>34</v>
@@ -3747,7 +3753,7 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>43</v>
@@ -4053,7 +4059,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7">
         <v>13</v>
@@ -4082,10 +4088,10 @@
         <v>51</v>
       </c>
       <c r="E8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G8">
         <v>80</v>
@@ -4094,10 +4100,10 @@
         <v>86</v>
       </c>
       <c r="I8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J8">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>57</v>
@@ -4211,7 +4217,7 @@
         <v>2</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -4383,7 +4389,7 @@
         <v>3</v>
       </c>
       <c r="K16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -4400,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -4461,7 +4467,7 @@
         <v>46</v>
       </c>
       <c r="D19">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E19">
         <v>40</v>
@@ -4511,13 +4517,13 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20">
         <v>7</v>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -4540,7 +4546,7 @@
         <v>14</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>11</v>
@@ -4718,7 +4724,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -4794,7 +4800,7 @@
         <v>86</v>
       </c>
       <c r="E28">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28">
         <v>96</v>
@@ -4815,10 +4821,10 @@
         <v>71</v>
       </c>
       <c r="L28">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M28">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4946,7 +4952,7 @@
         <v>111</v>
       </c>
       <c r="F32">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G32">
         <v>92</v>
@@ -4955,7 +4961,7 @@
         <v>66</v>
       </c>
       <c r="I32">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J32">
         <v>67</v>
@@ -4964,7 +4970,7 @@
         <v>65</v>
       </c>
       <c r="L32">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M32">
         <v>49</v>
@@ -5080,7 +5086,7 @@
         <v>66</v>
       </c>
       <c r="E36">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F36">
         <v>71</v>
@@ -5104,7 +5110,7 @@
         <v>80</v>
       </c>
       <c r="M36">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5240,7 +5246,7 @@
         <v>51</v>
       </c>
       <c r="B41">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41">
         <v>25</v>
@@ -5480,7 +5486,7 @@
         <v>44</v>
       </c>
       <c r="C47">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D47">
         <v>43</v>
@@ -5521,7 +5527,7 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48">
         <v>14</v>
@@ -5653,7 +5659,7 @@
         <v>4</v>
       </c>
       <c r="F51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G51">
         <v>8</v>
@@ -5674,7 +5680,7 @@
         <v>8</v>
       </c>
       <c r="M51">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -5682,13 +5688,13 @@
         <v>62</v>
       </c>
       <c r="B52">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C52">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D52">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E52">
         <v>26</v>
@@ -5726,10 +5732,10 @@
         <v>194</v>
       </c>
       <c r="C53">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D53">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E53">
         <v>578</v>
@@ -5741,19 +5747,19 @@
         <v>219</v>
       </c>
       <c r="H53">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I53">
         <v>279</v>
       </c>
       <c r="J53">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K53">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L53">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M53">
         <v>97</v>
@@ -5770,7 +5776,7 @@
         <v>9</v>
       </c>
       <c r="D54">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E54">
         <v>12</v>
@@ -6003,7 +6009,7 @@
         <v>19</v>
       </c>
       <c r="H61">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I61">
         <v>17</v>
@@ -6152,7 +6158,7 @@
         <v>48</v>
       </c>
       <c r="D65">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E65">
         <v>37</v>
@@ -6252,7 +6258,7 @@
         <v>4</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K67">
         <v>6</v>
@@ -6354,19 +6360,19 @@
         <v>57</v>
       </c>
       <c r="F70">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G70">
         <v>34</v>
       </c>
       <c r="H70">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I70">
         <v>29</v>
       </c>
       <c r="J70">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K70">
         <v>28</v>
@@ -6515,7 +6521,7 @@
         <v>32</v>
       </c>
       <c r="K74">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L74">
         <v>17</v>
@@ -6567,10 +6573,10 @@
         <v>86</v>
       </c>
       <c r="B76">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C76">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D76">
         <v>47</v>
@@ -6588,7 +6594,7 @@
         <v>35</v>
       </c>
       <c r="I76">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J76">
         <v>38</v>
@@ -6608,7 +6614,7 @@
         <v>87</v>
       </c>
       <c r="B77">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C77">
         <v>59</v>
@@ -6617,16 +6623,16 @@
         <v>43</v>
       </c>
       <c r="E77">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F77">
         <v>53</v>
       </c>
       <c r="G77">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H77">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I77">
         <v>72</v>
@@ -6635,7 +6641,7 @@
         <v>59</v>
       </c>
       <c r="K77">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L77">
         <v>41</v>
@@ -6751,7 +6757,7 @@
         <v>8</v>
       </c>
       <c r="E81">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F81">
         <v>10</v>
@@ -6786,7 +6792,7 @@
         <v>4</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -6839,7 +6845,7 @@
         <v>13</v>
       </c>
       <c r="H83">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I83">
         <v>13</v>
@@ -6938,7 +6944,7 @@
         <v>19</v>
       </c>
       <c r="D86">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E86">
         <v>13</v>
@@ -7292,7 +7298,7 @@
         <v>13</v>
       </c>
       <c r="C95">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D95">
         <v>46</v>
@@ -7316,7 +7322,7 @@
         <v>11</v>
       </c>
       <c r="K95">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L95">
         <v>24</v>
@@ -7386,7 +7392,7 @@
         <v>18</v>
       </c>
       <c r="G97">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H97">
         <v>8</v>
@@ -7453,40 +7459,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="C99">
-        <v>1817</v>
+        <v>1826</v>
       </c>
       <c r="D99">
-        <v>1990</v>
+        <v>1997</v>
       </c>
       <c r="E99">
-        <v>2303</v>
+        <v>2309</v>
       </c>
       <c r="F99">
-        <v>2410</v>
+        <v>2414</v>
       </c>
       <c r="G99">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="H99">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="I99">
-        <v>1439</v>
+        <v>1444</v>
       </c>
       <c r="J99">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="K99">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="L99">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="M99">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -7789,7 +7795,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -7830,7 +7836,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>13</v>
@@ -8599,7 +8605,7 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -8681,7 +8687,7 @@
         <v>48</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8">
         <v>37</v>
@@ -8893,7 +8899,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -8934,7 +8940,7 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -9159,7 +9165,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -9200,7 +9206,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>25</v>
@@ -9452,7 +9458,7 @@
         <v>22</v>
       </c>
       <c r="L7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7">
         <v>13</v>
@@ -9475,7 +9481,7 @@
         <v>64</v>
       </c>
       <c r="F8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G8">
         <v>49</v>
@@ -9484,7 +9490,7 @@
         <v>24</v>
       </c>
       <c r="I8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J8">
         <v>29</v>
@@ -9516,7 +9522,7 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G9">
         <v>92</v>
@@ -9525,7 +9531,7 @@
         <v>66</v>
       </c>
       <c r="I9">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J9">
         <v>67</v>
@@ -9534,7 +9540,7 @@
         <v>65</v>
       </c>
       <c r="L9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M9">
         <v>49</v>
@@ -10007,7 +10013,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -10048,7 +10054,7 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -11240,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -11278,13 +11284,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>20</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>21</v>
@@ -11319,13 +11325,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>26</v>
@@ -12135,6 +12141,9 @@
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>1</v>
       </c>
@@ -12263,7 +12272,7 @@
         <v>4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -12492,7 +12501,7 @@
         <v>12</v>
       </c>
       <c r="K6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6">
         <v>8</v>
@@ -12533,7 +12542,7 @@
         <v>32</v>
       </c>
       <c r="K7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7">
         <v>17</v>
@@ -13421,7 +13430,7 @@
         <v>18</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>24</v>
@@ -13433,10 +13442,10 @@
         <v>45</v>
       </c>
       <c r="I7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -13462,10 +13471,10 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8">
         <v>52</v>
@@ -13503,10 +13512,10 @@
         <v>51</v>
       </c>
       <c r="E9">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F9">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G9">
         <v>80</v>
@@ -13515,10 +13524,10 @@
         <v>86</v>
       </c>
       <c r="I9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9">
         <v>57</v>
@@ -13969,7 +13978,7 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -14010,7 +14019,7 @@
         <v>18</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -14244,10 +14253,10 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>37</v>
@@ -14265,7 +14274,7 @@
         <v>19</v>
       </c>
       <c r="I7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <v>25</v>
@@ -14285,10 +14294,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8">
         <v>47</v>
@@ -14306,7 +14315,7 @@
         <v>35</v>
       </c>
       <c r="I8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J8">
         <v>38</v>
@@ -14708,7 +14717,7 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -14819,7 +14828,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9">
         <v>39</v>
@@ -14828,7 +14837,7 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9">
         <v>38</v>
@@ -14837,7 +14846,7 @@
         <v>25</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9">
         <v>30</v>
@@ -14846,7 +14855,7 @@
         <v>33</v>
       </c>
       <c r="K9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L9">
         <v>16</v>
@@ -14860,7 +14869,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10">
         <v>59</v>
@@ -14869,16 +14878,16 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F10">
         <v>53</v>
       </c>
       <c r="G10">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H10">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I10">
         <v>72</v>
@@ -14887,7 +14896,7 @@
         <v>59</v>
       </c>
       <c r="K10">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L10">
         <v>41</v>
@@ -15107,7 +15116,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -15148,7 +15157,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7">
         <v>13</v>
@@ -15319,7 +15328,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -15401,7 +15410,7 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>11</v>
@@ -15579,7 +15588,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15685,7 +15694,7 @@
         <v>37</v>
       </c>
       <c r="E8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>31</v>
@@ -15726,7 +15735,7 @@
         <v>66</v>
       </c>
       <c r="E9">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9">
         <v>71</v>
@@ -15750,7 +15759,7 @@
         <v>80</v>
       </c>
       <c r="M9">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -17393,7 +17402,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -17434,7 +17443,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -18173,7 +18182,7 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -18194,7 +18203,7 @@
         <v>15</v>
       </c>
       <c r="L3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -18220,7 +18229,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18283,7 +18292,7 @@
         <v>37</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -18341,7 +18350,7 @@
         <v>86</v>
       </c>
       <c r="E9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F9">
         <v>96</v>
@@ -18362,10 +18371,10 @@
         <v>71</v>
       </c>
       <c r="L9">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M9">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -18501,7 +18510,7 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -18539,7 +18548,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -19130,7 +19139,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19193,7 +19202,7 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -19234,7 +19243,7 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -19255,7 +19264,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -19337,6 +19346,9 @@
       <c r="H2">
         <v>2</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="L2">
         <v>1</v>
       </c>
@@ -19364,7 +19376,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -19486,13 +19498,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <v>7</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -20024,7 +20036,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -20059,7 +20071,7 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -20489,7 +20501,7 @@
         <v>10</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2">
         <v>13</v>
@@ -20536,7 +20548,7 @@
         <v>24</v>
       </c>
       <c r="L3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3">
         <v>17</v>
@@ -20668,10 +20680,10 @@
         <v>156</v>
       </c>
       <c r="C9">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D9">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E9">
         <v>511</v>
@@ -20683,16 +20695,16 @@
         <v>149</v>
       </c>
       <c r="H9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I9">
         <v>166</v>
       </c>
       <c r="J9">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K9">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L9">
         <v>69</v>
@@ -20709,10 +20721,10 @@
         <v>194</v>
       </c>
       <c r="C10">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D10">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E10">
         <v>578</v>
@@ -20724,19 +20736,19 @@
         <v>219</v>
       </c>
       <c r="H10">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I10">
         <v>279</v>
       </c>
       <c r="J10">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K10">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L10">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M10">
         <v>97</v>
@@ -24187,10 +24199,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -24317,124 +24329,132 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>21</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>32</v>
-      </c>
-      <c r="E6">
-        <v>45</v>
-      </c>
-      <c r="F6">
-        <v>74</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
       <c r="H6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>45</v>
+      </c>
+      <c r="F7">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>24</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>27</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>39</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>57</v>
       </c>
-      <c r="F7">
-        <v>94</v>
-      </c>
-      <c r="G7">
+      <c r="F8">
+        <v>95</v>
+      </c>
+      <c r="G8">
         <v>34</v>
       </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-      <c r="I7">
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
         <v>29</v>
       </c>
-      <c r="J7">
-        <v>18</v>
-      </c>
-      <c r="K7">
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
         <v>28</v>
       </c>
-      <c r="L7">
+      <c r="L8">
         <v>13</v>
       </c>
-      <c r="M7">
+      <c r="M8">
         <v>9</v>
       </c>
     </row>
@@ -24517,7 +24537,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -24543,7 +24563,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -25161,6 +25181,9 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
@@ -25198,7 +25221,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>1</v>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -14,14 +14,14 @@
     <sheet name="Grand Crossing" sheetId="5" r:id="rId5"/>
     <sheet name="Englewood" sheetId="6" r:id="rId6"/>
     <sheet name="Loop" sheetId="7" r:id="rId7"/>
-    <sheet name="Grand Boulevard" sheetId="8" r:id="rId8"/>
-    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Gage Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Lower West Side" sheetId="11" r:id="rId11"/>
-    <sheet name="Little Italy, UIC" sheetId="12" r:id="rId12"/>
-    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
-    <sheet name="Albany Park" sheetId="14" r:id="rId14"/>
-    <sheet name="Wicker Park" sheetId="15" r:id="rId15"/>
+    <sheet name="Old Town" sheetId="8" r:id="rId8"/>
+    <sheet name="Gage Park" sheetId="9" r:id="rId9"/>
+    <sheet name="Lower West Side" sheetId="10" r:id="rId10"/>
+    <sheet name="Little Italy, UIC" sheetId="11" r:id="rId11"/>
+    <sheet name="Chatham" sheetId="12" r:id="rId12"/>
+    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
+    <sheet name="Wicker Park" sheetId="14" r:id="rId14"/>
+    <sheet name="Grand Boulevard" sheetId="15" r:id="rId15"/>
     <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
     <sheet name="West Town" sheetId="17" r:id="rId17"/>
     <sheet name="Washington Park" sheetId="18" r:id="rId18"/>
@@ -55,22 +55,22 @@
     <sheet name="Near South Side" sheetId="46" r:id="rId46"/>
     <sheet name="Roseland" sheetId="47" r:id="rId47"/>
     <sheet name="Auburn Gresham" sheetId="48" r:id="rId48"/>
-    <sheet name="Chinatown" sheetId="49" r:id="rId49"/>
-    <sheet name="Mckinley Park" sheetId="50" r:id="rId50"/>
-    <sheet name="Irving Park" sheetId="51" r:id="rId51"/>
-    <sheet name="Armour Square" sheetId="52" r:id="rId52"/>
-    <sheet name="Uptown" sheetId="53" r:id="rId53"/>
-    <sheet name="West Elsdon" sheetId="54" r:id="rId54"/>
-    <sheet name="Douglas" sheetId="55" r:id="rId55"/>
-    <sheet name="Lincoln Park" sheetId="56" r:id="rId56"/>
-    <sheet name="Ukrainian Village" sheetId="57" r:id="rId57"/>
-    <sheet name="Calumet Heights" sheetId="58" r:id="rId58"/>
-    <sheet name="Clearing" sheetId="59" r:id="rId59"/>
-    <sheet name="Bucktown" sheetId="60" r:id="rId60"/>
-    <sheet name="Brighton Park" sheetId="61" r:id="rId61"/>
-    <sheet name="Fuller Park" sheetId="62" r:id="rId62"/>
-    <sheet name="Little Village" sheetId="63" r:id="rId63"/>
-    <sheet name="Chicago Lawn" sheetId="64" r:id="rId64"/>
+    <sheet name="Chicago Lawn" sheetId="49" r:id="rId49"/>
+    <sheet name="Chinatown" sheetId="50" r:id="rId50"/>
+    <sheet name="Mckinley Park" sheetId="51" r:id="rId51"/>
+    <sheet name="Irving Park" sheetId="52" r:id="rId52"/>
+    <sheet name="Armour Square" sheetId="53" r:id="rId53"/>
+    <sheet name="Uptown" sheetId="54" r:id="rId54"/>
+    <sheet name="West Elsdon" sheetId="55" r:id="rId55"/>
+    <sheet name="Douglas" sheetId="56" r:id="rId56"/>
+    <sheet name="Lincoln Park" sheetId="57" r:id="rId57"/>
+    <sheet name="Ukrainian Village" sheetId="58" r:id="rId58"/>
+    <sheet name="Calumet Heights" sheetId="59" r:id="rId59"/>
+    <sheet name="Clearing" sheetId="60" r:id="rId60"/>
+    <sheet name="Bucktown" sheetId="61" r:id="rId61"/>
+    <sheet name="Brighton Park" sheetId="62" r:id="rId62"/>
+    <sheet name="Fuller Park" sheetId="63" r:id="rId63"/>
+    <sheet name="Little Village" sheetId="64" r:id="rId64"/>
     <sheet name="Archer Heights" sheetId="65" r:id="rId65"/>
     <sheet name="Printers Row" sheetId="66" r:id="rId66"/>
     <sheet name="South Deering" sheetId="67" r:id="rId67"/>
@@ -875,7 +875,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2">
         <v>77</v>
@@ -893,7 +893,7 @@
         <v>92</v>
       </c>
       <c r="I2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J2">
         <v>99</v>
@@ -905,7 +905,7 @@
         <v>114</v>
       </c>
       <c r="M2">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -916,34 +916,34 @@
         <v>65</v>
       </c>
       <c r="C3">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3">
         <v>109</v>
       </c>
       <c r="E3">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F3">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I3">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J3">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K3">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L3">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M3">
         <v>162</v>
@@ -1021,10 +1021,10 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6">
         <v>19</v>
@@ -1123,34 +1123,34 @@
         <v>314</v>
       </c>
       <c r="C9">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D9">
         <v>336</v>
       </c>
       <c r="E9">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F9">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G9">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H9">
         <v>378</v>
       </c>
       <c r="I9">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J9">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K9">
         <v>422</v>
       </c>
       <c r="L9">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M9">
         <v>210</v>
@@ -1161,40 +1161,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="C10">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="D10">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="E10">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="F10">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="G10">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="H10">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I10">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="J10">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K10">
         <v>584</v>
       </c>
       <c r="L10">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M10">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1202,37 +1202,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="C11">
-        <v>1826</v>
+        <v>1837</v>
       </c>
       <c r="D11">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="E11">
-        <v>2309</v>
+        <v>2316</v>
       </c>
       <c r="F11">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="G11">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="H11">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="I11">
-        <v>1444</v>
+        <v>1451</v>
       </c>
       <c r="J11">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="K11">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="L11">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="M11">
         <v>903</v>
@@ -1244,260 +1244,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>27</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>9</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>13</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1659,13 +1405,13 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>9</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -1700,13 +1446,13 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -1735,7 +1481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1950,7 +1696,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1991,7 +1737,7 @@
         <v>20</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7">
         <v>36</v>
@@ -2008,7 +1754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2307,6 +2053,249 @@
       </c>
       <c r="M10">
         <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2379,60 +2368,36 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
+      <c r="E2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>2</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2442,32 +2407,29 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>1</v>
+      <c r="H5">
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2475,40 +2437,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>19</v>
+      </c>
+      <c r="G6">
         <v>7</v>
       </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>7</v>
       </c>
-      <c r="G6">
+      <c r="L6">
         <v>8</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
+      <c r="M6">
         <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2516,40 +2478,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>21</v>
+      </c>
+      <c r="G7">
         <v>7</v>
       </c>
-      <c r="C7">
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
         <v>13</v>
       </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7">
         <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>14</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2562,7 +2524,7 @@
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2622,28 +2584,52 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>1</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -2651,9 +2637,9 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
+        <v>6</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -2661,29 +2647,38 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2691,40 +2686,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
         <v>9</v>
       </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
       <c r="K6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2732,40 +2727,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>7</v>
       </c>
       <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
         <v>13</v>
       </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
       <c r="K7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3381,7 +3376,7 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -3463,7 +3458,7 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>13</v>
@@ -3709,7 +3704,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>41</v>
@@ -3750,7 +3745,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8">
         <v>64</v>
@@ -3956,7 +3951,7 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>19</v>
@@ -3965,7 +3960,7 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>31</v>
@@ -4091,7 +4086,7 @@
         <v>92</v>
       </c>
       <c r="F8">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G8">
         <v>80</v>
@@ -4100,10 +4095,10 @@
         <v>86</v>
       </c>
       <c r="I8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8">
         <v>57</v>
@@ -4286,7 +4281,7 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <v>9</v>
@@ -4505,7 +4500,7 @@
         <v>23</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -4535,7 +4530,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4558,7 +4553,7 @@
         <v>22</v>
       </c>
       <c r="G21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <v>17</v>
@@ -4750,7 +4745,7 @@
         <v>37</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27">
         <v>21</v>
@@ -4759,7 +4754,7 @@
         <v>23</v>
       </c>
       <c r="E27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -4794,7 +4789,7 @@
         <v>82</v>
       </c>
       <c r="C28">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28">
         <v>86</v>
@@ -4806,13 +4801,13 @@
         <v>96</v>
       </c>
       <c r="G28">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H28">
         <v>63</v>
       </c>
       <c r="I28">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J28">
         <v>46</v>
@@ -4853,7 +4848,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J29">
         <v>20</v>
@@ -4882,7 +4877,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F30">
         <v>9</v>
@@ -4943,7 +4938,7 @@
         <v>51</v>
       </c>
       <c r="C32">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D32">
         <v>84</v>
@@ -4955,13 +4950,13 @@
         <v>169</v>
       </c>
       <c r="G32">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32">
         <v>66</v>
       </c>
       <c r="I32">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J32">
         <v>67</v>
@@ -5036,10 +5031,10 @@
         <v>45</v>
       </c>
       <c r="B35">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D35">
         <v>16</v>
@@ -5069,7 +5064,7 @@
         <v>16</v>
       </c>
       <c r="M35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -5080,7 +5075,7 @@
         <v>59</v>
       </c>
       <c r="C36">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36">
         <v>66</v>
@@ -5107,7 +5102,7 @@
         <v>85</v>
       </c>
       <c r="L36">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M36">
         <v>42</v>
@@ -5118,7 +5113,7 @@
         <v>47</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -5174,7 +5169,7 @@
         <v>5</v>
       </c>
       <c r="H38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38">
         <v>9</v>
@@ -5258,7 +5253,7 @@
         <v>19</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G41">
         <v>27</v>
@@ -5401,7 +5396,7 @@
         <v>55</v>
       </c>
       <c r="B45">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45">
         <v>16</v>
@@ -5425,7 +5420,7 @@
         <v>11</v>
       </c>
       <c r="J45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K45">
         <v>14</v>
@@ -5483,7 +5478,7 @@
         <v>57</v>
       </c>
       <c r="B47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C47">
         <v>64</v>
@@ -5527,7 +5522,7 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48">
         <v>14</v>
@@ -5630,7 +5625,7 @@
         <v>20</v>
       </c>
       <c r="J50">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K50">
         <v>36</v>
@@ -5735,25 +5730,25 @@
         <v>295</v>
       </c>
       <c r="D53">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E53">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F53">
         <v>547</v>
       </c>
       <c r="G53">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H53">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I53">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J53">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K53">
         <v>172</v>
@@ -5776,13 +5771,13 @@
         <v>9</v>
       </c>
       <c r="D54">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E54">
         <v>12</v>
       </c>
       <c r="F54">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G54">
         <v>9</v>
@@ -5855,7 +5850,7 @@
         <v>6</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D56">
         <v>9</v>
@@ -6006,10 +6001,10 @@
         <v>39</v>
       </c>
       <c r="G61">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H61">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I61">
         <v>17</v>
@@ -6076,7 +6071,7 @@
         <v>11</v>
       </c>
       <c r="C63">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D63">
         <v>7</v>
@@ -6179,7 +6174,7 @@
         <v>13</v>
       </c>
       <c r="K65">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L65">
         <v>19</v>
@@ -6287,7 +6282,7 @@
         <v>22</v>
       </c>
       <c r="F68">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G68">
         <v>7</v>
@@ -6305,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="L68">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M68">
         <v>23</v>
@@ -6357,7 +6352,7 @@
         <v>39</v>
       </c>
       <c r="E70">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F70">
         <v>95</v>
@@ -6395,7 +6390,7 @@
         <v>2</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71">
         <v>4</v>
@@ -6433,7 +6428,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D72">
         <v>11</v>
@@ -6500,7 +6495,7 @@
         <v>34</v>
       </c>
       <c r="D74">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E74">
         <v>69</v>
@@ -6576,13 +6571,13 @@
         <v>42</v>
       </c>
       <c r="C76">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D76">
         <v>47</v>
       </c>
       <c r="E76">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F76">
         <v>54</v>
@@ -6620,7 +6615,7 @@
         <v>59</v>
       </c>
       <c r="D77">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E77">
         <v>61</v>
@@ -6632,19 +6627,19 @@
         <v>45</v>
       </c>
       <c r="H77">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I77">
         <v>72</v>
       </c>
       <c r="J77">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K77">
         <v>57</v>
       </c>
       <c r="L77">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M77">
         <v>29</v>
@@ -6801,7 +6796,7 @@
         <v>3</v>
       </c>
       <c r="F82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G82">
         <v>3</v>
@@ -6953,7 +6948,7 @@
         <v>22</v>
       </c>
       <c r="G86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H86">
         <v>6</v>
@@ -7070,7 +7065,7 @@
         <v>17</v>
       </c>
       <c r="E89">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F89">
         <v>13</v>
@@ -7342,7 +7337,7 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E96">
         <v>28</v>
@@ -7424,7 +7419,7 @@
         <v>10</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E98">
         <v>10</v>
@@ -7459,37 +7454,37 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="C99">
-        <v>1826</v>
+        <v>1837</v>
       </c>
       <c r="D99">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="E99">
-        <v>2309</v>
+        <v>2316</v>
       </c>
       <c r="F99">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="G99">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="H99">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="I99">
-        <v>1444</v>
+        <v>1451</v>
       </c>
       <c r="J99">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="K99">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="L99">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="M99">
         <v>903</v>
@@ -8566,7 +8561,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -8708,7 +8703,7 @@
         <v>13</v>
       </c>
       <c r="K8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L8">
         <v>19</v>
@@ -9136,7 +9131,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -9218,7 +9213,7 @@
         <v>19</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>27</v>
@@ -9363,7 +9358,7 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -9449,7 +9444,7 @@
         <v>32</v>
       </c>
       <c r="I7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7">
         <v>24</v>
@@ -9472,7 +9467,7 @@
         <v>39</v>
       </c>
       <c r="C8">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>41</v>
@@ -9513,7 +9508,7 @@
         <v>51</v>
       </c>
       <c r="C9">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>84</v>
@@ -9525,13 +9520,13 @@
         <v>169</v>
       </c>
       <c r="G9">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9">
         <v>66</v>
       </c>
       <c r="I9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J9">
         <v>67</v>
@@ -9981,7 +9976,7 @@
         <v>4</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -10063,7 +10058,7 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -10249,7 +10244,7 @@
         <v>22</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -10267,7 +10262,7 @@
         <v>11</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -10290,7 +10285,7 @@
         <v>22</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -10308,7 +10303,7 @@
         <v>16</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8">
         <v>23</v>
@@ -10578,6 +10573,9 @@
       <c r="H3">
         <v>3</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>2</v>
       </c>
@@ -10650,7 +10648,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -10691,7 +10689,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>16</v>
@@ -10715,7 +10713,7 @@
         <v>11</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8">
         <v>14</v>
@@ -10800,6 +10798,9 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>2</v>
       </c>
@@ -10917,7 +10918,7 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -11460,6 +11461,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>2</v>
       </c>
@@ -11547,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -11992,7 +11996,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -12033,7 +12037,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -12480,7 +12484,7 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6">
         <v>63</v>
@@ -12521,7 +12525,7 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7">
         <v>69</v>
@@ -12966,7 +12970,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -12975,7 +12979,7 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>16</v>
@@ -13007,7 +13011,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>21</v>
@@ -13016,7 +13020,7 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>24</v>
@@ -13442,10 +13446,10 @@
         <v>45</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -13474,7 +13478,7 @@
         <v>51</v>
       </c>
       <c r="F8">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8">
         <v>52</v>
@@ -13515,7 +13519,7 @@
         <v>92</v>
       </c>
       <c r="F9">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G9">
         <v>80</v>
@@ -13524,10 +13528,10 @@
         <v>86</v>
       </c>
       <c r="I9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K9">
         <v>57</v>
@@ -13714,7 +13718,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -13755,7 +13759,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -14256,13 +14260,13 @@
         <v>39</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7">
         <v>37</v>
       </c>
       <c r="E7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7">
         <v>39</v>
@@ -14297,13 +14301,13 @@
         <v>42</v>
       </c>
       <c r="C8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>47</v>
       </c>
       <c r="E8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8">
         <v>54</v>
@@ -14720,7 +14724,7 @@
         <v>4</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -14732,7 +14736,7 @@
         <v>6</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -14811,13 +14815,13 @@
         <v>27</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K8">
         <v>16</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -14834,7 +14838,7 @@
         <v>39</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>39</v>
@@ -14875,7 +14879,7 @@
         <v>59</v>
       </c>
       <c r="D10">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>61</v>
@@ -14887,19 +14891,19 @@
         <v>45</v>
       </c>
       <c r="H10">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I10">
         <v>72</v>
       </c>
       <c r="J10">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K10">
         <v>57</v>
       </c>
       <c r="L10">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M10">
         <v>29</v>
@@ -15179,7 +15183,7 @@
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15242,25 +15246,22 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -15269,178 +15270,165 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
       <c r="F7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
         <v>8</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>12</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>6</v>
-      </c>
-      <c r="K8">
-        <v>6</v>
-      </c>
-      <c r="L8">
-        <v>4</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>11</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>24</v>
-      </c>
-      <c r="J9">
-        <v>13</v>
-      </c>
-      <c r="K9">
-        <v>27</v>
-      </c>
-      <c r="L9">
-        <v>25</v>
-      </c>
-      <c r="M9">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15674,7 +15662,7 @@
         <v>35</v>
       </c>
       <c r="L7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M7">
         <v>13</v>
@@ -15688,7 +15676,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8">
         <v>37</v>
@@ -15729,7 +15717,7 @@
         <v>59</v>
       </c>
       <c r="C9">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9">
         <v>66</v>
@@ -15756,7 +15744,7 @@
         <v>85</v>
       </c>
       <c r="L9">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M9">
         <v>42</v>
@@ -15769,7 +15757,7 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15832,150 +15820,205 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="M2">
-        <v>1</v>
+      <c r="L2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
       </c>
       <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
         <v>6</v>
       </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
       <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>16</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="J8">
         <v>6</v>
       </c>
-      <c r="C7">
+      <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
+      <c r="B9">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>24</v>
+      </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
+      <c r="K9">
+        <v>27</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
         <v>7</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16051,29 +16094,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
         <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -16083,31 +16111,16 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
+      <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -16115,7 +16128,7 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -16127,36 +16140,18 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -16165,40 +16160,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>8</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16206,40 +16201,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
         <v>11</v>
       </c>
-      <c r="C7">
-        <v>12</v>
-      </c>
       <c r="D7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>14</v>
-      </c>
       <c r="M7">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16322,13 +16317,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -16347,42 +16345,36 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -16391,40 +16383,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16432,40 +16424,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>9</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>9</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16473,40 +16465,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C7">
+        <v>12</v>
+      </c>
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="D7">
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
         <v>12</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>31</v>
       </c>
       <c r="G7">
         <v>13</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -16515,6 +16507,273 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>16</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16803,7 +17062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16999,7 +17258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17247,7 +17506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17367,7 +17626,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -17443,7 +17702,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -17481,7 +17740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17655,7 +17914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17850,221 +18109,6 @@
       </c>
       <c r="M6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>12</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>16</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>5</v>
-      </c>
-      <c r="M8">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18176,7 +18220,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -18194,7 +18238,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -18315,7 +18359,7 @@
         <v>53</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8">
         <v>25</v>
@@ -18344,7 +18388,7 @@
         <v>82</v>
       </c>
       <c r="C9">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D9">
         <v>86</v>
@@ -18356,13 +18400,13 @@
         <v>96</v>
       </c>
       <c r="G9">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>63</v>
       </c>
       <c r="I9">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J9">
         <v>46</v>
@@ -18383,6 +18427,221 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <v>16</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18559,7 +18818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18770,7 +19029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18942,7 +19201,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -19024,7 +19283,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9">
         <v>20</v>
@@ -19037,234 +19296,6 @@
       </c>
       <c r="M9">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>5</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -19337,22 +19368,16 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
+      <c r="K2">
         <v>2</v>
       </c>
     </row>
@@ -19360,48 +19385,27 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -19410,30 +19414,33 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -19442,40 +19449,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
         <v>6</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
       <c r="M6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19483,40 +19490,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
       <c r="H7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
         <v>9</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -19824,7 +19831,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -19865,7 +19872,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -19985,7 +19992,7 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -20080,7 +20087,7 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -20498,7 +20505,7 @@
         <v>8</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>17</v>
@@ -20683,25 +20690,25 @@
         <v>250</v>
       </c>
       <c r="D9">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E9">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F9">
         <v>484</v>
       </c>
       <c r="G9">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H9">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I9">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J9">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K9">
         <v>90</v>
@@ -20724,25 +20731,25 @@
         <v>295</v>
       </c>
       <c r="D10">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E10">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F10">
         <v>547</v>
       </c>
       <c r="G10">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H10">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I10">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J10">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K10">
         <v>172</v>
@@ -22399,7 +22406,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -22431,7 +22438,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -22471,10 +22478,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -22534,14 +22541,14 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -22550,13 +22557,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22564,153 +22568,173 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>9</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>45</v>
+      </c>
+      <c r="F7">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>39</v>
+      </c>
+      <c r="E8">
+        <v>58</v>
+      </c>
+      <c r="F8">
+        <v>95</v>
+      </c>
+      <c r="G8">
+        <v>34</v>
+      </c>
+      <c r="H8">
         <v>19</v>
       </c>
-      <c r="F7">
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>28</v>
+      </c>
+      <c r="L8">
         <v>13</v>
       </c>
-      <c r="G7">
-        <v>14</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
+      <c r="M8">
         <v>9</v>
-      </c>
-      <c r="J7">
-        <v>13</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -23342,7 +23366,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -23380,7 +23404,7 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -24262,25 +24286,22 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -24291,45 +24312,39 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -24340,40 +24355,37 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24381,40 +24393,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -24422,40 +24434,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C8">
+        <v>23</v>
+      </c>
+      <c r="D8">
         <v>27</v>
       </c>
-      <c r="D8">
-        <v>39</v>
-      </c>
       <c r="E8">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H8">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="L8">
         <v>13</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-ytd.xlsx
+++ b/output/cta-index-crime-ytd.xlsx
@@ -59,24 +59,24 @@
     <sheet name="Douglas" sheetId="50" r:id="rId50"/>
     <sheet name="Printers Row" sheetId="51" r:id="rId51"/>
     <sheet name="Hyde Park" sheetId="52" r:id="rId52"/>
-    <sheet name="Chinatown" sheetId="53" r:id="rId53"/>
-    <sheet name="Mckinley Park" sheetId="54" r:id="rId54"/>
-    <sheet name="Irving Park" sheetId="55" r:id="rId55"/>
-    <sheet name="Armour Square" sheetId="56" r:id="rId56"/>
-    <sheet name="Uptown" sheetId="57" r:id="rId57"/>
+    <sheet name="Uptown" sheetId="53" r:id="rId53"/>
+    <sheet name="Chinatown" sheetId="54" r:id="rId54"/>
+    <sheet name="Mckinley Park" sheetId="55" r:id="rId55"/>
+    <sheet name="Irving Park" sheetId="56" r:id="rId56"/>
+    <sheet name="Armour Square" sheetId="57" r:id="rId57"/>
     <sheet name="West Elsdon" sheetId="58" r:id="rId58"/>
     <sheet name="Morgan Park" sheetId="59" r:id="rId59"/>
-    <sheet name="Montclare" sheetId="60" r:id="rId60"/>
-    <sheet name="Lincoln Park" sheetId="61" r:id="rId61"/>
-    <sheet name="Ukrainian Village" sheetId="62" r:id="rId62"/>
-    <sheet name="Calumet Heights" sheetId="63" r:id="rId63"/>
-    <sheet name="Clearing" sheetId="64" r:id="rId64"/>
-    <sheet name="Bucktown" sheetId="65" r:id="rId65"/>
-    <sheet name="Brighton Park" sheetId="66" r:id="rId66"/>
-    <sheet name="Fuller Park" sheetId="67" r:id="rId67"/>
-    <sheet name="Little Village" sheetId="68" r:id="rId68"/>
-    <sheet name="Archer Heights" sheetId="69" r:id="rId69"/>
-    <sheet name="South Deering" sheetId="70" r:id="rId70"/>
+    <sheet name="South Deering" sheetId="60" r:id="rId60"/>
+    <sheet name="Montclare" sheetId="61" r:id="rId61"/>
+    <sheet name="Lincoln Park" sheetId="62" r:id="rId62"/>
+    <sheet name="Ukrainian Village" sheetId="63" r:id="rId63"/>
+    <sheet name="Calumet Heights" sheetId="64" r:id="rId64"/>
+    <sheet name="Clearing" sheetId="65" r:id="rId65"/>
+    <sheet name="Bucktown" sheetId="66" r:id="rId66"/>
+    <sheet name="Brighton Park" sheetId="67" r:id="rId67"/>
+    <sheet name="Fuller Park" sheetId="68" r:id="rId68"/>
+    <sheet name="Little Village" sheetId="69" r:id="rId69"/>
+    <sheet name="Archer Heights" sheetId="70" r:id="rId70"/>
     <sheet name="Washington Heights" sheetId="71" r:id="rId71"/>
     <sheet name="Boystown" sheetId="72" r:id="rId72"/>
     <sheet name="West Ridge" sheetId="73" r:id="rId73"/>
@@ -878,13 +878,13 @@
         <v>58</v>
       </c>
       <c r="D2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E2">
         <v>60</v>
       </c>
       <c r="F2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>74</v>
@@ -902,7 +902,7 @@
         <v>123</v>
       </c>
       <c r="L2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M2">
         <v>99</v>
@@ -913,31 +913,31 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E3">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F3">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G3">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H3">
         <v>122</v>
       </c>
       <c r="I3">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J3">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K3">
         <v>190</v>
@@ -1009,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -1120,37 +1120,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C9">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D9">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E9">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F9">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G9">
         <v>393</v>
       </c>
       <c r="H9">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I9">
         <v>433</v>
       </c>
       <c r="J9">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K9">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L9">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M9">
         <v>213</v>
@@ -1161,40 +1161,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="C10">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="D10">
-        <v>1489</v>
+        <v>1500</v>
       </c>
       <c r="E10">
-        <v>1784</v>
+        <v>1792</v>
       </c>
       <c r="F10">
-        <v>1825</v>
+        <v>1834</v>
       </c>
       <c r="G10">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="H10">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I10">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="J10">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="K10">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L10">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M10">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1202,40 +1202,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1530</v>
+        <v>1543</v>
       </c>
       <c r="C11">
-        <v>1854</v>
+        <v>1866</v>
       </c>
       <c r="D11">
-        <v>2029</v>
+        <v>2044</v>
       </c>
       <c r="E11">
-        <v>2341</v>
+        <v>2352</v>
       </c>
       <c r="F11">
-        <v>2448</v>
+        <v>2461</v>
       </c>
       <c r="G11">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="H11">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="I11">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="J11">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="K11">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="L11">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="M11">
-        <v>920</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1912,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5">
         <v>11</v>
@@ -1994,7 +1994,7 @@
         <v>27</v>
       </c>
       <c r="K7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L7">
         <v>38</v>
@@ -2171,6 +2171,9 @@
       <c r="H6">
         <v>1</v>
       </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
@@ -2232,7 +2235,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>37</v>
@@ -2262,7 +2265,7 @@
         <v>16</v>
       </c>
       <c r="L9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M9">
         <v>11</v>
@@ -2273,7 +2276,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>46</v>
@@ -2294,7 +2297,7 @@
         <v>20</v>
       </c>
       <c r="I10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J10">
         <v>35</v>
@@ -2303,7 +2306,7 @@
         <v>47</v>
       </c>
       <c r="L10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M10">
         <v>23</v>
@@ -2487,7 +2490,7 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -2528,7 +2531,7 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -2870,6 +2873,9 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>2</v>
       </c>
@@ -2984,7 +2990,7 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>16</v>
@@ -3296,6 +3302,9 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
       <c r="G2">
         <v>2</v>
       </c>
@@ -3360,7 +3369,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -3442,7 +3451,7 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -3451,7 +3460,7 @@
         <v>16</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -3697,7 +3706,7 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7">
         <v>34</v>
@@ -3738,7 +3747,7 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>44</v>
@@ -3854,7 +3863,7 @@
         <v>8</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -3944,10 +3953,10 @@
         <v>25</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>17</v>
@@ -4044,7 +4053,7 @@
         <v>11</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>13</v>
@@ -4070,7 +4079,7 @@
         <v>82</v>
       </c>
       <c r="D8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8">
         <v>92</v>
@@ -4082,7 +4091,7 @@
         <v>80</v>
       </c>
       <c r="H8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I8">
         <v>68</v>
@@ -4248,7 +4257,7 @@
         <v>23</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4268,7 +4277,7 @@
         <v>24</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>9</v>
@@ -4446,7 +4455,7 @@
         <v>29</v>
       </c>
       <c r="B19">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>46</v>
@@ -4467,7 +4476,7 @@
         <v>20</v>
       </c>
       <c r="I19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J19">
         <v>35</v>
@@ -4476,7 +4485,7 @@
         <v>47</v>
       </c>
       <c r="L19">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M19">
         <v>23</v>
@@ -4511,7 +4520,7 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>4</v>
@@ -4546,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I21">
         <v>24</v>
@@ -4619,10 +4628,10 @@
         <v>16</v>
       </c>
       <c r="E23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -4768,7 +4777,7 @@
         <v>18</v>
       </c>
       <c r="M27">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -4776,22 +4785,22 @@
         <v>38</v>
       </c>
       <c r="B28">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28">
         <v>117</v>
       </c>
       <c r="D28">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E28">
         <v>75</v>
       </c>
       <c r="F28">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G28">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H28">
         <v>63</v>
@@ -4826,7 +4835,7 @@
         <v>24</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F29">
         <v>24</v>
@@ -4931,10 +4940,10 @@
         <v>80</v>
       </c>
       <c r="D32">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F32">
         <v>171</v>
@@ -4949,7 +4958,7 @@
         <v>83</v>
       </c>
       <c r="J32">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K32">
         <v>65</v>
@@ -5024,7 +5033,7 @@
         <v>18</v>
       </c>
       <c r="C35">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D35">
         <v>16</v>
@@ -5086,7 +5095,7 @@
         <v>67</v>
       </c>
       <c r="J36">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K36">
         <v>85</v>
@@ -5188,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -5252,7 +5261,7 @@
         <v>15</v>
       </c>
       <c r="I41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J41">
         <v>27</v>
@@ -5313,7 +5322,7 @@
         <v>53</v>
       </c>
       <c r="B43">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C43">
         <v>13</v>
@@ -5401,13 +5410,13 @@
         <v>21</v>
       </c>
       <c r="G45">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H45">
         <v>15</v>
       </c>
       <c r="I45">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J45">
         <v>11</v>
@@ -5471,7 +5480,7 @@
         <v>45</v>
       </c>
       <c r="C47">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D47">
         <v>44</v>
@@ -5618,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="K50">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L50">
         <v>38</v>
@@ -5714,40 +5723,40 @@
         <v>63</v>
       </c>
       <c r="B53">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C53">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D53">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E53">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F53">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="G53">
         <v>222</v>
       </c>
       <c r="H53">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I53">
         <v>284</v>
       </c>
       <c r="J53">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K53">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L53">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M53">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5988,7 +5997,7 @@
         <v>22</v>
       </c>
       <c r="E61">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F61">
         <v>40</v>
@@ -6012,7 +6021,7 @@
         <v>14</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6032,7 +6041,7 @@
         <v>23</v>
       </c>
       <c r="F62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G62">
         <v>14</v>
@@ -6041,10 +6050,10 @@
         <v>12</v>
       </c>
       <c r="I62">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J62">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K62">
         <v>18</v>
@@ -6152,7 +6161,7 @@
         <v>37</v>
       </c>
       <c r="F65">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G65">
         <v>41</v>
@@ -6170,7 +6179,7 @@
         <v>26</v>
       </c>
       <c r="L65">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M65">
         <v>16</v>
@@ -6228,13 +6237,13 @@
         <v>10</v>
       </c>
       <c r="D67">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E67">
         <v>16</v>
       </c>
       <c r="F67">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G67">
         <v>8</v>
@@ -6255,7 +6264,7 @@
         <v>7</v>
       </c>
       <c r="M67">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6266,7 +6275,7 @@
         <v>10</v>
       </c>
       <c r="C68">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68">
         <v>22</v>
@@ -6290,7 +6299,7 @@
         <v>12</v>
       </c>
       <c r="K68">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L68">
         <v>17</v>
@@ -6342,7 +6351,7 @@
         <v>28</v>
       </c>
       <c r="D70">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E70">
         <v>58</v>
@@ -6421,7 +6430,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D72">
         <v>11</v>
@@ -6494,7 +6503,7 @@
         <v>69</v>
       </c>
       <c r="F74">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G74">
         <v>30</v>
@@ -6564,10 +6573,10 @@
         <v>44</v>
       </c>
       <c r="C76">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D76">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E76">
         <v>85</v>
@@ -6602,10 +6611,10 @@
         <v>87</v>
       </c>
       <c r="B77">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C77">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D77">
         <v>44</v>
@@ -6646,7 +6655,7 @@
         <v>35</v>
       </c>
       <c r="C78">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D78">
         <v>52</v>
@@ -6736,7 +6745,7 @@
         <v>91</v>
       </c>
       <c r="B81">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C81">
         <v>14</v>
@@ -6807,7 +6816,7 @@
         <v>1</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M82">
         <v>2</v>
@@ -6824,7 +6833,7 @@
         <v>28</v>
       </c>
       <c r="D83">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E83">
         <v>19</v>
@@ -6833,7 +6842,7 @@
         <v>23</v>
       </c>
       <c r="G83">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H83">
         <v>17</v>
@@ -6959,7 +6968,7 @@
         <v>11</v>
       </c>
       <c r="L86">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M86">
         <v>9</v>
@@ -6970,7 +6979,7 @@
         <v>97</v>
       </c>
       <c r="B87">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C87">
         <v>35</v>
@@ -7000,10 +7009,10 @@
         <v>29</v>
       </c>
       <c r="L87">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M87">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -7055,7 +7064,7 @@
         <v>20</v>
       </c>
       <c r="C89">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D89">
         <v>17</v>
@@ -7064,7 +7073,7 @@
         <v>16</v>
       </c>
       <c r="F89">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G89">
         <v>12</v>
@@ -7105,7 +7114,7 @@
         <v>9</v>
       </c>
       <c r="F90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90">
         <v>4</v>
@@ -7193,7 +7202,7 @@
         <v>22</v>
       </c>
       <c r="K92">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L92">
         <v>19</v>
@@ -7216,7 +7225,7 @@
         <v>5</v>
       </c>
       <c r="E93">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93">
         <v>8</v>
@@ -7450,40 +7459,40 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>1530</v>
+        <v>1543</v>
       </c>
       <c r="C99">
-        <v>1854</v>
+        <v>1866</v>
       </c>
       <c r="D99">
-        <v>2029</v>
+        <v>2044</v>
       </c>
       <c r="E99">
-        <v>2341</v>
+        <v>2352</v>
       </c>
       <c r="F99">
-        <v>2448</v>
+        <v>2461</v>
       </c>
       <c r="G99">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="H99">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="I99">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="J99">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="K99">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="L99">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="M99">
-        <v>920</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -7703,6 +7712,9 @@
       <c r="F3">
         <v>3</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>5</v>
       </c>
@@ -7774,7 +7786,7 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>11</v>
@@ -7815,7 +7827,7 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>19</v>
@@ -7824,7 +7836,7 @@
         <v>23</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6">
         <v>17</v>
@@ -8333,7 +8345,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -8415,7 +8427,7 @@
         <v>22</v>
       </c>
       <c r="K9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9">
         <v>19</v>
@@ -8525,7 +8537,7 @@
         <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -8605,7 +8617,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <v>11</v>
@@ -8687,7 +8699,7 @@
         <v>37</v>
       </c>
       <c r="F8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>41</v>
@@ -8705,7 +8717,7 @@
         <v>26</v>
       </c>
       <c r="L8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M8">
         <v>16</v>
@@ -8884,7 +8896,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -8925,7 +8937,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -9183,7 +9195,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -9224,7 +9236,7 @@
         <v>15</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8">
         <v>27</v>
@@ -9434,7 +9446,7 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>47</v>
@@ -9472,10 +9484,10 @@
         <v>48</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8">
         <v>114</v>
@@ -9490,7 +9502,7 @@
         <v>44</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8">
         <v>25</v>
@@ -9513,10 +9525,10 @@
         <v>80</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F9">
         <v>171</v>
@@ -9531,7 +9543,7 @@
         <v>83</v>
       </c>
       <c r="J9">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K9">
         <v>65</v>
@@ -9724,7 +9736,7 @@
         <v>29</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>48</v>
@@ -9765,7 +9777,7 @@
         <v>35</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>52</v>
@@ -9993,7 +10005,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -10075,7 +10087,7 @@
         <v>11</v>
       </c>
       <c r="L9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -10699,13 +10711,13 @@
         <v>18</v>
       </c>
       <c r="G7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7">
         <v>7</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -10740,13 +10752,13 @@
         <v>21</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8">
         <v>15</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8">
         <v>11</v>
@@ -11543,7 +11555,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -11584,7 +11596,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -12253,13 +12265,13 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>15</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -12280,7 +12292,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -12294,13 +12306,13 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>16</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -12321,7 +12333,7 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -12526,7 +12538,7 @@
         <v>63</v>
       </c>
       <c r="F6">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6">
         <v>17</v>
@@ -12567,7 +12579,7 @@
         <v>69</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7">
         <v>30</v>
@@ -12710,6 +12722,9 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
       </c>
@@ -12774,7 +12789,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -12791,7 +12806,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>22</v>
@@ -12815,7 +12830,7 @@
         <v>12</v>
       </c>
       <c r="K8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8">
         <v>17</v>
@@ -13046,7 +13061,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -13087,7 +13102,7 @@
         <v>18</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -13394,7 +13409,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>6</v>
@@ -13527,7 +13542,7 @@
         <v>52</v>
       </c>
       <c r="H8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8">
         <v>34</v>
@@ -13556,7 +13571,7 @@
         <v>82</v>
       </c>
       <c r="D9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9">
         <v>92</v>
@@ -13568,7 +13583,7 @@
         <v>80</v>
       </c>
       <c r="H9">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I9">
         <v>68</v>
@@ -14306,10 +14321,10 @@
         <v>41</v>
       </c>
       <c r="C7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>68</v>
@@ -14347,10 +14362,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D8">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8">
         <v>85</v>
@@ -14549,7 +14564,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -14578,7 +14593,7 @@
         <v>17</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -14587,7 +14602,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -14619,7 +14634,7 @@
         <v>23</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8">
         <v>14</v>
@@ -14628,10 +14643,10 @@
         <v>12</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8">
         <v>18</v>
@@ -14840,7 +14855,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>13</v>
@@ -14884,7 +14899,7 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>30</v>
@@ -14922,10 +14937,10 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10">
         <v>44</v>
@@ -15082,7 +15097,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -15210,7 +15225,7 @@
         <v>11</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>13</v>
@@ -15427,7 +15442,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -15468,7 +15483,7 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>4</v>
@@ -15806,7 +15821,7 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -15851,7 +15866,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -15930,10 +15945,10 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -16068,7 +16083,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -16147,7 +16162,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -16470,65 +16485,83 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>3</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -16536,15 +16569,15 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I5">
+      <c r="B5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
@@ -16556,10 +16589,10 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -16568,25 +16601,25 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -16594,40 +16627,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16635,40 +16668,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I9">
+        <v>18</v>
+      </c>
+      <c r="J9">
         <v>24</v>
       </c>
-      <c r="J9">
-        <v>13</v>
-      </c>
       <c r="K9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -16678,7 +16711,7 @@
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15